--- a/public/templates/cac_mau_doi_soat_v3.xlsx
+++ b/public/templates/cac_mau_doi_soat_v3.xlsx
@@ -737,7 +737,7 @@
     <t>CỘNG</t>
   </si>
   <si>
-    <t xml:space="preserve"> Doanh số Vacom HCM đạt được (M-invoice thực thu) trong tháng 07/2025</t>
+    <t xml:space="preserve"> Doanh số Vacom HCM đạt được (M-invoice thực thu) trong tháng </t>
   </si>
   <si>
     <t>=K24</t>
@@ -752,7 +752,7 @@
     <t>=K25</t>
   </si>
   <si>
-    <t>HCM, ngày 07 tháng 11 năm 2025</t>
+    <t xml:space="preserve">HCM, ngày   tháng   năm  </t>
   </si>
   <si>
     <t>M-INVOICE HCM</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">BẢNG KÊ PHÁT TRIỂN HÓA ĐƠN ĐIỆN TỬ CHO KHÁCH HÀNG </t>
   </si>
   <si>
-    <t xml:space="preserve">Số </t>
+    <t xml:space="preserve">Số : </t>
   </si>
   <si>
     <t>NGÀY PHÁT SINH</t>

--- a/public/templates/cac_mau_doi_soat_v3.xlsx
+++ b/public/templates/cac_mau_doi_soat_v3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10440" activeTab="3"/>
+    <workbookView windowWidth="23040" windowHeight="10440" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="MẪU VACOM CKS" sheetId="6" r:id="rId1"/>
@@ -10098,10 +10098,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="J9" s="58"/>
       <c r="K9" s="58">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -10118,10 +10115,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O9" s="58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="O9" s="58"/>
     </row>
     <row r="10" s="45" customFormat="1" ht="34.5" customHeight="1" spans="1:15">
       <c r="A10" s="59"/>
@@ -10170,10 +10164,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J11" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="J11" s="61"/>
       <c r="K11" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -10190,10 +10181,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O11" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="O11" s="61"/>
     </row>
     <row r="12" s="45" customFormat="1" ht="38.4" customHeight="1" spans="1:15">
       <c r="A12" s="59"/>
@@ -10239,10 +10227,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J13" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J13" s="67"/>
       <c r="K13" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -10259,10 +10244,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O13" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="O13" s="67"/>
       <c r="Q13" s="106"/>
     </row>
     <row r="14" s="44" customFormat="1" ht="38.4" customHeight="1" spans="1:15">
@@ -10309,10 +10291,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J15" s="58">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="J15" s="58"/>
       <c r="K15" s="58">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -10329,10 +10308,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O15" s="58">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="O15" s="58"/>
       <c r="Q15" s="106"/>
     </row>
     <row r="16" s="44" customFormat="1" ht="38.4" customHeight="1" spans="1:15">
@@ -10387,10 +10363,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J17" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+      <c r="J17" s="73"/>
       <c r="K17" s="73">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -10407,10 +10380,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O17" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+      <c r="O17" s="73"/>
       <c r="Q17" s="106"/>
     </row>
     <row r="18" s="44" customFormat="1" ht="38.4" customHeight="1" spans="1:15">
@@ -10457,10 +10427,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J19" s="73">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="J19" s="73"/>
       <c r="K19" s="73">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -10477,10 +10444,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O19" s="73">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="O19" s="73"/>
       <c r="Q19" s="106"/>
     </row>
     <row r="20" s="44" customFormat="1" ht="38.4" customHeight="1" spans="1:15">
@@ -10527,10 +10491,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J21" s="60">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
+      <c r="J21" s="60"/>
       <c r="K21" s="60">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -10547,10 +10508,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O21" s="60">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
+      <c r="O21" s="60"/>
     </row>
     <row r="22" s="44" customFormat="1" ht="35.25" customHeight="1" spans="1:15">
       <c r="A22" s="59"/>
@@ -10596,10 +10554,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J23" s="84">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
+      <c r="J23" s="84"/>
       <c r="K23" s="84">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -10616,10 +10571,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="O23" s="84">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
+      <c r="O23" s="84"/>
     </row>
     <row r="24" s="46" customFormat="1" ht="17.25" customHeight="1" spans="3:14">
       <c r="C24" s="85" t="s">

--- a/public/templates/cac_mau_doi_soat_v3.xlsx
+++ b/public/templates/cac_mau_doi_soat_v3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10440" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="10440" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="MẪU VACOM CKS" sheetId="6" r:id="rId1"/>
@@ -258,7 +258,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="215">
   <si>
     <t>CÔNG TY TNHH HÓA ĐƠN ĐIỆN TỬ M-INVOICE - CN TPHỒ CHÍ MINH</t>
   </si>
@@ -650,10 +650,7 @@
     <t xml:space="preserve">BẢNG KÊ PHÁT TRIỂN KHÁCH HÀNG  </t>
   </si>
   <si>
-    <t xml:space="preserve">THÁNG: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ĐẠI LÝ: </t>
+    <t>THÁNG: 11/2025</t>
   </si>
   <si>
     <t>Số 10.2025MINV/HCM/VC</t>
@@ -737,10 +734,7 @@
     <t>CỘNG</t>
   </si>
   <si>
-    <t xml:space="preserve"> Doanh số Vacom HCM đạt được (M-invoice thực thu) trong tháng </t>
-  </si>
-  <si>
-    <t>=K24</t>
+    <t xml:space="preserve"> Doanh số Vacom HCM đạt được (M-invoice thực thu) trong tháng 07/2025</t>
   </si>
   <si>
     <t>% thưởng đạt doanh số</t>
@@ -749,10 +743,7 @@
     <t>Tổng Minvoice HCM thực thu:</t>
   </si>
   <si>
-    <t>=K25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCM, ngày   tháng   năm  </t>
+    <t>HCM, ngày 07 tháng 11 năm 2025</t>
   </si>
   <si>
     <t>M-INVOICE HCM</t>
@@ -912,6 +903,9 @@
   </si>
   <si>
     <t xml:space="preserve">BẢNG KÊ PHÁT TRIỂN HÓA ĐƠN ĐIỆN TỬ CHO KHÁCH HÀNG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ĐẠI LÝ: </t>
   </si>
   <si>
     <t xml:space="preserve">Số : </t>
@@ -2012,7 +2006,7 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="197">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="64" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="71" applyFont="1" applyAlignment="1"/>
@@ -2272,222 +2266,228 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="59" applyFont="1" applyFill="1"/>
     <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="69" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="64" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="64" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="64" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="64" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="64" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="64" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="64" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="64" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="64" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="64" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="66" applyFont="1"/>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="64" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="66" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="64" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="64" applyFont="1"/>
-    <xf numFmtId="17" fontId="18" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="64" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="17" fontId="18" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="64" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="64" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="20" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="20" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="64" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="64" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="64" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="64" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="64" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="64" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="64" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="9" borderId="14" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="9" borderId="15" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="9" borderId="16" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="9" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="10" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="10" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="10" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="10" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="10" borderId="14" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="10" borderId="15" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="10" borderId="16" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="4" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="64" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="64" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="16" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="64" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="18" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="64" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="5" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="64" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="64" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="64" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="64" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="64" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="64" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="64" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="13" xfId="64" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="11" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="64" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="64" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="64" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="64" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="64" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="9" borderId="14" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="9" borderId="15" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="9" borderId="16" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="9" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="10" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="10" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="10" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="10" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="10" borderId="14" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="10" borderId="15" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="10" borderId="16" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="4" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="64" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="64" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="16" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="64" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="18" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="64" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="5" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="64" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="64" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="64" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="64" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="64" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="64" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="64" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="13" xfId="64" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="11" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="64" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="64" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="64" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="64" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="64" applyFont="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2514,13 +2514,18 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="64" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="64" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="64" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="66" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="66" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="17" fontId="18" fillId="0" borderId="0" xfId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="74">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2637,6 +2642,74 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1184910" cy="657225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>851535</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -3982,7 +4055,7 @@
       <c r="E4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="197" t="s">
+      <c r="F4" s="201" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="172"/>
@@ -4120,1760 +4193,1760 @@
       <c r="H12" s="181" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="196"/>
-      <c r="J12" s="196"/>
-      <c r="K12" s="196"/>
-      <c r="L12" s="196"/>
-      <c r="M12" s="196"/>
-      <c r="N12" s="196"/>
-      <c r="O12" s="196"/>
-      <c r="P12" s="196"/>
-      <c r="Q12" s="196"/>
-      <c r="R12" s="196"/>
-      <c r="S12" s="196"/>
-      <c r="T12" s="196"/>
-      <c r="U12" s="196"/>
+      <c r="I12" s="198"/>
+      <c r="J12" s="198"/>
+      <c r="K12" s="198"/>
+      <c r="L12" s="198"/>
+      <c r="M12" s="198"/>
+      <c r="N12" s="198"/>
+      <c r="O12" s="198"/>
+      <c r="P12" s="198"/>
+      <c r="Q12" s="198"/>
+      <c r="R12" s="198"/>
+      <c r="S12" s="198"/>
+      <c r="T12" s="198"/>
+      <c r="U12" s="198"/>
     </row>
     <row r="13" ht="38.25" customHeight="1" spans="1:21">
       <c r="A13" s="182">
         <v>1</v>
       </c>
-      <c r="B13" s="147" t="s">
+      <c r="B13" s="183" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="183" t="s">
+      <c r="C13" s="184" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="184" t="s">
+      <c r="D13" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="185">
+      <c r="E13" s="186">
         <v>560000</v>
       </c>
-      <c r="F13" s="186">
+      <c r="F13" s="187">
         <f t="shared" ref="F13" si="0">E13*8%</f>
         <v>44800</v>
       </c>
-      <c r="G13" s="187">
+      <c r="G13" s="188">
         <f t="shared" ref="G13:G55" si="1">E13+F13</f>
         <v>604800</v>
       </c>
-      <c r="H13" s="124"/>
-      <c r="I13" s="107"/>
-      <c r="J13" s="164"/>
-      <c r="K13" s="107"/>
-      <c r="L13" s="107"/>
-      <c r="M13" s="196"/>
-      <c r="N13" s="196"/>
-      <c r="O13" s="196"/>
-      <c r="P13" s="196"/>
-      <c r="Q13" s="196"/>
-      <c r="R13" s="196"/>
-      <c r="S13" s="196"/>
-      <c r="T13" s="196"/>
-      <c r="U13" s="196"/>
+      <c r="H13" s="189"/>
+      <c r="I13" s="199"/>
+      <c r="J13" s="200"/>
+      <c r="K13" s="199"/>
+      <c r="L13" s="199"/>
+      <c r="M13" s="198"/>
+      <c r="N13" s="198"/>
+      <c r="O13" s="198"/>
+      <c r="P13" s="198"/>
+      <c r="Q13" s="198"/>
+      <c r="R13" s="198"/>
+      <c r="S13" s="198"/>
+      <c r="T13" s="198"/>
+      <c r="U13" s="198"/>
     </row>
     <row r="14" ht="38.25" customHeight="1" spans="1:21">
       <c r="A14" s="182">
         <f>A13+1</f>
         <v>2</v>
       </c>
-      <c r="B14" s="147" t="s">
+      <c r="B14" s="183" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="183" t="s">
+      <c r="C14" s="184" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="184" t="s">
+      <c r="D14" s="185" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="185"/>
-      <c r="F14" s="186"/>
-      <c r="G14" s="187"/>
-      <c r="H14" s="124"/>
-      <c r="I14" s="107"/>
-      <c r="J14" s="164"/>
-      <c r="K14" s="107"/>
-      <c r="L14" s="107"/>
-      <c r="M14" s="196"/>
-      <c r="N14" s="196"/>
-      <c r="O14" s="196"/>
-      <c r="P14" s="196"/>
-      <c r="Q14" s="196"/>
-      <c r="R14" s="196"/>
-      <c r="S14" s="196"/>
-      <c r="T14" s="196"/>
-      <c r="U14" s="196"/>
+      <c r="E14" s="186"/>
+      <c r="F14" s="187"/>
+      <c r="G14" s="188"/>
+      <c r="H14" s="189"/>
+      <c r="I14" s="199"/>
+      <c r="J14" s="200"/>
+      <c r="K14" s="199"/>
+      <c r="L14" s="199"/>
+      <c r="M14" s="198"/>
+      <c r="N14" s="198"/>
+      <c r="O14" s="198"/>
+      <c r="P14" s="198"/>
+      <c r="Q14" s="198"/>
+      <c r="R14" s="198"/>
+      <c r="S14" s="198"/>
+      <c r="T14" s="198"/>
+      <c r="U14" s="198"/>
     </row>
     <row r="15" ht="38.25" customHeight="1" spans="1:21">
       <c r="A15" s="182">
         <f t="shared" ref="A15:A55" si="2">A14+1</f>
         <v>3</v>
       </c>
-      <c r="B15" s="147" t="s">
+      <c r="B15" s="183" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="183" t="s">
+      <c r="C15" s="184" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="184" t="s">
+      <c r="D15" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="185">
+      <c r="E15" s="186">
         <v>560000</v>
       </c>
-      <c r="F15" s="186">
+      <c r="F15" s="187">
         <f t="shared" ref="F15" si="3">E15*8%</f>
         <v>44800</v>
       </c>
-      <c r="G15" s="187">
+      <c r="G15" s="188">
         <f t="shared" si="1"/>
         <v>604800</v>
       </c>
-      <c r="H15" s="124"/>
-      <c r="I15" s="107"/>
-      <c r="J15" s="164"/>
-      <c r="K15" s="107"/>
-      <c r="L15" s="107"/>
-      <c r="M15" s="196"/>
-      <c r="N15" s="196"/>
-      <c r="O15" s="196"/>
-      <c r="P15" s="196"/>
-      <c r="Q15" s="196"/>
-      <c r="R15" s="196"/>
-      <c r="S15" s="196"/>
-      <c r="T15" s="196"/>
-      <c r="U15" s="196"/>
+      <c r="H15" s="189"/>
+      <c r="I15" s="199"/>
+      <c r="J15" s="200"/>
+      <c r="K15" s="199"/>
+      <c r="L15" s="199"/>
+      <c r="M15" s="198"/>
+      <c r="N15" s="198"/>
+      <c r="O15" s="198"/>
+      <c r="P15" s="198"/>
+      <c r="Q15" s="198"/>
+      <c r="R15" s="198"/>
+      <c r="S15" s="198"/>
+      <c r="T15" s="198"/>
+      <c r="U15" s="198"/>
     </row>
     <row r="16" ht="38.25" customHeight="1" spans="1:21">
       <c r="A16" s="182">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="B16" s="147" t="s">
+      <c r="B16" s="183" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="183" t="s">
+      <c r="C16" s="184" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="184" t="s">
+      <c r="D16" s="185" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="185"/>
-      <c r="F16" s="186"/>
-      <c r="G16" s="187"/>
-      <c r="H16" s="124"/>
-      <c r="I16" s="107"/>
-      <c r="J16" s="164"/>
-      <c r="K16" s="107"/>
-      <c r="L16" s="107"/>
-      <c r="M16" s="196"/>
-      <c r="N16" s="196"/>
-      <c r="O16" s="196"/>
-      <c r="P16" s="196"/>
-      <c r="Q16" s="196"/>
-      <c r="R16" s="196"/>
-      <c r="S16" s="196"/>
-      <c r="T16" s="196"/>
-      <c r="U16" s="196"/>
+      <c r="E16" s="186"/>
+      <c r="F16" s="187"/>
+      <c r="G16" s="188"/>
+      <c r="H16" s="189"/>
+      <c r="I16" s="199"/>
+      <c r="J16" s="200"/>
+      <c r="K16" s="199"/>
+      <c r="L16" s="199"/>
+      <c r="M16" s="198"/>
+      <c r="N16" s="198"/>
+      <c r="O16" s="198"/>
+      <c r="P16" s="198"/>
+      <c r="Q16" s="198"/>
+      <c r="R16" s="198"/>
+      <c r="S16" s="198"/>
+      <c r="T16" s="198"/>
+      <c r="U16" s="198"/>
     </row>
     <row r="17" ht="38.25" customHeight="1" spans="1:21">
       <c r="A17" s="182">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="B17" s="147" t="s">
+      <c r="B17" s="183" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="183" t="s">
+      <c r="C17" s="184" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="184" t="s">
+      <c r="D17" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="185">
+      <c r="E17" s="186">
         <v>560000</v>
       </c>
-      <c r="F17" s="186">
+      <c r="F17" s="187">
         <f t="shared" ref="F17:F18" si="4">E17*8%</f>
         <v>44800</v>
       </c>
-      <c r="G17" s="187">
+      <c r="G17" s="188">
         <f t="shared" si="1"/>
         <v>604800</v>
       </c>
-      <c r="H17" s="188"/>
-      <c r="I17" s="107"/>
-      <c r="J17" s="164"/>
-      <c r="K17" s="107"/>
-      <c r="L17" s="107"/>
-      <c r="M17" s="196"/>
-      <c r="N17" s="196"/>
-      <c r="O17" s="196"/>
-      <c r="P17" s="196"/>
-      <c r="Q17" s="196"/>
-      <c r="R17" s="196"/>
-      <c r="S17" s="196"/>
-      <c r="T17" s="196"/>
-      <c r="U17" s="196"/>
+      <c r="H17" s="190"/>
+      <c r="I17" s="199"/>
+      <c r="J17" s="200"/>
+      <c r="K17" s="199"/>
+      <c r="L17" s="199"/>
+      <c r="M17" s="198"/>
+      <c r="N17" s="198"/>
+      <c r="O17" s="198"/>
+      <c r="P17" s="198"/>
+      <c r="Q17" s="198"/>
+      <c r="R17" s="198"/>
+      <c r="S17" s="198"/>
+      <c r="T17" s="198"/>
+      <c r="U17" s="198"/>
     </row>
     <row r="18" ht="38.25" customHeight="1" spans="1:21">
       <c r="A18" s="182">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="B18" s="147" t="s">
+      <c r="B18" s="183" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="183" t="s">
+      <c r="C18" s="184" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="184" t="s">
+      <c r="D18" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="185">
+      <c r="E18" s="186">
         <v>560000</v>
       </c>
-      <c r="F18" s="186">
+      <c r="F18" s="187">
         <f t="shared" si="4"/>
         <v>44800</v>
       </c>
-      <c r="G18" s="187">
+      <c r="G18" s="188">
         <f t="shared" si="1"/>
         <v>604800</v>
       </c>
-      <c r="H18" s="188"/>
-      <c r="I18" s="107"/>
-      <c r="J18" s="164"/>
-      <c r="K18" s="107"/>
-      <c r="L18" s="107"/>
-      <c r="M18" s="196"/>
-      <c r="N18" s="196"/>
-      <c r="O18" s="196"/>
-      <c r="P18" s="196"/>
-      <c r="Q18" s="196"/>
-      <c r="R18" s="196"/>
-      <c r="S18" s="196"/>
-      <c r="T18" s="196"/>
-      <c r="U18" s="196"/>
+      <c r="H18" s="190"/>
+      <c r="I18" s="199"/>
+      <c r="J18" s="200"/>
+      <c r="K18" s="199"/>
+      <c r="L18" s="199"/>
+      <c r="M18" s="198"/>
+      <c r="N18" s="198"/>
+      <c r="O18" s="198"/>
+      <c r="P18" s="198"/>
+      <c r="Q18" s="198"/>
+      <c r="R18" s="198"/>
+      <c r="S18" s="198"/>
+      <c r="T18" s="198"/>
+      <c r="U18" s="198"/>
     </row>
     <row r="19" ht="38.25" customHeight="1" spans="1:21">
       <c r="A19" s="182">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="B19" s="147" t="s">
+      <c r="B19" s="183" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="183" t="s">
+      <c r="C19" s="184" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="184" t="s">
+      <c r="D19" s="185" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="185"/>
-      <c r="F19" s="186"/>
-      <c r="G19" s="187"/>
-      <c r="H19" s="188"/>
-      <c r="I19" s="107"/>
-      <c r="J19" s="164"/>
-      <c r="K19" s="107"/>
-      <c r="L19" s="107"/>
-      <c r="M19" s="196"/>
-      <c r="N19" s="196"/>
-      <c r="O19" s="196"/>
-      <c r="P19" s="196"/>
-      <c r="Q19" s="196"/>
-      <c r="R19" s="196"/>
-      <c r="S19" s="196"/>
-      <c r="T19" s="196"/>
-      <c r="U19" s="196"/>
+      <c r="E19" s="186"/>
+      <c r="F19" s="187"/>
+      <c r="G19" s="188"/>
+      <c r="H19" s="190"/>
+      <c r="I19" s="199"/>
+      <c r="J19" s="200"/>
+      <c r="K19" s="199"/>
+      <c r="L19" s="199"/>
+      <c r="M19" s="198"/>
+      <c r="N19" s="198"/>
+      <c r="O19" s="198"/>
+      <c r="P19" s="198"/>
+      <c r="Q19" s="198"/>
+      <c r="R19" s="198"/>
+      <c r="S19" s="198"/>
+      <c r="T19" s="198"/>
+      <c r="U19" s="198"/>
     </row>
     <row r="20" ht="31.9" customHeight="1" spans="1:21">
       <c r="A20" s="182">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="B20" s="147" t="s">
+      <c r="B20" s="183" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="183" t="s">
+      <c r="C20" s="184" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="184" t="s">
+      <c r="D20" s="185" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="185">
+      <c r="E20" s="186">
         <v>367000</v>
       </c>
-      <c r="F20" s="186">
+      <c r="F20" s="187">
         <f t="shared" ref="F20:F55" si="5">E20*8%</f>
         <v>29360</v>
       </c>
-      <c r="G20" s="187">
+      <c r="G20" s="188">
         <f t="shared" si="1"/>
         <v>396360</v>
       </c>
-      <c r="H20" s="188"/>
-      <c r="I20" s="107"/>
-      <c r="J20" s="164"/>
-      <c r="K20" s="107"/>
-      <c r="L20" s="107"/>
-      <c r="M20" s="196"/>
-      <c r="N20" s="196"/>
-      <c r="O20" s="196"/>
-      <c r="P20" s="196"/>
-      <c r="Q20" s="196"/>
-      <c r="R20" s="196"/>
-      <c r="S20" s="196"/>
-      <c r="T20" s="196"/>
-      <c r="U20" s="196"/>
+      <c r="H20" s="190"/>
+      <c r="I20" s="199"/>
+      <c r="J20" s="200"/>
+      <c r="K20" s="199"/>
+      <c r="L20" s="199"/>
+      <c r="M20" s="198"/>
+      <c r="N20" s="198"/>
+      <c r="O20" s="198"/>
+      <c r="P20" s="198"/>
+      <c r="Q20" s="198"/>
+      <c r="R20" s="198"/>
+      <c r="S20" s="198"/>
+      <c r="T20" s="198"/>
+      <c r="U20" s="198"/>
     </row>
     <row r="21" ht="31.9" customHeight="1" spans="1:21">
       <c r="A21" s="182">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="B21" s="147" t="s">
+      <c r="B21" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="183" t="s">
+      <c r="C21" s="184" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="184" t="s">
+      <c r="D21" s="185" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="185">
+      <c r="E21" s="186">
         <v>520000</v>
       </c>
-      <c r="F21" s="186">
+      <c r="F21" s="187">
         <f t="shared" si="5"/>
         <v>41600</v>
       </c>
-      <c r="G21" s="187">
+      <c r="G21" s="188">
         <f t="shared" si="1"/>
         <v>561600</v>
       </c>
-      <c r="H21" s="188"/>
-      <c r="I21" s="107"/>
-      <c r="J21" s="164"/>
-      <c r="K21" s="107"/>
-      <c r="L21" s="107"/>
-      <c r="M21" s="196"/>
-      <c r="N21" s="196"/>
-      <c r="O21" s="196"/>
-      <c r="P21" s="196"/>
-      <c r="Q21" s="196"/>
-      <c r="R21" s="196"/>
-      <c r="S21" s="196"/>
-      <c r="T21" s="196"/>
-      <c r="U21" s="196"/>
+      <c r="H21" s="190"/>
+      <c r="I21" s="199"/>
+      <c r="J21" s="200"/>
+      <c r="K21" s="199"/>
+      <c r="L21" s="199"/>
+      <c r="M21" s="198"/>
+      <c r="N21" s="198"/>
+      <c r="O21" s="198"/>
+      <c r="P21" s="198"/>
+      <c r="Q21" s="198"/>
+      <c r="R21" s="198"/>
+      <c r="S21" s="198"/>
+      <c r="T21" s="198"/>
+      <c r="U21" s="198"/>
     </row>
     <row r="22" ht="38.25" customHeight="1" spans="1:21">
       <c r="A22" s="182">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="B22" s="147" t="s">
+      <c r="B22" s="183" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="183" t="s">
+      <c r="C22" s="184" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="184" t="s">
+      <c r="D22" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="185">
+      <c r="E22" s="186">
         <v>560000</v>
       </c>
-      <c r="F22" s="186">
+      <c r="F22" s="187">
         <f t="shared" si="5"/>
         <v>44800</v>
       </c>
-      <c r="G22" s="187">
+      <c r="G22" s="188">
         <f t="shared" si="1"/>
         <v>604800</v>
       </c>
-      <c r="H22" s="188"/>
-      <c r="I22" s="107"/>
-      <c r="J22" s="164"/>
-      <c r="K22" s="107"/>
-      <c r="L22" s="107"/>
-      <c r="M22" s="196"/>
-      <c r="N22" s="196"/>
-      <c r="O22" s="196"/>
-      <c r="P22" s="196"/>
-      <c r="Q22" s="196"/>
-      <c r="R22" s="196"/>
-      <c r="S22" s="196"/>
-      <c r="T22" s="196"/>
-      <c r="U22" s="196"/>
+      <c r="H22" s="190"/>
+      <c r="I22" s="199"/>
+      <c r="J22" s="200"/>
+      <c r="K22" s="199"/>
+      <c r="L22" s="199"/>
+      <c r="M22" s="198"/>
+      <c r="N22" s="198"/>
+      <c r="O22" s="198"/>
+      <c r="P22" s="198"/>
+      <c r="Q22" s="198"/>
+      <c r="R22" s="198"/>
+      <c r="S22" s="198"/>
+      <c r="T22" s="198"/>
+      <c r="U22" s="198"/>
     </row>
     <row r="23" ht="38.25" customHeight="1" spans="1:21">
       <c r="A23" s="182">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="B23" s="147" t="s">
+      <c r="B23" s="183" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="183" t="s">
+      <c r="C23" s="184" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="184" t="s">
+      <c r="D23" s="185" t="s">
         <v>56</v>
       </c>
-      <c r="E23" s="185">
+      <c r="E23" s="186">
         <f>390000/1.1</f>
         <v>354545.454545455</v>
       </c>
-      <c r="F23" s="186">
+      <c r="F23" s="187">
         <f t="shared" si="5"/>
         <v>28363.6363636364</v>
       </c>
-      <c r="G23" s="187">
+      <c r="G23" s="188">
         <f t="shared" si="1"/>
         <v>382909.090909091</v>
       </c>
-      <c r="H23" s="188"/>
-      <c r="I23" s="107"/>
-      <c r="J23" s="164"/>
-      <c r="K23" s="107"/>
-      <c r="L23" s="107"/>
-      <c r="M23" s="196"/>
-      <c r="N23" s="196"/>
-      <c r="O23" s="196"/>
-      <c r="P23" s="196"/>
-      <c r="Q23" s="196"/>
-      <c r="R23" s="196"/>
-      <c r="S23" s="196"/>
-      <c r="T23" s="196"/>
-      <c r="U23" s="196"/>
+      <c r="H23" s="190"/>
+      <c r="I23" s="199"/>
+      <c r="J23" s="200"/>
+      <c r="K23" s="199"/>
+      <c r="L23" s="199"/>
+      <c r="M23" s="198"/>
+      <c r="N23" s="198"/>
+      <c r="O23" s="198"/>
+      <c r="P23" s="198"/>
+      <c r="Q23" s="198"/>
+      <c r="R23" s="198"/>
+      <c r="S23" s="198"/>
+      <c r="T23" s="198"/>
+      <c r="U23" s="198"/>
     </row>
     <row r="24" ht="33.65" customHeight="1" spans="1:21">
       <c r="A24" s="182">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="B24" s="147" t="s">
+      <c r="B24" s="183" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="183" t="s">
+      <c r="C24" s="184" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="184" t="s">
+      <c r="D24" s="185" t="s">
         <v>48</v>
       </c>
-      <c r="E24" s="185">
+      <c r="E24" s="186">
         <v>367000</v>
       </c>
-      <c r="F24" s="186">
+      <c r="F24" s="187">
         <f t="shared" si="5"/>
         <v>29360</v>
       </c>
-      <c r="G24" s="187">
+      <c r="G24" s="188">
         <f t="shared" si="1"/>
         <v>396360</v>
       </c>
-      <c r="H24" s="188"/>
-      <c r="I24" s="107"/>
-      <c r="J24" s="164"/>
-      <c r="K24" s="107"/>
-      <c r="L24" s="107"/>
-      <c r="M24" s="196"/>
-      <c r="N24" s="196"/>
-      <c r="O24" s="196"/>
-      <c r="P24" s="196"/>
-      <c r="Q24" s="196"/>
-      <c r="R24" s="196"/>
-      <c r="S24" s="196"/>
-      <c r="T24" s="196"/>
-      <c r="U24" s="196"/>
+      <c r="H24" s="190"/>
+      <c r="I24" s="199"/>
+      <c r="J24" s="200"/>
+      <c r="K24" s="199"/>
+      <c r="L24" s="199"/>
+      <c r="M24" s="198"/>
+      <c r="N24" s="198"/>
+      <c r="O24" s="198"/>
+      <c r="P24" s="198"/>
+      <c r="Q24" s="198"/>
+      <c r="R24" s="198"/>
+      <c r="S24" s="198"/>
+      <c r="T24" s="198"/>
+      <c r="U24" s="198"/>
     </row>
     <row r="25" ht="43.2" customHeight="1" spans="1:21">
       <c r="A25" s="182">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="B25" s="147" t="s">
+      <c r="B25" s="183" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="183" t="s">
+      <c r="C25" s="184" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="184" t="s">
+      <c r="D25" s="185" t="s">
         <v>51</v>
       </c>
-      <c r="E25" s="185">
+      <c r="E25" s="186">
         <v>520000</v>
       </c>
-      <c r="F25" s="186">
+      <c r="F25" s="187">
         <f t="shared" si="5"/>
         <v>41600</v>
       </c>
-      <c r="G25" s="187">
+      <c r="G25" s="188">
         <f t="shared" si="1"/>
         <v>561600</v>
       </c>
-      <c r="H25" s="188"/>
-      <c r="I25" s="107"/>
-      <c r="J25" s="164"/>
-      <c r="K25" s="107"/>
-      <c r="L25" s="107"/>
-      <c r="M25" s="196"/>
-      <c r="N25" s="196"/>
-      <c r="O25" s="196"/>
-      <c r="P25" s="196"/>
-      <c r="Q25" s="196"/>
-      <c r="R25" s="196"/>
-      <c r="S25" s="196"/>
-      <c r="T25" s="196"/>
-      <c r="U25" s="196"/>
+      <c r="H25" s="190"/>
+      <c r="I25" s="199"/>
+      <c r="J25" s="200"/>
+      <c r="K25" s="199"/>
+      <c r="L25" s="199"/>
+      <c r="M25" s="198"/>
+      <c r="N25" s="198"/>
+      <c r="O25" s="198"/>
+      <c r="P25" s="198"/>
+      <c r="Q25" s="198"/>
+      <c r="R25" s="198"/>
+      <c r="S25" s="198"/>
+      <c r="T25" s="198"/>
+      <c r="U25" s="198"/>
     </row>
     <row r="26" ht="33.65" customHeight="1" spans="1:21">
       <c r="A26" s="182">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="B26" s="147" t="s">
+      <c r="B26" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="183" t="s">
+      <c r="C26" s="184" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="184" t="s">
+      <c r="D26" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E26" s="185">
+      <c r="E26" s="186">
         <v>560000</v>
       </c>
-      <c r="F26" s="186">
+      <c r="F26" s="187">
         <f t="shared" si="5"/>
         <v>44800</v>
       </c>
-      <c r="G26" s="187">
+      <c r="G26" s="188">
         <f t="shared" si="1"/>
         <v>604800</v>
       </c>
-      <c r="H26" s="188"/>
-      <c r="I26" s="107"/>
-      <c r="J26" s="164"/>
-      <c r="K26" s="107"/>
-      <c r="L26" s="107"/>
-      <c r="M26" s="196"/>
-      <c r="N26" s="196"/>
-      <c r="O26" s="196"/>
-      <c r="P26" s="196"/>
-      <c r="Q26" s="196"/>
-      <c r="R26" s="196"/>
-      <c r="S26" s="196"/>
-      <c r="T26" s="196"/>
-      <c r="U26" s="196"/>
+      <c r="H26" s="190"/>
+      <c r="I26" s="199"/>
+      <c r="J26" s="200"/>
+      <c r="K26" s="199"/>
+      <c r="L26" s="199"/>
+      <c r="M26" s="198"/>
+      <c r="N26" s="198"/>
+      <c r="O26" s="198"/>
+      <c r="P26" s="198"/>
+      <c r="Q26" s="198"/>
+      <c r="R26" s="198"/>
+      <c r="S26" s="198"/>
+      <c r="T26" s="198"/>
+      <c r="U26" s="198"/>
     </row>
     <row r="27" ht="33.65" customHeight="1" spans="1:21">
       <c r="A27" s="182">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="B27" s="147" t="s">
+      <c r="B27" s="183" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="183" t="s">
+      <c r="C27" s="184" t="s">
         <v>64</v>
       </c>
-      <c r="D27" s="184" t="s">
+      <c r="D27" s="185" t="s">
         <v>51</v>
       </c>
-      <c r="E27" s="185">
+      <c r="E27" s="186">
         <v>520000</v>
       </c>
-      <c r="F27" s="186">
+      <c r="F27" s="187">
         <f t="shared" si="5"/>
         <v>41600</v>
       </c>
-      <c r="G27" s="187">
+      <c r="G27" s="188">
         <f t="shared" si="1"/>
         <v>561600</v>
       </c>
-      <c r="H27" s="188"/>
-      <c r="I27" s="107"/>
-      <c r="J27" s="164"/>
-      <c r="K27" s="107"/>
-      <c r="L27" s="107"/>
-      <c r="M27" s="196"/>
-      <c r="N27" s="196"/>
-      <c r="O27" s="196"/>
-      <c r="P27" s="196"/>
-      <c r="Q27" s="196"/>
-      <c r="R27" s="196"/>
-      <c r="S27" s="196"/>
-      <c r="T27" s="196"/>
-      <c r="U27" s="196"/>
+      <c r="H27" s="190"/>
+      <c r="I27" s="199"/>
+      <c r="J27" s="200"/>
+      <c r="K27" s="199"/>
+      <c r="L27" s="199"/>
+      <c r="M27" s="198"/>
+      <c r="N27" s="198"/>
+      <c r="O27" s="198"/>
+      <c r="P27" s="198"/>
+      <c r="Q27" s="198"/>
+      <c r="R27" s="198"/>
+      <c r="S27" s="198"/>
+      <c r="T27" s="198"/>
+      <c r="U27" s="198"/>
     </row>
     <row r="28" ht="33.65" customHeight="1" spans="1:21">
       <c r="A28" s="182">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="B28" s="147" t="s">
+      <c r="B28" s="183" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="183" t="s">
+      <c r="C28" s="184" t="s">
         <v>66</v>
       </c>
-      <c r="D28" s="184" t="s">
+      <c r="D28" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E28" s="185">
+      <c r="E28" s="186">
         <v>560000</v>
       </c>
-      <c r="F28" s="186">
+      <c r="F28" s="187">
         <f t="shared" si="5"/>
         <v>44800</v>
       </c>
-      <c r="G28" s="187">
+      <c r="G28" s="188">
         <f t="shared" si="1"/>
         <v>604800</v>
       </c>
-      <c r="H28" s="188"/>
-      <c r="I28" s="107"/>
-      <c r="J28" s="164"/>
-      <c r="K28" s="107"/>
-      <c r="L28" s="107"/>
-      <c r="M28" s="196"/>
-      <c r="N28" s="196"/>
-      <c r="O28" s="196"/>
-      <c r="P28" s="196"/>
-      <c r="Q28" s="196"/>
-      <c r="R28" s="196"/>
-      <c r="S28" s="196"/>
-      <c r="T28" s="196"/>
-      <c r="U28" s="196"/>
+      <c r="H28" s="190"/>
+      <c r="I28" s="199"/>
+      <c r="J28" s="200"/>
+      <c r="K28" s="199"/>
+      <c r="L28" s="199"/>
+      <c r="M28" s="198"/>
+      <c r="N28" s="198"/>
+      <c r="O28" s="198"/>
+      <c r="P28" s="198"/>
+      <c r="Q28" s="198"/>
+      <c r="R28" s="198"/>
+      <c r="S28" s="198"/>
+      <c r="T28" s="198"/>
+      <c r="U28" s="198"/>
     </row>
     <row r="29" ht="33.65" customHeight="1" spans="1:21">
       <c r="A29" s="182">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="B29" s="147" t="s">
+      <c r="B29" s="183" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="183" t="s">
+      <c r="C29" s="184" t="s">
         <v>68</v>
       </c>
-      <c r="D29" s="184" t="s">
+      <c r="D29" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E29" s="185">
+      <c r="E29" s="186">
         <v>560000</v>
       </c>
-      <c r="F29" s="186">
+      <c r="F29" s="187">
         <f t="shared" si="5"/>
         <v>44800</v>
       </c>
-      <c r="G29" s="187">
+      <c r="G29" s="188">
         <f t="shared" si="1"/>
         <v>604800</v>
       </c>
-      <c r="H29" s="188"/>
-      <c r="I29" s="107"/>
-      <c r="J29" s="164"/>
-      <c r="K29" s="107"/>
-      <c r="L29" s="107"/>
-      <c r="M29" s="196"/>
-      <c r="N29" s="196"/>
-      <c r="O29" s="196"/>
-      <c r="P29" s="196"/>
-      <c r="Q29" s="196"/>
-      <c r="R29" s="196"/>
-      <c r="S29" s="196"/>
-      <c r="T29" s="196"/>
-      <c r="U29" s="196"/>
+      <c r="H29" s="190"/>
+      <c r="I29" s="199"/>
+      <c r="J29" s="200"/>
+      <c r="K29" s="199"/>
+      <c r="L29" s="199"/>
+      <c r="M29" s="198"/>
+      <c r="N29" s="198"/>
+      <c r="O29" s="198"/>
+      <c r="P29" s="198"/>
+      <c r="Q29" s="198"/>
+      <c r="R29" s="198"/>
+      <c r="S29" s="198"/>
+      <c r="T29" s="198"/>
+      <c r="U29" s="198"/>
     </row>
     <row r="30" ht="33.65" customHeight="1" spans="1:21">
       <c r="A30" s="182">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="B30" s="147" t="s">
+      <c r="B30" s="183" t="s">
         <v>69</v>
       </c>
-      <c r="C30" s="183" t="s">
+      <c r="C30" s="184" t="s">
         <v>70</v>
       </c>
-      <c r="D30" s="184" t="s">
+      <c r="D30" s="185" t="s">
         <v>71</v>
       </c>
-      <c r="E30" s="189">
+      <c r="E30" s="191">
         <v>232000</v>
       </c>
-      <c r="F30" s="186">
+      <c r="F30" s="187">
         <f t="shared" si="5"/>
         <v>18560</v>
       </c>
-      <c r="G30" s="187">
+      <c r="G30" s="188">
         <f t="shared" si="1"/>
         <v>250560</v>
       </c>
-      <c r="H30" s="188"/>
-      <c r="I30" s="107"/>
-      <c r="J30" s="164"/>
-      <c r="K30" s="107"/>
-      <c r="L30" s="107"/>
-      <c r="M30" s="196"/>
-      <c r="N30" s="196"/>
-      <c r="O30" s="196"/>
-      <c r="P30" s="196"/>
-      <c r="Q30" s="196"/>
-      <c r="R30" s="196"/>
-      <c r="S30" s="196"/>
-      <c r="T30" s="196"/>
-      <c r="U30" s="196"/>
+      <c r="H30" s="190"/>
+      <c r="I30" s="199"/>
+      <c r="J30" s="200"/>
+      <c r="K30" s="199"/>
+      <c r="L30" s="199"/>
+      <c r="M30" s="198"/>
+      <c r="N30" s="198"/>
+      <c r="O30" s="198"/>
+      <c r="P30" s="198"/>
+      <c r="Q30" s="198"/>
+      <c r="R30" s="198"/>
+      <c r="S30" s="198"/>
+      <c r="T30" s="198"/>
+      <c r="U30" s="198"/>
     </row>
     <row r="31" ht="33.65" customHeight="1" spans="1:21">
       <c r="A31" s="182">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="B31" s="147" t="s">
+      <c r="B31" s="183" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="183" t="s">
+      <c r="C31" s="184" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="184" t="s">
+      <c r="D31" s="185" t="s">
         <v>71</v>
       </c>
-      <c r="E31" s="189">
+      <c r="E31" s="191">
         <v>232000</v>
       </c>
-      <c r="F31" s="186">
+      <c r="F31" s="187">
         <f t="shared" si="5"/>
         <v>18560</v>
       </c>
-      <c r="G31" s="187">
+      <c r="G31" s="188">
         <f t="shared" si="1"/>
         <v>250560</v>
       </c>
-      <c r="H31" s="188"/>
-      <c r="I31" s="107"/>
-      <c r="J31" s="164"/>
-      <c r="K31" s="107"/>
-      <c r="L31" s="107"/>
-      <c r="M31" s="196"/>
-      <c r="N31" s="196"/>
-      <c r="O31" s="196"/>
-      <c r="P31" s="196"/>
-      <c r="Q31" s="196"/>
-      <c r="R31" s="196"/>
-      <c r="S31" s="196"/>
-      <c r="T31" s="196"/>
-      <c r="U31" s="196"/>
+      <c r="H31" s="190"/>
+      <c r="I31" s="199"/>
+      <c r="J31" s="200"/>
+      <c r="K31" s="199"/>
+      <c r="L31" s="199"/>
+      <c r="M31" s="198"/>
+      <c r="N31" s="198"/>
+      <c r="O31" s="198"/>
+      <c r="P31" s="198"/>
+      <c r="Q31" s="198"/>
+      <c r="R31" s="198"/>
+      <c r="S31" s="198"/>
+      <c r="T31" s="198"/>
+      <c r="U31" s="198"/>
     </row>
     <row r="32" ht="33.65" customHeight="1" spans="1:21">
       <c r="A32" s="182">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="B32" s="147" t="s">
+      <c r="B32" s="183" t="s">
         <v>74</v>
       </c>
-      <c r="C32" s="183" t="s">
+      <c r="C32" s="184" t="s">
         <v>75</v>
       </c>
-      <c r="D32" s="184" t="s">
+      <c r="D32" s="185" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="185">
+      <c r="E32" s="186">
         <v>367000</v>
       </c>
-      <c r="F32" s="186">
+      <c r="F32" s="187">
         <f t="shared" si="5"/>
         <v>29360</v>
       </c>
-      <c r="G32" s="187">
+      <c r="G32" s="188">
         <f t="shared" si="1"/>
         <v>396360</v>
       </c>
-      <c r="H32" s="188"/>
-      <c r="I32" s="107"/>
-      <c r="J32" s="164"/>
-      <c r="K32" s="107"/>
-      <c r="L32" s="107"/>
-      <c r="M32" s="196"/>
-      <c r="N32" s="196"/>
-      <c r="O32" s="196"/>
-      <c r="P32" s="196"/>
-      <c r="Q32" s="196"/>
-      <c r="R32" s="196"/>
-      <c r="S32" s="196"/>
-      <c r="T32" s="196"/>
-      <c r="U32" s="196"/>
+      <c r="H32" s="190"/>
+      <c r="I32" s="199"/>
+      <c r="J32" s="200"/>
+      <c r="K32" s="199"/>
+      <c r="L32" s="199"/>
+      <c r="M32" s="198"/>
+      <c r="N32" s="198"/>
+      <c r="O32" s="198"/>
+      <c r="P32" s="198"/>
+      <c r="Q32" s="198"/>
+      <c r="R32" s="198"/>
+      <c r="S32" s="198"/>
+      <c r="T32" s="198"/>
+      <c r="U32" s="198"/>
     </row>
     <row r="33" ht="33.65" customHeight="1" spans="1:21">
       <c r="A33" s="182">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="B33" s="147" t="s">
+      <c r="B33" s="183" t="s">
         <v>76</v>
       </c>
-      <c r="C33" s="183" t="s">
+      <c r="C33" s="184" t="s">
         <v>77</v>
       </c>
-      <c r="D33" s="184" t="s">
+      <c r="D33" s="185" t="s">
         <v>56</v>
       </c>
-      <c r="E33" s="185">
+      <c r="E33" s="186">
         <f>390000/1.1</f>
         <v>354545.454545455</v>
       </c>
-      <c r="F33" s="186">
+      <c r="F33" s="187">
         <f t="shared" si="5"/>
         <v>28363.6363636364</v>
       </c>
-      <c r="G33" s="187">
+      <c r="G33" s="188">
         <f t="shared" si="1"/>
         <v>382909.090909091</v>
       </c>
-      <c r="H33" s="188"/>
-      <c r="I33" s="107"/>
-      <c r="J33" s="164"/>
-      <c r="K33" s="107"/>
-      <c r="L33" s="107"/>
-      <c r="M33" s="196"/>
-      <c r="N33" s="196"/>
-      <c r="O33" s="196"/>
-      <c r="P33" s="196"/>
-      <c r="Q33" s="196"/>
-      <c r="R33" s="196"/>
-      <c r="S33" s="196"/>
-      <c r="T33" s="196"/>
-      <c r="U33" s="196"/>
+      <c r="H33" s="190"/>
+      <c r="I33" s="199"/>
+      <c r="J33" s="200"/>
+      <c r="K33" s="199"/>
+      <c r="L33" s="199"/>
+      <c r="M33" s="198"/>
+      <c r="N33" s="198"/>
+      <c r="O33" s="198"/>
+      <c r="P33" s="198"/>
+      <c r="Q33" s="198"/>
+      <c r="R33" s="198"/>
+      <c r="S33" s="198"/>
+      <c r="T33" s="198"/>
+      <c r="U33" s="198"/>
     </row>
     <row r="34" ht="33.65" customHeight="1" spans="1:21">
       <c r="A34" s="182">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="B34" s="147" t="s">
+      <c r="B34" s="183" t="s">
         <v>78</v>
       </c>
-      <c r="C34" s="183" t="s">
+      <c r="C34" s="184" t="s">
         <v>79</v>
       </c>
-      <c r="D34" s="184" t="s">
+      <c r="D34" s="185" t="s">
         <v>80</v>
       </c>
-      <c r="E34" s="185">
+      <c r="E34" s="186">
         <v>535000</v>
       </c>
-      <c r="F34" s="186">
+      <c r="F34" s="187">
         <f t="shared" si="5"/>
         <v>42800</v>
       </c>
-      <c r="G34" s="187">
+      <c r="G34" s="188">
         <f t="shared" si="1"/>
         <v>577800</v>
       </c>
-      <c r="H34" s="188"/>
-      <c r="I34" s="107"/>
-      <c r="J34" s="164"/>
-      <c r="K34" s="107"/>
-      <c r="L34" s="107"/>
-      <c r="M34" s="196"/>
-      <c r="N34" s="196"/>
-      <c r="O34" s="196"/>
-      <c r="P34" s="196"/>
-      <c r="Q34" s="196"/>
-      <c r="R34" s="196"/>
-      <c r="S34" s="196"/>
-      <c r="T34" s="196"/>
-      <c r="U34" s="196"/>
+      <c r="H34" s="190"/>
+      <c r="I34" s="199"/>
+      <c r="J34" s="200"/>
+      <c r="K34" s="199"/>
+      <c r="L34" s="199"/>
+      <c r="M34" s="198"/>
+      <c r="N34" s="198"/>
+      <c r="O34" s="198"/>
+      <c r="P34" s="198"/>
+      <c r="Q34" s="198"/>
+      <c r="R34" s="198"/>
+      <c r="S34" s="198"/>
+      <c r="T34" s="198"/>
+      <c r="U34" s="198"/>
     </row>
     <row r="35" ht="33.65" customHeight="1" spans="1:21">
       <c r="A35" s="182">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="B35" s="147" t="s">
+      <c r="B35" s="183" t="s">
         <v>81</v>
       </c>
-      <c r="C35" s="183" t="s">
+      <c r="C35" s="184" t="s">
         <v>82</v>
       </c>
-      <c r="D35" s="184" t="s">
+      <c r="D35" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E35" s="185">
+      <c r="E35" s="186">
         <v>560000</v>
       </c>
-      <c r="F35" s="186">
+      <c r="F35" s="187">
         <f t="shared" si="5"/>
         <v>44800</v>
       </c>
-      <c r="G35" s="187">
+      <c r="G35" s="188">
         <f t="shared" si="1"/>
         <v>604800</v>
       </c>
-      <c r="H35" s="188"/>
-      <c r="I35" s="107"/>
-      <c r="J35" s="164"/>
-      <c r="K35" s="107"/>
-      <c r="L35" s="107"/>
-      <c r="M35" s="196"/>
-      <c r="N35" s="196"/>
-      <c r="O35" s="196"/>
-      <c r="P35" s="196"/>
-      <c r="Q35" s="196"/>
-      <c r="R35" s="196"/>
-      <c r="S35" s="196"/>
-      <c r="T35" s="196"/>
-      <c r="U35" s="196"/>
+      <c r="H35" s="190"/>
+      <c r="I35" s="199"/>
+      <c r="J35" s="200"/>
+      <c r="K35" s="199"/>
+      <c r="L35" s="199"/>
+      <c r="M35" s="198"/>
+      <c r="N35" s="198"/>
+      <c r="O35" s="198"/>
+      <c r="P35" s="198"/>
+      <c r="Q35" s="198"/>
+      <c r="R35" s="198"/>
+      <c r="S35" s="198"/>
+      <c r="T35" s="198"/>
+      <c r="U35" s="198"/>
     </row>
     <row r="36" ht="33.65" customHeight="1" spans="1:21">
       <c r="A36" s="182">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="B36" s="147" t="s">
+      <c r="B36" s="183" t="s">
         <v>83</v>
       </c>
-      <c r="C36" s="183" t="s">
+      <c r="C36" s="184" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="184" t="s">
+      <c r="D36" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E36" s="185">
+      <c r="E36" s="186">
         <v>560000</v>
       </c>
-      <c r="F36" s="186">
+      <c r="F36" s="187">
         <f t="shared" si="5"/>
         <v>44800</v>
       </c>
-      <c r="G36" s="187">
+      <c r="G36" s="188">
         <f t="shared" si="1"/>
         <v>604800</v>
       </c>
-      <c r="H36" s="188"/>
-      <c r="I36" s="107"/>
-      <c r="J36" s="164"/>
-      <c r="K36" s="107"/>
-      <c r="L36" s="107"/>
-      <c r="M36" s="196"/>
-      <c r="N36" s="196"/>
-      <c r="O36" s="196"/>
-      <c r="P36" s="196"/>
-      <c r="Q36" s="196"/>
-      <c r="R36" s="196"/>
-      <c r="S36" s="196"/>
-      <c r="T36" s="196"/>
-      <c r="U36" s="196"/>
+      <c r="H36" s="190"/>
+      <c r="I36" s="199"/>
+      <c r="J36" s="200"/>
+      <c r="K36" s="199"/>
+      <c r="L36" s="199"/>
+      <c r="M36" s="198"/>
+      <c r="N36" s="198"/>
+      <c r="O36" s="198"/>
+      <c r="P36" s="198"/>
+      <c r="Q36" s="198"/>
+      <c r="R36" s="198"/>
+      <c r="S36" s="198"/>
+      <c r="T36" s="198"/>
+      <c r="U36" s="198"/>
     </row>
     <row r="37" ht="33.65" customHeight="1" spans="1:21">
       <c r="A37" s="182">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="B37" s="147" t="s">
+      <c r="B37" s="183" t="s">
         <v>85</v>
       </c>
-      <c r="C37" s="183" t="s">
+      <c r="C37" s="184" t="s">
         <v>86</v>
       </c>
-      <c r="D37" s="184" t="s">
+      <c r="D37" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E37" s="185">
+      <c r="E37" s="186">
         <v>560000</v>
       </c>
-      <c r="F37" s="186">
+      <c r="F37" s="187">
         <f t="shared" si="5"/>
         <v>44800</v>
       </c>
-      <c r="G37" s="187">
+      <c r="G37" s="188">
         <f t="shared" si="1"/>
         <v>604800</v>
       </c>
-      <c r="H37" s="188"/>
-      <c r="I37" s="107"/>
-      <c r="J37" s="164"/>
-      <c r="K37" s="107"/>
-      <c r="L37" s="107"/>
-      <c r="M37" s="196"/>
-      <c r="N37" s="196"/>
-      <c r="O37" s="196"/>
-      <c r="P37" s="196"/>
-      <c r="Q37" s="196"/>
-      <c r="R37" s="196"/>
-      <c r="S37" s="196"/>
-      <c r="T37" s="196"/>
-      <c r="U37" s="196"/>
+      <c r="H37" s="190"/>
+      <c r="I37" s="199"/>
+      <c r="J37" s="200"/>
+      <c r="K37" s="199"/>
+      <c r="L37" s="199"/>
+      <c r="M37" s="198"/>
+      <c r="N37" s="198"/>
+      <c r="O37" s="198"/>
+      <c r="P37" s="198"/>
+      <c r="Q37" s="198"/>
+      <c r="R37" s="198"/>
+      <c r="S37" s="198"/>
+      <c r="T37" s="198"/>
+      <c r="U37" s="198"/>
     </row>
     <row r="38" ht="33.65" customHeight="1" spans="1:21">
       <c r="A38" s="182">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="B38" s="147" t="s">
+      <c r="B38" s="183" t="s">
         <v>87</v>
       </c>
-      <c r="C38" s="183" t="s">
+      <c r="C38" s="184" t="s">
         <v>88</v>
       </c>
-      <c r="D38" s="184" t="s">
+      <c r="D38" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E38" s="185">
+      <c r="E38" s="186">
         <v>560000</v>
       </c>
-      <c r="F38" s="186">
+      <c r="F38" s="187">
         <f t="shared" si="5"/>
         <v>44800</v>
       </c>
-      <c r="G38" s="187">
+      <c r="G38" s="188">
         <f t="shared" si="1"/>
         <v>604800</v>
       </c>
-      <c r="H38" s="188"/>
-      <c r="I38" s="107"/>
-      <c r="J38" s="164"/>
-      <c r="K38" s="107"/>
-      <c r="L38" s="107"/>
-      <c r="M38" s="196"/>
-      <c r="N38" s="196"/>
-      <c r="O38" s="196"/>
-      <c r="P38" s="196"/>
-      <c r="Q38" s="196"/>
-      <c r="R38" s="196"/>
-      <c r="S38" s="196"/>
-      <c r="T38" s="196"/>
-      <c r="U38" s="196"/>
+      <c r="H38" s="190"/>
+      <c r="I38" s="199"/>
+      <c r="J38" s="200"/>
+      <c r="K38" s="199"/>
+      <c r="L38" s="199"/>
+      <c r="M38" s="198"/>
+      <c r="N38" s="198"/>
+      <c r="O38" s="198"/>
+      <c r="P38" s="198"/>
+      <c r="Q38" s="198"/>
+      <c r="R38" s="198"/>
+      <c r="S38" s="198"/>
+      <c r="T38" s="198"/>
+      <c r="U38" s="198"/>
     </row>
     <row r="39" ht="33.65" customHeight="1" spans="1:21">
       <c r="A39" s="182">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="B39" s="147" t="s">
+      <c r="B39" s="183" t="s">
         <v>89</v>
       </c>
-      <c r="C39" s="183" t="s">
+      <c r="C39" s="184" t="s">
         <v>90</v>
       </c>
-      <c r="D39" s="184" t="s">
+      <c r="D39" s="185" t="s">
         <v>51</v>
       </c>
-      <c r="E39" s="185">
+      <c r="E39" s="186">
         <v>520000</v>
       </c>
-      <c r="F39" s="186">
+      <c r="F39" s="187">
         <f t="shared" si="5"/>
         <v>41600</v>
       </c>
-      <c r="G39" s="187">
+      <c r="G39" s="188">
         <f t="shared" si="1"/>
         <v>561600</v>
       </c>
-      <c r="H39" s="188"/>
-      <c r="I39" s="107"/>
-      <c r="J39" s="164"/>
-      <c r="K39" s="107"/>
-      <c r="L39" s="107"/>
-      <c r="M39" s="196"/>
-      <c r="N39" s="196"/>
-      <c r="O39" s="196"/>
-      <c r="P39" s="196"/>
-      <c r="Q39" s="196"/>
-      <c r="R39" s="196"/>
-      <c r="S39" s="196"/>
-      <c r="T39" s="196"/>
-      <c r="U39" s="196"/>
+      <c r="H39" s="190"/>
+      <c r="I39" s="199"/>
+      <c r="J39" s="200"/>
+      <c r="K39" s="199"/>
+      <c r="L39" s="199"/>
+      <c r="M39" s="198"/>
+      <c r="N39" s="198"/>
+      <c r="O39" s="198"/>
+      <c r="P39" s="198"/>
+      <c r="Q39" s="198"/>
+      <c r="R39" s="198"/>
+      <c r="S39" s="198"/>
+      <c r="T39" s="198"/>
+      <c r="U39" s="198"/>
     </row>
     <row r="40" ht="33.65" customHeight="1" spans="1:21">
       <c r="A40" s="182">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="B40" s="147" t="s">
+      <c r="B40" s="183" t="s">
         <v>91</v>
       </c>
-      <c r="C40" s="183" t="s">
+      <c r="C40" s="184" t="s">
         <v>92</v>
       </c>
-      <c r="D40" s="184" t="s">
+      <c r="D40" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E40" s="185">
+      <c r="E40" s="186">
         <v>560000</v>
       </c>
-      <c r="F40" s="186">
+      <c r="F40" s="187">
         <f t="shared" si="5"/>
         <v>44800</v>
       </c>
-      <c r="G40" s="187">
+      <c r="G40" s="188">
         <f t="shared" si="1"/>
         <v>604800</v>
       </c>
-      <c r="H40" s="188"/>
-      <c r="I40" s="107"/>
-      <c r="J40" s="164"/>
-      <c r="K40" s="107"/>
-      <c r="L40" s="107"/>
-      <c r="M40" s="196"/>
-      <c r="N40" s="196"/>
-      <c r="O40" s="196"/>
-      <c r="P40" s="196"/>
-      <c r="Q40" s="196"/>
-      <c r="R40" s="196"/>
-      <c r="S40" s="196"/>
-      <c r="T40" s="196"/>
-      <c r="U40" s="196"/>
+      <c r="H40" s="190"/>
+      <c r="I40" s="199"/>
+      <c r="J40" s="200"/>
+      <c r="K40" s="199"/>
+      <c r="L40" s="199"/>
+      <c r="M40" s="198"/>
+      <c r="N40" s="198"/>
+      <c r="O40" s="198"/>
+      <c r="P40" s="198"/>
+      <c r="Q40" s="198"/>
+      <c r="R40" s="198"/>
+      <c r="S40" s="198"/>
+      <c r="T40" s="198"/>
+      <c r="U40" s="198"/>
     </row>
     <row r="41" ht="33.65" customHeight="1" spans="1:21">
       <c r="A41" s="182">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="B41" s="147" t="s">
+      <c r="B41" s="183" t="s">
         <v>93</v>
       </c>
-      <c r="C41" s="183" t="s">
+      <c r="C41" s="184" t="s">
         <v>94</v>
       </c>
-      <c r="D41" s="184" t="s">
+      <c r="D41" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E41" s="185">
+      <c r="E41" s="186">
         <v>560000</v>
       </c>
-      <c r="F41" s="186">
+      <c r="F41" s="187">
         <f t="shared" si="5"/>
         <v>44800</v>
       </c>
-      <c r="G41" s="187">
+      <c r="G41" s="188">
         <f t="shared" si="1"/>
         <v>604800</v>
       </c>
-      <c r="H41" s="188"/>
-      <c r="I41" s="107"/>
-      <c r="J41" s="164"/>
-      <c r="K41" s="107"/>
-      <c r="L41" s="107"/>
-      <c r="M41" s="196"/>
-      <c r="N41" s="196"/>
-      <c r="O41" s="196"/>
-      <c r="P41" s="196"/>
-      <c r="Q41" s="196"/>
-      <c r="R41" s="196"/>
-      <c r="S41" s="196"/>
-      <c r="T41" s="196"/>
-      <c r="U41" s="196"/>
+      <c r="H41" s="190"/>
+      <c r="I41" s="199"/>
+      <c r="J41" s="200"/>
+      <c r="K41" s="199"/>
+      <c r="L41" s="199"/>
+      <c r="M41" s="198"/>
+      <c r="N41" s="198"/>
+      <c r="O41" s="198"/>
+      <c r="P41" s="198"/>
+      <c r="Q41" s="198"/>
+      <c r="R41" s="198"/>
+      <c r="S41" s="198"/>
+      <c r="T41" s="198"/>
+      <c r="U41" s="198"/>
     </row>
     <row r="42" ht="33.65" customHeight="1" spans="1:21">
       <c r="A42" s="182">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="B42" s="147" t="s">
+      <c r="B42" s="183" t="s">
         <v>95</v>
       </c>
-      <c r="C42" s="183" t="s">
+      <c r="C42" s="184" t="s">
         <v>96</v>
       </c>
-      <c r="D42" s="184" t="s">
+      <c r="D42" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E42" s="185">
+      <c r="E42" s="186">
         <v>560000</v>
       </c>
-      <c r="F42" s="186">
+      <c r="F42" s="187">
         <f t="shared" si="5"/>
         <v>44800</v>
       </c>
-      <c r="G42" s="187">
+      <c r="G42" s="188">
         <f t="shared" si="1"/>
         <v>604800</v>
       </c>
-      <c r="H42" s="188"/>
-      <c r="I42" s="107"/>
-      <c r="J42" s="164"/>
-      <c r="K42" s="107"/>
-      <c r="L42" s="107"/>
-      <c r="M42" s="196"/>
-      <c r="N42" s="196"/>
-      <c r="O42" s="196"/>
-      <c r="P42" s="196"/>
-      <c r="Q42" s="196"/>
-      <c r="R42" s="196"/>
-      <c r="S42" s="196"/>
-      <c r="T42" s="196"/>
-      <c r="U42" s="196"/>
+      <c r="H42" s="190"/>
+      <c r="I42" s="199"/>
+      <c r="J42" s="200"/>
+      <c r="K42" s="199"/>
+      <c r="L42" s="199"/>
+      <c r="M42" s="198"/>
+      <c r="N42" s="198"/>
+      <c r="O42" s="198"/>
+      <c r="P42" s="198"/>
+      <c r="Q42" s="198"/>
+      <c r="R42" s="198"/>
+      <c r="S42" s="198"/>
+      <c r="T42" s="198"/>
+      <c r="U42" s="198"/>
     </row>
     <row r="43" ht="33.65" customHeight="1" spans="1:21">
       <c r="A43" s="182">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="B43" s="147" t="s">
+      <c r="B43" s="183" t="s">
         <v>97</v>
       </c>
-      <c r="C43" s="183" t="s">
+      <c r="C43" s="184" t="s">
         <v>98</v>
       </c>
-      <c r="D43" s="184" t="s">
+      <c r="D43" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E43" s="185">
+      <c r="E43" s="186">
         <v>560000</v>
       </c>
-      <c r="F43" s="186">
+      <c r="F43" s="187">
         <f t="shared" si="5"/>
         <v>44800</v>
       </c>
-      <c r="G43" s="187">
+      <c r="G43" s="188">
         <f t="shared" si="1"/>
         <v>604800</v>
       </c>
-      <c r="H43" s="188"/>
-      <c r="I43" s="107"/>
-      <c r="J43" s="164"/>
-      <c r="K43" s="107"/>
-      <c r="L43" s="107"/>
-      <c r="M43" s="196"/>
-      <c r="N43" s="196"/>
-      <c r="O43" s="196"/>
-      <c r="P43" s="196"/>
-      <c r="Q43" s="196"/>
-      <c r="R43" s="196"/>
-      <c r="S43" s="196"/>
-      <c r="T43" s="196"/>
-      <c r="U43" s="196"/>
+      <c r="H43" s="190"/>
+      <c r="I43" s="199"/>
+      <c r="J43" s="200"/>
+      <c r="K43" s="199"/>
+      <c r="L43" s="199"/>
+      <c r="M43" s="198"/>
+      <c r="N43" s="198"/>
+      <c r="O43" s="198"/>
+      <c r="P43" s="198"/>
+      <c r="Q43" s="198"/>
+      <c r="R43" s="198"/>
+      <c r="S43" s="198"/>
+      <c r="T43" s="198"/>
+      <c r="U43" s="198"/>
     </row>
     <row r="44" ht="33.65" customHeight="1" spans="1:21">
       <c r="A44" s="182">
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
-      <c r="B44" s="147" t="s">
+      <c r="B44" s="183" t="s">
         <v>99</v>
       </c>
-      <c r="C44" s="183" t="s">
+      <c r="C44" s="184" t="s">
         <v>100</v>
       </c>
-      <c r="D44" s="184" t="s">
+      <c r="D44" s="185" t="s">
         <v>56</v>
       </c>
-      <c r="E44" s="185">
+      <c r="E44" s="186">
         <f>390000/1.1</f>
         <v>354545.454545455</v>
       </c>
-      <c r="F44" s="186">
+      <c r="F44" s="187">
         <f t="shared" si="5"/>
         <v>28363.6363636364</v>
       </c>
-      <c r="G44" s="187">
+      <c r="G44" s="188">
         <f t="shared" si="1"/>
         <v>382909.090909091</v>
       </c>
-      <c r="H44" s="188"/>
-      <c r="I44" s="107"/>
-      <c r="J44" s="164"/>
-      <c r="K44" s="107"/>
-      <c r="L44" s="107"/>
-      <c r="M44" s="196"/>
-      <c r="N44" s="196"/>
-      <c r="O44" s="196"/>
-      <c r="P44" s="196"/>
-      <c r="Q44" s="196"/>
-      <c r="R44" s="196"/>
-      <c r="S44" s="196"/>
-      <c r="T44" s="196"/>
-      <c r="U44" s="196"/>
+      <c r="H44" s="190"/>
+      <c r="I44" s="199"/>
+      <c r="J44" s="200"/>
+      <c r="K44" s="199"/>
+      <c r="L44" s="199"/>
+      <c r="M44" s="198"/>
+      <c r="N44" s="198"/>
+      <c r="O44" s="198"/>
+      <c r="P44" s="198"/>
+      <c r="Q44" s="198"/>
+      <c r="R44" s="198"/>
+      <c r="S44" s="198"/>
+      <c r="T44" s="198"/>
+      <c r="U44" s="198"/>
     </row>
     <row r="45" ht="33.65" customHeight="1" spans="1:21">
       <c r="A45" s="182">
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="B45" s="147" t="s">
+      <c r="B45" s="183" t="s">
         <v>101</v>
       </c>
-      <c r="C45" s="183" t="s">
+      <c r="C45" s="184" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="184" t="s">
+      <c r="D45" s="185" t="s">
         <v>48</v>
       </c>
-      <c r="E45" s="185">
+      <c r="E45" s="186">
         <v>367000</v>
       </c>
-      <c r="F45" s="186">
+      <c r="F45" s="187">
         <f t="shared" si="5"/>
         <v>29360</v>
       </c>
-      <c r="G45" s="187">
+      <c r="G45" s="188">
         <f t="shared" si="1"/>
         <v>396360</v>
       </c>
-      <c r="H45" s="188"/>
-      <c r="I45" s="107"/>
-      <c r="J45" s="164"/>
-      <c r="K45" s="107"/>
-      <c r="L45" s="107"/>
-      <c r="M45" s="196"/>
-      <c r="N45" s="196"/>
-      <c r="O45" s="196"/>
-      <c r="P45" s="196"/>
-      <c r="Q45" s="196"/>
-      <c r="R45" s="196"/>
-      <c r="S45" s="196"/>
-      <c r="T45" s="196"/>
-      <c r="U45" s="196"/>
+      <c r="H45" s="190"/>
+      <c r="I45" s="199"/>
+      <c r="J45" s="200"/>
+      <c r="K45" s="199"/>
+      <c r="L45" s="199"/>
+      <c r="M45" s="198"/>
+      <c r="N45" s="198"/>
+      <c r="O45" s="198"/>
+      <c r="P45" s="198"/>
+      <c r="Q45" s="198"/>
+      <c r="R45" s="198"/>
+      <c r="S45" s="198"/>
+      <c r="T45" s="198"/>
+      <c r="U45" s="198"/>
     </row>
     <row r="46" ht="33.65" customHeight="1" spans="1:21">
       <c r="A46" s="182">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="B46" s="147" t="s">
+      <c r="B46" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="C46" s="183" t="s">
+      <c r="C46" s="184" t="s">
         <v>62</v>
       </c>
-      <c r="D46" s="184" t="s">
+      <c r="D46" s="185" t="s">
         <v>56</v>
       </c>
-      <c r="E46" s="185">
+      <c r="E46" s="186">
         <f>390000/1.1</f>
         <v>354545.454545455</v>
       </c>
-      <c r="F46" s="186">
+      <c r="F46" s="187">
         <f t="shared" si="5"/>
         <v>28363.6363636364</v>
       </c>
-      <c r="G46" s="187">
+      <c r="G46" s="188">
         <f t="shared" si="1"/>
         <v>382909.090909091</v>
       </c>
-      <c r="H46" s="188"/>
-      <c r="I46" s="107"/>
-      <c r="J46" s="164"/>
-      <c r="K46" s="107"/>
-      <c r="L46" s="107"/>
-      <c r="M46" s="196"/>
-      <c r="N46" s="196"/>
-      <c r="O46" s="196"/>
-      <c r="P46" s="196"/>
-      <c r="Q46" s="196"/>
-      <c r="R46" s="196"/>
-      <c r="S46" s="196"/>
-      <c r="T46" s="196"/>
-      <c r="U46" s="196"/>
+      <c r="H46" s="190"/>
+      <c r="I46" s="199"/>
+      <c r="J46" s="200"/>
+      <c r="K46" s="199"/>
+      <c r="L46" s="199"/>
+      <c r="M46" s="198"/>
+      <c r="N46" s="198"/>
+      <c r="O46" s="198"/>
+      <c r="P46" s="198"/>
+      <c r="Q46" s="198"/>
+      <c r="R46" s="198"/>
+      <c r="S46" s="198"/>
+      <c r="T46" s="198"/>
+      <c r="U46" s="198"/>
     </row>
     <row r="47" ht="33.65" customHeight="1" spans="1:21">
       <c r="A47" s="182">
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="B47" s="147" t="s">
+      <c r="B47" s="183" t="s">
         <v>103</v>
       </c>
-      <c r="C47" s="183" t="s">
+      <c r="C47" s="184" t="s">
         <v>104</v>
       </c>
-      <c r="D47" s="184" t="s">
+      <c r="D47" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E47" s="185">
+      <c r="E47" s="186">
         <v>560000</v>
       </c>
-      <c r="F47" s="186">
+      <c r="F47" s="187">
         <f t="shared" si="5"/>
         <v>44800</v>
       </c>
-      <c r="G47" s="187">
+      <c r="G47" s="188">
         <f t="shared" si="1"/>
         <v>604800</v>
       </c>
-      <c r="H47" s="188"/>
-      <c r="I47" s="107"/>
-      <c r="J47" s="164"/>
-      <c r="K47" s="107"/>
-      <c r="L47" s="107"/>
-      <c r="M47" s="196"/>
-      <c r="N47" s="196"/>
-      <c r="O47" s="196"/>
-      <c r="P47" s="196"/>
-      <c r="Q47" s="196"/>
-      <c r="R47" s="196"/>
-      <c r="S47" s="196"/>
-      <c r="T47" s="196"/>
-      <c r="U47" s="196"/>
+      <c r="H47" s="190"/>
+      <c r="I47" s="199"/>
+      <c r="J47" s="200"/>
+      <c r="K47" s="199"/>
+      <c r="L47" s="199"/>
+      <c r="M47" s="198"/>
+      <c r="N47" s="198"/>
+      <c r="O47" s="198"/>
+      <c r="P47" s="198"/>
+      <c r="Q47" s="198"/>
+      <c r="R47" s="198"/>
+      <c r="S47" s="198"/>
+      <c r="T47" s="198"/>
+      <c r="U47" s="198"/>
     </row>
     <row r="48" ht="33.65" customHeight="1" spans="1:21">
       <c r="A48" s="182">
         <f t="shared" si="2"/>
         <v>36</v>
       </c>
-      <c r="B48" s="147" t="s">
+      <c r="B48" s="183" t="s">
         <v>105</v>
       </c>
-      <c r="C48" s="183" t="s">
+      <c r="C48" s="184" t="s">
         <v>106</v>
       </c>
-      <c r="D48" s="184" t="s">
+      <c r="D48" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E48" s="185">
+      <c r="E48" s="186">
         <v>560000</v>
       </c>
-      <c r="F48" s="186">
+      <c r="F48" s="187">
         <f t="shared" si="5"/>
         <v>44800</v>
       </c>
-      <c r="G48" s="187">
+      <c r="G48" s="188">
         <f t="shared" si="1"/>
         <v>604800</v>
       </c>
-      <c r="H48" s="188"/>
-      <c r="I48" s="107"/>
-      <c r="J48" s="164"/>
-      <c r="K48" s="107"/>
-      <c r="L48" s="107"/>
-      <c r="M48" s="196"/>
-      <c r="N48" s="196"/>
-      <c r="O48" s="196"/>
-      <c r="P48" s="196"/>
-      <c r="Q48" s="196"/>
-      <c r="R48" s="196"/>
-      <c r="S48" s="196"/>
-      <c r="T48" s="196"/>
-      <c r="U48" s="196"/>
+      <c r="H48" s="190"/>
+      <c r="I48" s="199"/>
+      <c r="J48" s="200"/>
+      <c r="K48" s="199"/>
+      <c r="L48" s="199"/>
+      <c r="M48" s="198"/>
+      <c r="N48" s="198"/>
+      <c r="O48" s="198"/>
+      <c r="P48" s="198"/>
+      <c r="Q48" s="198"/>
+      <c r="R48" s="198"/>
+      <c r="S48" s="198"/>
+      <c r="T48" s="198"/>
+      <c r="U48" s="198"/>
     </row>
     <row r="49" ht="33.65" customHeight="1" spans="1:21">
       <c r="A49" s="182">
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="B49" s="147" t="s">
+      <c r="B49" s="183" t="s">
         <v>107</v>
       </c>
-      <c r="C49" s="183" t="s">
+      <c r="C49" s="184" t="s">
         <v>108</v>
       </c>
-      <c r="D49" s="184" t="s">
+      <c r="D49" s="185" t="s">
         <v>48</v>
       </c>
-      <c r="E49" s="185">
+      <c r="E49" s="186">
         <v>367000</v>
       </c>
-      <c r="F49" s="186">
+      <c r="F49" s="187">
         <f t="shared" si="5"/>
         <v>29360</v>
       </c>
-      <c r="G49" s="187">
+      <c r="G49" s="188">
         <f t="shared" si="1"/>
         <v>396360</v>
       </c>
-      <c r="H49" s="188"/>
-      <c r="I49" s="107"/>
-      <c r="J49" s="164"/>
-      <c r="K49" s="107"/>
-      <c r="L49" s="107"/>
-      <c r="M49" s="196"/>
-      <c r="N49" s="196"/>
-      <c r="O49" s="196"/>
-      <c r="P49" s="196"/>
-      <c r="Q49" s="196"/>
-      <c r="R49" s="196"/>
-      <c r="S49" s="196"/>
-      <c r="T49" s="196"/>
-      <c r="U49" s="196"/>
+      <c r="H49" s="190"/>
+      <c r="I49" s="199"/>
+      <c r="J49" s="200"/>
+      <c r="K49" s="199"/>
+      <c r="L49" s="199"/>
+      <c r="M49" s="198"/>
+      <c r="N49" s="198"/>
+      <c r="O49" s="198"/>
+      <c r="P49" s="198"/>
+      <c r="Q49" s="198"/>
+      <c r="R49" s="198"/>
+      <c r="S49" s="198"/>
+      <c r="T49" s="198"/>
+      <c r="U49" s="198"/>
     </row>
     <row r="50" ht="33.65" customHeight="1" spans="1:21">
       <c r="A50" s="182">
         <f t="shared" si="2"/>
         <v>38</v>
       </c>
-      <c r="B50" s="198" t="s">
+      <c r="B50" s="202" t="s">
         <v>109</v>
       </c>
-      <c r="C50" s="183" t="s">
+      <c r="C50" s="184" t="s">
         <v>110</v>
       </c>
-      <c r="D50" s="184" t="s">
+      <c r="D50" s="185" t="s">
         <v>111</v>
       </c>
-      <c r="E50" s="187">
+      <c r="E50" s="188">
         <v>390909</v>
       </c>
-      <c r="F50" s="186">
+      <c r="F50" s="187">
         <f t="shared" si="5"/>
         <v>31272.72</v>
       </c>
-      <c r="G50" s="187">
+      <c r="G50" s="188">
         <f t="shared" si="1"/>
         <v>422181.72</v>
       </c>
-      <c r="H50" s="188"/>
-      <c r="I50" s="107"/>
-      <c r="J50" s="164"/>
-      <c r="K50" s="107"/>
-      <c r="L50" s="107"/>
-      <c r="M50" s="196"/>
-      <c r="N50" s="196"/>
-      <c r="O50" s="196"/>
-      <c r="P50" s="196"/>
-      <c r="Q50" s="196"/>
-      <c r="R50" s="196"/>
-      <c r="S50" s="196"/>
-      <c r="T50" s="196"/>
-      <c r="U50" s="196"/>
+      <c r="H50" s="190"/>
+      <c r="I50" s="199"/>
+      <c r="J50" s="200"/>
+      <c r="K50" s="199"/>
+      <c r="L50" s="199"/>
+      <c r="M50" s="198"/>
+      <c r="N50" s="198"/>
+      <c r="O50" s="198"/>
+      <c r="P50" s="198"/>
+      <c r="Q50" s="198"/>
+      <c r="R50" s="198"/>
+      <c r="S50" s="198"/>
+      <c r="T50" s="198"/>
+      <c r="U50" s="198"/>
     </row>
     <row r="51" ht="33.65" customHeight="1" spans="1:21">
       <c r="A51" s="182">
         <f t="shared" si="2"/>
         <v>39</v>
       </c>
-      <c r="B51" s="147" t="s">
+      <c r="B51" s="183" t="s">
         <v>112</v>
       </c>
-      <c r="C51" s="183" t="s">
+      <c r="C51" s="184" t="s">
         <v>113</v>
       </c>
-      <c r="D51" s="184" t="s">
+      <c r="D51" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E51" s="185">
+      <c r="E51" s="186">
         <v>560000</v>
       </c>
-      <c r="F51" s="186">
+      <c r="F51" s="187">
         <f t="shared" si="5"/>
         <v>44800</v>
       </c>
-      <c r="G51" s="187">
+      <c r="G51" s="188">
         <f t="shared" si="1"/>
         <v>604800</v>
       </c>
-      <c r="H51" s="188"/>
-      <c r="I51" s="107"/>
-      <c r="J51" s="164"/>
-      <c r="K51" s="107"/>
-      <c r="L51" s="107"/>
-      <c r="M51" s="196"/>
-      <c r="N51" s="196"/>
-      <c r="O51" s="196"/>
-      <c r="P51" s="196"/>
-      <c r="Q51" s="196"/>
-      <c r="R51" s="196"/>
-      <c r="S51" s="196"/>
-      <c r="T51" s="196"/>
-      <c r="U51" s="196"/>
+      <c r="H51" s="190"/>
+      <c r="I51" s="199"/>
+      <c r="J51" s="200"/>
+      <c r="K51" s="199"/>
+      <c r="L51" s="199"/>
+      <c r="M51" s="198"/>
+      <c r="N51" s="198"/>
+      <c r="O51" s="198"/>
+      <c r="P51" s="198"/>
+      <c r="Q51" s="198"/>
+      <c r="R51" s="198"/>
+      <c r="S51" s="198"/>
+      <c r="T51" s="198"/>
+      <c r="U51" s="198"/>
     </row>
     <row r="52" ht="33.65" customHeight="1" spans="1:21">
       <c r="A52" s="182">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="B52" s="147" t="s">
+      <c r="B52" s="183" t="s">
         <v>114</v>
       </c>
-      <c r="C52" s="183" t="s">
+      <c r="C52" s="184" t="s">
         <v>115</v>
       </c>
-      <c r="D52" s="184" t="s">
+      <c r="D52" s="185" t="s">
         <v>48</v>
       </c>
-      <c r="E52" s="185">
+      <c r="E52" s="186">
         <v>367000</v>
       </c>
-      <c r="F52" s="186">
+      <c r="F52" s="187">
         <f t="shared" si="5"/>
         <v>29360</v>
       </c>
-      <c r="G52" s="187">
+      <c r="G52" s="188">
         <f t="shared" si="1"/>
         <v>396360</v>
       </c>
-      <c r="H52" s="188"/>
-      <c r="I52" s="107"/>
-      <c r="J52" s="164"/>
-      <c r="K52" s="107"/>
-      <c r="L52" s="107"/>
-      <c r="M52" s="196"/>
-      <c r="N52" s="196"/>
-      <c r="O52" s="196"/>
-      <c r="P52" s="196"/>
-      <c r="Q52" s="196"/>
-      <c r="R52" s="196"/>
-      <c r="S52" s="196"/>
-      <c r="T52" s="196"/>
-      <c r="U52" s="196"/>
+      <c r="H52" s="190"/>
+      <c r="I52" s="199"/>
+      <c r="J52" s="200"/>
+      <c r="K52" s="199"/>
+      <c r="L52" s="199"/>
+      <c r="M52" s="198"/>
+      <c r="N52" s="198"/>
+      <c r="O52" s="198"/>
+      <c r="P52" s="198"/>
+      <c r="Q52" s="198"/>
+      <c r="R52" s="198"/>
+      <c r="S52" s="198"/>
+      <c r="T52" s="198"/>
+      <c r="U52" s="198"/>
     </row>
     <row r="53" ht="33.65" customHeight="1" spans="1:21">
       <c r="A53" s="182">
         <f t="shared" si="2"/>
         <v>41</v>
       </c>
-      <c r="B53" s="147" t="s">
+      <c r="B53" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="C53" s="183" t="s">
+      <c r="C53" s="184" t="s">
         <v>117</v>
       </c>
-      <c r="D53" s="184" t="s">
+      <c r="D53" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E53" s="185">
+      <c r="E53" s="186">
         <v>560000</v>
       </c>
-      <c r="F53" s="186">
+      <c r="F53" s="187">
         <f t="shared" si="5"/>
         <v>44800</v>
       </c>
-      <c r="G53" s="187">
+      <c r="G53" s="188">
         <f t="shared" si="1"/>
         <v>604800</v>
       </c>
-      <c r="H53" s="188"/>
-      <c r="I53" s="107"/>
-      <c r="J53" s="164"/>
-      <c r="K53" s="107"/>
-      <c r="L53" s="107"/>
-      <c r="M53" s="196"/>
-      <c r="N53" s="196"/>
-      <c r="O53" s="196"/>
-      <c r="P53" s="196"/>
-      <c r="Q53" s="196"/>
-      <c r="R53" s="196"/>
-      <c r="S53" s="196"/>
-      <c r="T53" s="196"/>
-      <c r="U53" s="196"/>
+      <c r="H53" s="190"/>
+      <c r="I53" s="199"/>
+      <c r="J53" s="200"/>
+      <c r="K53" s="199"/>
+      <c r="L53" s="199"/>
+      <c r="M53" s="198"/>
+      <c r="N53" s="198"/>
+      <c r="O53" s="198"/>
+      <c r="P53" s="198"/>
+      <c r="Q53" s="198"/>
+      <c r="R53" s="198"/>
+      <c r="S53" s="198"/>
+      <c r="T53" s="198"/>
+      <c r="U53" s="198"/>
     </row>
     <row r="54" ht="33.65" customHeight="1" spans="1:21">
       <c r="A54" s="182">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="B54" s="147" t="s">
+      <c r="B54" s="183" t="s">
         <v>118</v>
       </c>
-      <c r="C54" s="183" t="s">
+      <c r="C54" s="184" t="s">
         <v>119</v>
       </c>
-      <c r="D54" s="184" t="s">
+      <c r="D54" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="E54" s="185">
+      <c r="E54" s="186">
         <v>560000</v>
       </c>
-      <c r="F54" s="186">
+      <c r="F54" s="187">
         <f t="shared" si="5"/>
         <v>44800</v>
       </c>
-      <c r="G54" s="187">
+      <c r="G54" s="188">
         <f t="shared" si="1"/>
         <v>604800</v>
       </c>
-      <c r="H54" s="188"/>
-      <c r="I54" s="107"/>
-      <c r="J54" s="164"/>
-      <c r="K54" s="107"/>
-      <c r="L54" s="107"/>
-      <c r="M54" s="196"/>
-      <c r="N54" s="196"/>
-      <c r="O54" s="196"/>
-      <c r="P54" s="196"/>
-      <c r="Q54" s="196"/>
-      <c r="R54" s="196"/>
-      <c r="S54" s="196"/>
-      <c r="T54" s="196"/>
-      <c r="U54" s="196"/>
+      <c r="H54" s="190"/>
+      <c r="I54" s="199"/>
+      <c r="J54" s="200"/>
+      <c r="K54" s="199"/>
+      <c r="L54" s="199"/>
+      <c r="M54" s="198"/>
+      <c r="N54" s="198"/>
+      <c r="O54" s="198"/>
+      <c r="P54" s="198"/>
+      <c r="Q54" s="198"/>
+      <c r="R54" s="198"/>
+      <c r="S54" s="198"/>
+      <c r="T54" s="198"/>
+      <c r="U54" s="198"/>
     </row>
     <row r="55" ht="33.65" customHeight="1" spans="1:21">
       <c r="A55" s="182">
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="B55" s="147" t="s">
+      <c r="B55" s="183" t="s">
         <v>120</v>
       </c>
-      <c r="C55" s="183" t="s">
+      <c r="C55" s="184" t="s">
         <v>121</v>
       </c>
-      <c r="D55" s="184" t="s">
+      <c r="D55" s="185" t="s">
         <v>48</v>
       </c>
-      <c r="E55" s="185">
+      <c r="E55" s="186">
         <v>367000</v>
       </c>
-      <c r="F55" s="186">
+      <c r="F55" s="187">
         <f t="shared" si="5"/>
         <v>29360</v>
       </c>
-      <c r="G55" s="187">
+      <c r="G55" s="188">
         <f t="shared" si="1"/>
         <v>396360</v>
       </c>
-      <c r="H55" s="188"/>
-      <c r="I55" s="107"/>
-      <c r="J55" s="164"/>
-      <c r="K55" s="107"/>
-      <c r="L55" s="107"/>
-      <c r="M55" s="196"/>
-      <c r="N55" s="196"/>
-      <c r="O55" s="196"/>
-      <c r="P55" s="196"/>
-      <c r="Q55" s="196"/>
-      <c r="R55" s="196"/>
-      <c r="S55" s="196"/>
-      <c r="T55" s="196"/>
-      <c r="U55" s="196"/>
+      <c r="H55" s="190"/>
+      <c r="I55" s="199"/>
+      <c r="J55" s="200"/>
+      <c r="K55" s="199"/>
+      <c r="L55" s="199"/>
+      <c r="M55" s="198"/>
+      <c r="N55" s="198"/>
+      <c r="O55" s="198"/>
+      <c r="P55" s="198"/>
+      <c r="Q55" s="198"/>
+      <c r="R55" s="198"/>
+      <c r="S55" s="198"/>
+      <c r="T55" s="198"/>
+      <c r="U55" s="198"/>
     </row>
     <row r="56" ht="30" customHeight="1" spans="1:13">
-      <c r="A56" s="190"/>
+      <c r="A56" s="192"/>
       <c r="B56" s="181" t="s">
         <v>122</v>
       </c>
       <c r="C56" s="181"/>
-      <c r="D56" s="191"/>
-      <c r="E56" s="192">
+      <c r="D56" s="193"/>
+      <c r="E56" s="194">
         <f>SUM(E13:E55)</f>
         <v>19217090.8181818</v>
       </c>
-      <c r="F56" s="192">
+      <c r="F56" s="194">
         <f t="shared" ref="F56:G56" si="6">SUM(F13:F55)</f>
         <v>1537367.26545455</v>
       </c>
-      <c r="G56" s="192">
+      <c r="G56" s="194">
         <f t="shared" si="6"/>
         <v>20754458.0836364</v>
       </c>
-      <c r="H56" s="193">
+      <c r="H56" s="195">
         <f>SUM(H13:H26)</f>
         <v>0</v>
       </c>
-      <c r="J56" s="196"/>
-      <c r="K56" s="196"/>
-      <c r="L56" s="196"/>
-      <c r="M56" s="196"/>
+      <c r="J56" s="198"/>
+      <c r="K56" s="198"/>
+      <c r="L56" s="198"/>
+      <c r="M56" s="198"/>
     </row>
     <row r="57" ht="22.5" customHeight="1" spans="1:13">
       <c r="A57" s="8"/>
       <c r="B57" s="11"/>
-      <c r="C57" s="194"/>
-      <c r="D57" s="195"/>
-      <c r="E57" s="195"/>
-      <c r="F57" s="195"/>
-      <c r="G57" s="195"/>
+      <c r="C57" s="196"/>
+      <c r="D57" s="197"/>
+      <c r="E57" s="197"/>
+      <c r="F57" s="197"/>
+      <c r="G57" s="197"/>
       <c r="H57" s="11"/>
-      <c r="J57" s="196"/>
-      <c r="K57" s="196"/>
-      <c r="L57" s="196"/>
-      <c r="M57" s="196"/>
+      <c r="J57" s="198"/>
+      <c r="K57" s="198"/>
+      <c r="L57" s="198"/>
+      <c r="M57" s="198"/>
     </row>
     <row r="58" ht="12.75" customHeight="1" spans="4:13">
       <c r="D58" s="11"/>
@@ -5881,10 +5954,10 @@
         <v>123</v>
       </c>
       <c r="H58" s="1"/>
-      <c r="J58" s="196"/>
-      <c r="K58" s="196"/>
-      <c r="L58" s="196"/>
-      <c r="M58" s="196"/>
+      <c r="J58" s="198"/>
+      <c r="K58" s="198"/>
+      <c r="L58" s="198"/>
+      <c r="M58" s="198"/>
     </row>
     <row r="59" ht="12.75" customHeight="1" spans="2:8">
       <c r="B59" s="11" t="s">
@@ -5958,34 +6031,35 @@
     <col min="12" max="16384" width="13.4537037037037" style="107"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.75" customHeight="1" spans="1:7">
+    <row r="1" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A1" s="110"/>
       <c r="B1" s="111"/>
-      <c r="C1" s="199" t="s">
+      <c r="C1" s="203" t="s">
         <v>126</v>
       </c>
       <c r="D1" s="110"/>
       <c r="E1" s="113"/>
       <c r="G1" s="109"/>
     </row>
-    <row r="2" ht="12.75" customHeight="1" spans="1:7">
+    <row r="2" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A2" s="110"/>
       <c r="B2" s="111"/>
-      <c r="C2" s="199" t="s">
+      <c r="C2" s="203" t="s">
         <v>127</v>
       </c>
       <c r="D2" s="110"/>
       <c r="E2" s="113"/>
       <c r="G2" s="109"/>
     </row>
-    <row r="3" ht="12.75" customHeight="1" spans="3:7">
-      <c r="C3" s="199" t="s">
+    <row r="3" s="107" customFormat="1" ht="12.75" customHeight="1" spans="2:7">
+      <c r="B3" s="109"/>
+      <c r="C3" s="203" t="s">
         <v>128</v>
       </c>
       <c r="E3" s="114"/>
       <c r="G3" s="109"/>
     </row>
-    <row r="4" ht="23.25" customHeight="1" spans="1:11">
+    <row r="4" s="107" customFormat="1" ht="23.25" customHeight="1" spans="1:11">
       <c r="A4" s="115" t="s">
         <v>129</v>
       </c>
@@ -6001,7 +6075,7 @@
       <c r="K4" s="116"/>
     </row>
     <row r="5" s="107" customFormat="1" ht="23.25" customHeight="1" spans="1:11">
-      <c r="A5" s="117" t="s">
+      <c r="A5" s="204" t="s">
         <v>130</v>
       </c>
       <c r="B5" s="116"/>
@@ -6015,19 +6089,17 @@
       <c r="J5" s="116"/>
       <c r="K5" s="116"/>
     </row>
-    <row r="6" ht="23.25" customHeight="1" spans="1:2">
+    <row r="6" s="107" customFormat="1" ht="23.25" customHeight="1" spans="1:1">
       <c r="A6" s="118" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" s="107" customFormat="1" ht="23.25" customHeight="1" spans="1:1">
+      <c r="A7" s="118" t="s">
         <v>131</v>
       </c>
-      <c r="B6" s="107"/>
-    </row>
-    <row r="7" ht="23.25" customHeight="1" spans="1:2">
-      <c r="A7" s="118" t="s">
-        <v>132</v>
-      </c>
-      <c r="B7" s="107"/>
-    </row>
-    <row r="8" ht="12.75" customHeight="1" spans="1:11">
+    </row>
+    <row r="8" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:11">
       <c r="A8" s="118"/>
       <c r="B8" s="118"/>
       <c r="C8" s="118"/>
@@ -6040,7 +6112,7 @@
       <c r="J8" s="118"/>
       <c r="K8" s="118"/>
     </row>
-    <row r="9" ht="12.75" customHeight="1" spans="1:11">
+    <row r="9" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:11">
       <c r="A9" s="120" t="s">
         <v>13</v>
       </c>
@@ -6051,46 +6123,46 @@
         <v>15</v>
       </c>
       <c r="D9" s="122" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E9" s="123"/>
       <c r="F9" s="123"/>
       <c r="G9" s="122" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H9" s="123"/>
       <c r="I9" s="123"/>
       <c r="J9" s="123"/>
       <c r="K9" s="123"/>
     </row>
-    <row r="10" ht="62.7" customHeight="1" spans="1:11">
+    <row r="10" s="107" customFormat="1" ht="62.7" customHeight="1" spans="1:11">
       <c r="A10" s="123"/>
       <c r="B10" s="124"/>
       <c r="C10" s="123"/>
       <c r="D10" s="123"/>
       <c r="E10" s="125" t="s">
+        <v>134</v>
+      </c>
+      <c r="F10" s="122" t="s">
         <v>135</v>
       </c>
-      <c r="F10" s="122" t="s">
+      <c r="G10" s="122" t="s">
         <v>136</v>
       </c>
-      <c r="G10" s="122" t="s">
+      <c r="H10" s="122" t="s">
         <v>137</v>
       </c>
-      <c r="H10" s="122" t="s">
+      <c r="I10" s="122" t="s">
         <v>138</v>
       </c>
-      <c r="I10" s="122" t="s">
+      <c r="J10" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="J10" s="122" t="s">
+      <c r="K10" s="122" t="s">
         <v>140</v>
       </c>
-      <c r="K10" s="122" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="11" ht="29.25" customHeight="1" spans="1:11">
+    </row>
+    <row r="11" s="107" customFormat="1" ht="29.25" customHeight="1" spans="1:11">
       <c r="A11" s="126" t="s">
         <v>22</v>
       </c>
@@ -6108,47 +6180,49 @@
         <v>29</v>
       </c>
       <c r="G11" s="121" t="s">
+        <v>141</v>
+      </c>
+      <c r="H11" s="121" t="s">
         <v>142</v>
       </c>
-      <c r="H11" s="121" t="s">
+      <c r="I11" s="121" t="s">
         <v>143</v>
       </c>
-      <c r="I11" s="121" t="s">
+      <c r="J11" s="121" t="s">
         <v>144</v>
       </c>
-      <c r="J11" s="121" t="s">
+      <c r="K11" s="121" t="s">
         <v>145</v>
       </c>
-      <c r="K11" s="121" t="s">
+    </row>
+    <row r="12" s="107" customFormat="1" ht="36.25" customHeight="1" spans="1:11">
+      <c r="A12" s="127" t="s">
         <v>146</v>
-      </c>
-    </row>
-    <row r="12" ht="36.25" customHeight="1" spans="1:11">
-      <c r="A12" s="127" t="s">
-        <v>147</v>
       </c>
       <c r="B12" s="128"/>
       <c r="C12" s="129"/>
       <c r="D12" s="130"/>
       <c r="E12" s="130" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F12" s="130" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G12" s="130"/>
       <c r="H12" s="130" t="s">
-        <v>148</v>
-      </c>
-      <c r="I12" s="130"/>
+        <v>147</v>
+      </c>
+      <c r="I12" s="130" t="s">
+        <v>147</v>
+      </c>
       <c r="J12" s="130" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K12" s="130" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="13" ht="27" customHeight="1" spans="1:11">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" s="107" customFormat="1" ht="27" customHeight="1" spans="1:11">
       <c r="A13" s="131"/>
       <c r="B13"/>
       <c r="C13"/>
@@ -6173,7 +6247,7 @@
     <row r="14" s="108" customFormat="1" ht="32.25" hidden="1" customHeight="1" spans="1:11">
       <c r="A14" s="132"/>
       <c r="B14" s="133" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C14" s="134"/>
       <c r="D14" s="134"/>
@@ -6185,10 +6259,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G14" s="135">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="G14" s="135"/>
       <c r="H14" s="135">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6206,7 +6277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="30.75" hidden="1" customHeight="1" spans="1:11">
+    <row r="15" s="107" customFormat="1" ht="30.75" hidden="1" customHeight="1" spans="1:11">
       <c r="A15" s="131"/>
       <c r="B15" s="136"/>
       <c r="C15" s="137"/>
@@ -6221,30 +6292,32 @@
     </row>
     <row r="16" s="108" customFormat="1" ht="32.25" customHeight="1" spans="1:11">
       <c r="A16" s="141" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B16" s="142"/>
       <c r="C16" s="143"/>
       <c r="D16" s="134"/>
       <c r="E16" s="134" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F16" s="134" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G16" s="134"/>
       <c r="H16" s="134" t="s">
-        <v>151</v>
-      </c>
-      <c r="I16" s="134"/>
+        <v>150</v>
+      </c>
+      <c r="I16" s="134" t="s">
+        <v>150</v>
+      </c>
       <c r="J16" s="134" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K16" s="134" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="17" ht="30.75" customHeight="1" spans="1:11">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" s="107" customFormat="1" ht="30.75" customHeight="1" spans="1:11">
       <c r="A17" s="131"/>
       <c r="B17" s="136"/>
       <c r="C17" s="144"/>
@@ -6259,30 +6332,32 @@
     </row>
     <row r="18" s="108" customFormat="1" ht="32.25" customHeight="1" spans="1:11">
       <c r="A18" s="141" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B18" s="142"/>
       <c r="C18" s="143"/>
       <c r="D18" s="134"/>
       <c r="E18" s="134" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F18" s="134" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G18" s="134"/>
       <c r="H18" s="134" t="s">
-        <v>153</v>
-      </c>
-      <c r="I18" s="134"/>
+        <v>152</v>
+      </c>
+      <c r="I18" s="134" t="s">
+        <v>152</v>
+      </c>
       <c r="J18" s="134" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K18" s="134" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="19" ht="30.75" customHeight="1" spans="1:11">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19" s="107" customFormat="1" ht="30.75" customHeight="1" spans="1:11">
       <c r="A19" s="131"/>
       <c r="B19" s="136"/>
       <c r="C19" s="136"/>
@@ -6297,30 +6372,32 @@
     </row>
     <row r="20" s="108" customFormat="1" ht="32.25" customHeight="1" spans="1:11">
       <c r="A20" s="141" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B20" s="142"/>
       <c r="C20" s="143"/>
       <c r="D20" s="134"/>
       <c r="E20" s="134" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F20" s="134" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G20" s="134"/>
       <c r="H20" s="134" t="s">
-        <v>155</v>
-      </c>
-      <c r="I20" s="134"/>
+        <v>154</v>
+      </c>
+      <c r="I20" s="134" t="s">
+        <v>154</v>
+      </c>
       <c r="J20" s="134" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K20" s="134" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="21" ht="30.75" customHeight="1" spans="1:11">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="21" s="107" customFormat="1" ht="30.75" customHeight="1" spans="1:11">
       <c r="A21" s="131"/>
       <c r="B21" s="136"/>
       <c r="C21" s="136"/>
@@ -6335,30 +6412,32 @@
     </row>
     <row r="22" s="108" customFormat="1" ht="32.25" customHeight="1" spans="1:11">
       <c r="A22" s="141" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B22" s="142"/>
       <c r="C22" s="143"/>
       <c r="D22" s="134"/>
       <c r="E22" s="134" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F22" s="134" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G22" s="134"/>
       <c r="H22" s="134" t="s">
-        <v>157</v>
-      </c>
-      <c r="I22" s="134"/>
+        <v>156</v>
+      </c>
+      <c r="I22" s="134" t="s">
+        <v>156</v>
+      </c>
       <c r="J22" s="134" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K22" s="134" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="23" ht="30.75" customHeight="1" spans="1:11">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="23" s="107" customFormat="1" ht="30.75" customHeight="1" spans="1:11">
       <c r="A23" s="131"/>
       <c r="B23" s="146"/>
       <c r="C23" s="146"/>
@@ -6371,10 +6450,10 @@
       <c r="J23" s="131"/>
       <c r="K23" s="131"/>
     </row>
-    <row r="24" ht="32.25" customHeight="1" spans="1:11">
+    <row r="24" s="107" customFormat="1" ht="32.25" customHeight="1" spans="1:11">
       <c r="A24" s="147"/>
       <c r="B24" s="148" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C24" s="149"/>
       <c r="D24" s="150"/>
@@ -6391,7 +6470,10 @@
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="I24" s="150"/>
+      <c r="I24" s="150" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="J24" s="150" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
@@ -6401,28 +6483,29 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="25" ht="19.5" customHeight="1" spans="1:11">
+    <row r="25" s="107" customFormat="1" ht="19.5" customHeight="1" spans="1:11">
       <c r="A25" s="151"/>
       <c r="B25" s="111"/>
       <c r="C25" s="151" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D25" s="151"/>
       <c r="E25" s="152"/>
       <c r="F25" s="153"/>
       <c r="G25" s="111"/>
-      <c r="H25" s="154" t="s">
-        <v>160</v>
+      <c r="H25" s="154" t="e">
+        <f>K24</f>
+        <v>#VALUE!</v>
       </c>
       <c r="I25" s="151"/>
       <c r="J25" s="151"/>
       <c r="K25" s="158"/>
     </row>
-    <row r="26" ht="19.5" customHeight="1" spans="1:11">
+    <row r="26" s="107" customFormat="1" ht="19.5" customHeight="1" spans="1:11">
       <c r="A26" s="151"/>
       <c r="B26" s="111"/>
       <c r="C26" s="151" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D26" s="155"/>
       <c r="E26" s="156"/>
@@ -6433,23 +6516,24 @@
       <c r="J26" s="151"/>
       <c r="K26" s="158"/>
     </row>
-    <row r="27" ht="19.5" customHeight="1" spans="1:11">
+    <row r="27" s="107" customFormat="1" ht="19.5" customHeight="1" spans="1:11">
       <c r="A27" s="151"/>
       <c r="B27" s="111"/>
       <c r="C27" s="151" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D27" s="155"/>
       <c r="E27" s="156"/>
       <c r="G27" s="111"/>
-      <c r="H27" s="154" t="s">
-        <v>163</v>
+      <c r="H27" s="154" t="e">
+        <f>H25+H26</f>
+        <v>#VALUE!</v>
       </c>
       <c r="I27" s="151"/>
       <c r="J27" s="151"/>
       <c r="K27" s="158"/>
     </row>
-    <row r="28" ht="19.5" customHeight="1" spans="1:11">
+    <row r="28" s="107" customFormat="1" ht="19.5" customHeight="1" spans="1:11">
       <c r="A28" s="151"/>
       <c r="B28" s="111"/>
       <c r="C28" s="151"/>
@@ -6462,7 +6546,7 @@
       <c r="J28" s="151"/>
       <c r="K28" s="158"/>
     </row>
-    <row r="29" ht="19.95" customHeight="1" spans="1:8">
+    <row r="29" s="107" customFormat="1" ht="19.95" customHeight="1" spans="1:8">
       <c r="A29" s="155"/>
       <c r="B29" s="111"/>
       <c r="C29" s="155"/>
@@ -6471,10 +6555,10 @@
       <c r="F29" s="155"/>
       <c r="G29" s="111"/>
       <c r="H29" s="109" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="30" ht="19.95" customHeight="1" spans="1:8">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="30" s="107" customFormat="1" ht="19.95" customHeight="1" spans="1:8">
       <c r="A30" s="111"/>
       <c r="B30" s="111"/>
       <c r="C30" s="111" t="s">
@@ -6483,16 +6567,17 @@
       <c r="D30" s="111"/>
       <c r="E30" s="160"/>
       <c r="H30" s="111" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="31" ht="19.95" customHeight="1" spans="5:8">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="31" s="107" customFormat="1" ht="19.95" customHeight="1" spans="2:8">
+      <c r="B31" s="109"/>
       <c r="E31" s="114"/>
       <c r="F31" s="161"/>
       <c r="G31" s="162"/>
       <c r="H31" s="163"/>
     </row>
-    <row r="32" ht="24" customHeight="1" spans="1:7">
+    <row r="32" s="107" customFormat="1" ht="24" customHeight="1" spans="1:7">
       <c r="A32" s="164"/>
       <c r="B32" s="165"/>
       <c r="C32" s="110"/>
@@ -6500,7 +6585,7 @@
       <c r="E32" s="114"/>
       <c r="G32" s="109"/>
     </row>
-    <row r="33" ht="24" customHeight="1" spans="1:7">
+    <row r="33" s="107" customFormat="1" ht="24" customHeight="1" spans="1:7">
       <c r="A33" s="164"/>
       <c r="B33" s="165"/>
       <c r="C33" s="110"/>
@@ -6509,7 +6594,7 @@
       <c r="F33" s="166"/>
       <c r="G33" s="109"/>
     </row>
-    <row r="34" ht="24" customHeight="1" spans="1:7">
+    <row r="34" s="107" customFormat="1" ht="24" customHeight="1" spans="1:7">
       <c r="A34" s="164"/>
       <c r="B34" s="165"/>
       <c r="C34" s="110"/>
@@ -6518,3363 +6603,4099 @@
       <c r="F34" s="166"/>
       <c r="G34" s="109"/>
     </row>
-    <row r="35" ht="24" customHeight="1" spans="1:7">
+    <row r="35" s="107" customFormat="1" ht="24" customHeight="1" spans="1:7">
       <c r="A35" s="164"/>
       <c r="B35" s="167"/>
       <c r="E35" s="114"/>
       <c r="F35" s="161"/>
       <c r="G35" s="109"/>
     </row>
-    <row r="36" ht="24" customHeight="1" spans="1:7">
+    <row r="36" s="107" customFormat="1" ht="24" customHeight="1" spans="1:7">
       <c r="A36" s="164"/>
       <c r="B36" s="167"/>
       <c r="E36" s="114"/>
       <c r="G36" s="109"/>
     </row>
-    <row r="37" ht="24" customHeight="1" spans="1:7">
+    <row r="37" s="107" customFormat="1" ht="24" customHeight="1" spans="1:7">
       <c r="A37" s="164"/>
       <c r="B37" s="167"/>
       <c r="E37" s="114"/>
       <c r="F37" s="161"/>
       <c r="G37" s="109"/>
     </row>
-    <row r="38" ht="24" customHeight="1" spans="1:7">
+    <row r="38" s="107" customFormat="1" ht="24" customHeight="1" spans="1:7">
       <c r="A38" s="164"/>
       <c r="B38" s="167"/>
       <c r="E38" s="114"/>
       <c r="F38" s="161"/>
       <c r="G38" s="109"/>
     </row>
-    <row r="39" ht="24" customHeight="1" spans="1:7">
+    <row r="39" s="107" customFormat="1" ht="24" customHeight="1" spans="1:7">
       <c r="A39" s="164"/>
       <c r="B39" s="167"/>
       <c r="E39" s="114"/>
       <c r="F39" s="161"/>
       <c r="G39" s="109"/>
     </row>
-    <row r="40" ht="24" customHeight="1" spans="1:7">
+    <row r="40" s="107" customFormat="1" ht="24" customHeight="1" spans="1:7">
       <c r="A40" s="164"/>
       <c r="B40" s="167"/>
       <c r="E40" s="114"/>
       <c r="G40" s="109"/>
     </row>
-    <row r="41" ht="24" customHeight="1" spans="1:7">
+    <row r="41" s="107" customFormat="1" ht="24" customHeight="1" spans="1:7">
       <c r="A41" s="164"/>
       <c r="B41" s="167"/>
       <c r="E41" s="114"/>
       <c r="F41" s="161"/>
       <c r="G41" s="109"/>
     </row>
-    <row r="42" ht="24" customHeight="1" spans="1:7">
+    <row r="42" s="107" customFormat="1" ht="24" customHeight="1" spans="1:7">
       <c r="A42" s="164"/>
       <c r="B42" s="167"/>
       <c r="E42" s="114"/>
       <c r="G42" s="109"/>
     </row>
-    <row r="43" ht="24" customHeight="1" spans="1:7">
+    <row r="43" s="107" customFormat="1" ht="24" customHeight="1" spans="1:7">
       <c r="A43" s="164"/>
       <c r="B43" s="167"/>
       <c r="E43" s="114"/>
       <c r="G43" s="109"/>
     </row>
-    <row r="44" ht="24" customHeight="1" spans="1:7">
+    <row r="44" s="107" customFormat="1" ht="24" customHeight="1" spans="1:7">
       <c r="A44" s="164"/>
       <c r="B44" s="167"/>
       <c r="E44" s="114"/>
       <c r="G44" s="109"/>
     </row>
-    <row r="45" ht="12.75" customHeight="1" spans="1:7">
+    <row r="45" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A45" s="164"/>
       <c r="B45" s="167"/>
       <c r="E45" s="114"/>
       <c r="G45" s="109"/>
     </row>
-    <row r="46" ht="12.75" customHeight="1" spans="1:7">
+    <row r="46" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A46" s="164"/>
       <c r="B46" s="167"/>
       <c r="E46" s="114"/>
       <c r="G46" s="109"/>
     </row>
-    <row r="47" ht="12.75" customHeight="1" spans="1:7">
+    <row r="47" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A47" s="164"/>
       <c r="B47" s="167"/>
       <c r="E47" s="114"/>
       <c r="G47" s="109"/>
     </row>
-    <row r="48" ht="12.75" customHeight="1" spans="1:7">
+    <row r="48" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A48" s="164"/>
       <c r="B48" s="167"/>
       <c r="E48" s="114"/>
       <c r="G48" s="109"/>
     </row>
-    <row r="49" ht="12.75" customHeight="1" spans="1:7">
+    <row r="49" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A49" s="164"/>
       <c r="B49" s="167"/>
       <c r="E49" s="114"/>
       <c r="G49" s="109"/>
     </row>
-    <row r="50" ht="12.75" customHeight="1" spans="1:7">
+    <row r="50" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A50" s="164"/>
       <c r="B50" s="167"/>
       <c r="E50" s="114"/>
       <c r="G50" s="109"/>
     </row>
-    <row r="51" ht="12.75" customHeight="1" spans="1:7">
+    <row r="51" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A51" s="164"/>
       <c r="B51" s="167"/>
       <c r="E51" s="114"/>
       <c r="G51" s="109"/>
     </row>
-    <row r="52" ht="12.75" customHeight="1" spans="1:7">
+    <row r="52" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A52" s="164"/>
       <c r="B52" s="167"/>
       <c r="E52" s="114"/>
       <c r="G52" s="109"/>
     </row>
-    <row r="53" ht="12.75" customHeight="1" spans="1:7">
+    <row r="53" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A53" s="164"/>
       <c r="B53" s="167"/>
       <c r="E53" s="114"/>
       <c r="G53" s="109"/>
     </row>
-    <row r="54" ht="12.75" customHeight="1" spans="1:7">
+    <row r="54" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A54" s="164"/>
       <c r="B54" s="167"/>
       <c r="E54" s="114"/>
       <c r="G54" s="109"/>
     </row>
-    <row r="55" ht="12.75" customHeight="1" spans="1:7">
+    <row r="55" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A55" s="164"/>
       <c r="B55" s="167"/>
       <c r="E55" s="114"/>
       <c r="G55" s="109"/>
     </row>
-    <row r="56" ht="12.75" customHeight="1" spans="1:7">
+    <row r="56" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A56" s="164"/>
       <c r="B56" s="167"/>
       <c r="E56" s="114"/>
       <c r="G56" s="109"/>
     </row>
-    <row r="57" ht="12.75" customHeight="1" spans="1:7">
+    <row r="57" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A57" s="164"/>
       <c r="B57" s="167"/>
       <c r="E57" s="114"/>
       <c r="G57" s="109"/>
     </row>
-    <row r="58" ht="12.75" customHeight="1" spans="1:7">
+    <row r="58" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A58" s="164"/>
       <c r="B58" s="167"/>
       <c r="E58" s="114"/>
       <c r="G58" s="109"/>
     </row>
-    <row r="59" ht="12.75" customHeight="1" spans="1:7">
+    <row r="59" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A59" s="164"/>
       <c r="B59" s="167"/>
       <c r="E59" s="114"/>
       <c r="G59" s="109"/>
     </row>
-    <row r="60" ht="12.75" customHeight="1" spans="1:7">
+    <row r="60" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A60" s="164"/>
       <c r="B60" s="167"/>
       <c r="E60" s="114"/>
       <c r="G60" s="109"/>
     </row>
-    <row r="61" ht="12.75" customHeight="1" spans="1:7">
+    <row r="61" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A61" s="164"/>
       <c r="B61" s="167"/>
       <c r="E61" s="114"/>
       <c r="G61" s="109"/>
     </row>
-    <row r="62" ht="12.75" customHeight="1" spans="1:7">
+    <row r="62" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A62" s="164"/>
       <c r="B62" s="167"/>
       <c r="E62" s="114"/>
       <c r="G62" s="109"/>
     </row>
-    <row r="63" ht="12.75" customHeight="1" spans="1:7">
+    <row r="63" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A63" s="164"/>
       <c r="B63" s="167"/>
       <c r="E63" s="114"/>
       <c r="G63" s="109"/>
     </row>
-    <row r="64" ht="12.75" customHeight="1" spans="1:7">
+    <row r="64" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A64" s="164"/>
       <c r="B64" s="167"/>
       <c r="E64" s="114"/>
       <c r="G64" s="109"/>
     </row>
-    <row r="65" ht="12.75" customHeight="1" spans="1:7">
+    <row r="65" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A65" s="164"/>
       <c r="B65" s="167"/>
       <c r="E65" s="114"/>
       <c r="G65" s="109"/>
     </row>
-    <row r="66" ht="12.75" customHeight="1" spans="1:7">
+    <row r="66" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A66" s="164"/>
       <c r="B66" s="167"/>
       <c r="E66" s="114"/>
       <c r="G66" s="109"/>
     </row>
-    <row r="67" ht="12.75" customHeight="1" spans="1:7">
+    <row r="67" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A67" s="164"/>
       <c r="B67" s="167"/>
       <c r="E67" s="114"/>
       <c r="G67" s="109"/>
     </row>
-    <row r="68" ht="12.75" customHeight="1" spans="1:7">
+    <row r="68" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A68" s="164"/>
       <c r="B68" s="167"/>
       <c r="E68" s="114"/>
       <c r="G68" s="109"/>
     </row>
-    <row r="69" ht="12.75" customHeight="1" spans="1:7">
+    <row r="69" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A69" s="164"/>
       <c r="B69" s="167"/>
       <c r="E69" s="114"/>
       <c r="G69" s="109"/>
     </row>
-    <row r="70" ht="12.75" customHeight="1" spans="1:7">
+    <row r="70" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A70" s="164"/>
       <c r="B70" s="167"/>
       <c r="E70" s="114"/>
       <c r="G70" s="109"/>
     </row>
-    <row r="71" ht="12.75" customHeight="1" spans="1:7">
+    <row r="71" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A71" s="164"/>
       <c r="B71" s="167"/>
       <c r="E71" s="114"/>
       <c r="G71" s="109"/>
     </row>
-    <row r="72" ht="12.75" customHeight="1" spans="1:7">
+    <row r="72" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A72" s="164"/>
       <c r="B72" s="167"/>
       <c r="E72" s="114"/>
       <c r="G72" s="109"/>
     </row>
-    <row r="73" ht="12.75" customHeight="1" spans="1:7">
+    <row r="73" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A73" s="164"/>
       <c r="B73" s="167"/>
       <c r="E73" s="114"/>
       <c r="G73" s="109"/>
     </row>
-    <row r="74" ht="12.75" customHeight="1" spans="1:7">
+    <row r="74" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A74" s="164"/>
       <c r="B74" s="167"/>
       <c r="E74" s="114"/>
       <c r="G74" s="109"/>
     </row>
-    <row r="75" ht="12.75" customHeight="1" spans="1:7">
+    <row r="75" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A75" s="164"/>
       <c r="B75" s="167"/>
       <c r="E75" s="114"/>
       <c r="G75" s="109"/>
     </row>
-    <row r="76" ht="12.75" customHeight="1" spans="1:7">
+    <row r="76" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A76" s="164"/>
       <c r="B76" s="167"/>
       <c r="E76" s="114"/>
       <c r="G76" s="109"/>
     </row>
-    <row r="77" ht="12.75" customHeight="1" spans="1:7">
+    <row r="77" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A77" s="164"/>
       <c r="B77" s="167"/>
       <c r="E77" s="114"/>
       <c r="G77" s="109"/>
     </row>
-    <row r="78" ht="12.75" customHeight="1" spans="1:7">
+    <row r="78" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A78" s="164"/>
       <c r="B78" s="167"/>
       <c r="E78" s="114"/>
       <c r="G78" s="109"/>
     </row>
-    <row r="79" ht="12.75" customHeight="1" spans="1:7">
+    <row r="79" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A79" s="164"/>
       <c r="B79" s="167"/>
       <c r="E79" s="114"/>
       <c r="G79" s="109"/>
     </row>
-    <row r="80" ht="12.75" customHeight="1" spans="1:7">
+    <row r="80" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A80" s="164"/>
       <c r="B80" s="167"/>
       <c r="E80" s="114"/>
       <c r="G80" s="109"/>
     </row>
-    <row r="81" ht="12.75" customHeight="1" spans="1:7">
+    <row r="81" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A81" s="164"/>
       <c r="B81" s="167"/>
       <c r="E81" s="114"/>
       <c r="G81" s="109"/>
     </row>
-    <row r="82" ht="12.75" customHeight="1" spans="1:7">
+    <row r="82" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A82" s="164"/>
       <c r="B82" s="167"/>
       <c r="E82" s="114"/>
       <c r="G82" s="109"/>
     </row>
-    <row r="83" ht="12.75" customHeight="1" spans="1:7">
+    <row r="83" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A83" s="164"/>
       <c r="B83" s="167"/>
       <c r="E83" s="114"/>
       <c r="G83" s="109"/>
     </row>
-    <row r="84" ht="12.75" customHeight="1" spans="1:7">
+    <row r="84" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A84" s="164"/>
       <c r="B84" s="167"/>
       <c r="E84" s="114"/>
       <c r="G84" s="109"/>
     </row>
-    <row r="85" ht="12.75" customHeight="1" spans="1:7">
+    <row r="85" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A85" s="164"/>
       <c r="B85" s="167"/>
       <c r="E85" s="114"/>
       <c r="G85" s="109"/>
     </row>
-    <row r="86" ht="12.75" customHeight="1" spans="1:7">
+    <row r="86" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A86" s="164"/>
       <c r="B86" s="167"/>
       <c r="E86" s="114"/>
       <c r="G86" s="109"/>
     </row>
-    <row r="87" ht="12.75" customHeight="1" spans="1:7">
+    <row r="87" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A87" s="164"/>
       <c r="B87" s="167"/>
       <c r="E87" s="114"/>
       <c r="G87" s="109"/>
     </row>
-    <row r="88" ht="12.75" customHeight="1" spans="1:7">
+    <row r="88" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A88" s="164"/>
       <c r="B88" s="167"/>
       <c r="E88" s="114"/>
       <c r="G88" s="109"/>
     </row>
-    <row r="89" ht="12.75" customHeight="1" spans="1:7">
+    <row r="89" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A89" s="164"/>
       <c r="B89" s="167"/>
       <c r="E89" s="114"/>
       <c r="G89" s="109"/>
     </row>
-    <row r="90" ht="12.75" customHeight="1" spans="1:7">
+    <row r="90" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A90" s="164"/>
       <c r="B90" s="167"/>
       <c r="E90" s="114"/>
       <c r="G90" s="109"/>
     </row>
-    <row r="91" ht="12.75" customHeight="1" spans="1:7">
+    <row r="91" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A91" s="164"/>
       <c r="B91" s="167"/>
       <c r="E91" s="114"/>
       <c r="G91" s="109"/>
     </row>
-    <row r="92" ht="12.75" customHeight="1" spans="1:7">
+    <row r="92" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A92" s="164"/>
       <c r="B92" s="167"/>
       <c r="E92" s="114"/>
       <c r="G92" s="109"/>
     </row>
-    <row r="93" ht="12.75" customHeight="1" spans="1:7">
+    <row r="93" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A93" s="164"/>
       <c r="B93" s="167"/>
       <c r="E93" s="114"/>
       <c r="G93" s="109"/>
     </row>
-    <row r="94" ht="12.75" customHeight="1" spans="1:7">
+    <row r="94" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A94" s="164"/>
       <c r="B94" s="167"/>
       <c r="E94" s="114"/>
       <c r="G94" s="109"/>
     </row>
-    <row r="95" ht="12.75" customHeight="1" spans="1:7">
+    <row r="95" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A95" s="164"/>
       <c r="B95" s="167"/>
       <c r="E95" s="114"/>
       <c r="G95" s="109"/>
     </row>
-    <row r="96" ht="12.75" customHeight="1" spans="1:7">
+    <row r="96" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A96" s="164"/>
       <c r="B96" s="167"/>
       <c r="E96" s="114"/>
       <c r="G96" s="109"/>
     </row>
-    <row r="97" ht="12.75" customHeight="1" spans="1:7">
+    <row r="97" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A97" s="164"/>
       <c r="B97" s="167"/>
       <c r="E97" s="114"/>
       <c r="G97" s="109"/>
     </row>
-    <row r="98" ht="12.75" customHeight="1" spans="1:7">
+    <row r="98" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A98" s="164"/>
       <c r="B98" s="167"/>
       <c r="E98" s="114"/>
       <c r="G98" s="109"/>
     </row>
-    <row r="99" ht="12.75" customHeight="1" spans="1:7">
+    <row r="99" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A99" s="164"/>
       <c r="B99" s="167"/>
       <c r="E99" s="114"/>
       <c r="G99" s="109"/>
     </row>
-    <row r="100" ht="12.75" customHeight="1" spans="1:7">
+    <row r="100" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A100" s="164"/>
       <c r="B100" s="167"/>
       <c r="E100" s="114"/>
       <c r="G100" s="109"/>
     </row>
-    <row r="101" ht="12.75" customHeight="1" spans="1:7">
+    <row r="101" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A101" s="164"/>
       <c r="B101" s="167"/>
       <c r="E101" s="114"/>
       <c r="G101" s="109"/>
     </row>
-    <row r="102" ht="12.75" customHeight="1" spans="1:7">
+    <row r="102" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A102" s="164"/>
       <c r="B102" s="167"/>
       <c r="E102" s="114"/>
       <c r="G102" s="109"/>
     </row>
-    <row r="103" ht="12.75" customHeight="1" spans="1:7">
+    <row r="103" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A103" s="164"/>
       <c r="B103" s="167"/>
       <c r="E103" s="114"/>
       <c r="G103" s="109"/>
     </row>
-    <row r="104" ht="12.75" customHeight="1" spans="1:7">
+    <row r="104" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A104" s="164"/>
       <c r="B104" s="167"/>
       <c r="E104" s="114"/>
       <c r="G104" s="109"/>
     </row>
-    <row r="105" ht="12.75" customHeight="1" spans="1:7">
+    <row r="105" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A105" s="164"/>
       <c r="B105" s="167"/>
       <c r="E105" s="114"/>
       <c r="G105" s="109"/>
     </row>
-    <row r="106" ht="12.75" customHeight="1" spans="1:7">
+    <row r="106" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A106" s="164"/>
       <c r="B106" s="167"/>
       <c r="E106" s="114"/>
       <c r="G106" s="109"/>
     </row>
-    <row r="107" ht="12.75" customHeight="1" spans="1:7">
+    <row r="107" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A107" s="164"/>
       <c r="B107" s="167"/>
       <c r="E107" s="114"/>
       <c r="G107" s="109"/>
     </row>
-    <row r="108" ht="12.75" customHeight="1" spans="1:7">
+    <row r="108" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A108" s="164"/>
       <c r="B108" s="167"/>
       <c r="E108" s="114"/>
       <c r="G108" s="109"/>
     </row>
-    <row r="109" ht="12.75" customHeight="1" spans="1:7">
+    <row r="109" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A109" s="164"/>
       <c r="B109" s="167"/>
       <c r="E109" s="114"/>
       <c r="G109" s="109"/>
     </row>
-    <row r="110" ht="12.75" customHeight="1" spans="1:7">
+    <row r="110" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A110" s="164"/>
       <c r="B110" s="167"/>
       <c r="E110" s="114"/>
       <c r="G110" s="109"/>
     </row>
-    <row r="111" ht="12.75" customHeight="1" spans="1:7">
+    <row r="111" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A111" s="164"/>
       <c r="B111" s="167"/>
       <c r="E111" s="114"/>
       <c r="G111" s="109"/>
     </row>
-    <row r="112" ht="12.75" customHeight="1" spans="1:7">
+    <row r="112" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A112" s="164"/>
       <c r="B112" s="167"/>
       <c r="E112" s="114"/>
       <c r="G112" s="109"/>
     </row>
-    <row r="113" ht="12.75" customHeight="1" spans="1:7">
+    <row r="113" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A113" s="164"/>
       <c r="B113" s="167"/>
       <c r="E113" s="114"/>
       <c r="G113" s="109"/>
     </row>
-    <row r="114" ht="12.75" customHeight="1" spans="1:7">
+    <row r="114" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A114" s="164"/>
       <c r="B114" s="167"/>
       <c r="E114" s="114"/>
       <c r="G114" s="109"/>
     </row>
-    <row r="115" ht="12.75" customHeight="1" spans="1:7">
+    <row r="115" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A115" s="164"/>
       <c r="B115" s="167"/>
       <c r="E115" s="114"/>
       <c r="G115" s="109"/>
     </row>
-    <row r="116" ht="12.75" customHeight="1" spans="1:7">
+    <row r="116" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A116" s="164"/>
       <c r="B116" s="167"/>
       <c r="E116" s="114"/>
       <c r="G116" s="109"/>
     </row>
-    <row r="117" ht="12.75" customHeight="1" spans="1:7">
+    <row r="117" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A117" s="164"/>
       <c r="B117" s="167"/>
       <c r="E117" s="114"/>
       <c r="G117" s="109"/>
     </row>
-    <row r="118" ht="12.75" customHeight="1" spans="1:7">
+    <row r="118" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A118" s="164"/>
       <c r="B118" s="167"/>
       <c r="E118" s="114"/>
       <c r="G118" s="109"/>
     </row>
-    <row r="119" ht="12.75" customHeight="1" spans="1:7">
+    <row r="119" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A119" s="164"/>
       <c r="B119" s="167"/>
       <c r="E119" s="114"/>
       <c r="G119" s="109"/>
     </row>
-    <row r="120" ht="12.75" customHeight="1" spans="1:7">
+    <row r="120" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A120" s="164"/>
       <c r="B120" s="167"/>
       <c r="E120" s="114"/>
       <c r="G120" s="109"/>
     </row>
-    <row r="121" ht="12.75" customHeight="1" spans="1:7">
+    <row r="121" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A121" s="164"/>
       <c r="B121" s="167"/>
       <c r="E121" s="114"/>
       <c r="G121" s="109"/>
     </row>
-    <row r="122" ht="12.75" customHeight="1" spans="1:7">
+    <row r="122" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A122" s="164"/>
       <c r="B122" s="167"/>
       <c r="E122" s="114"/>
       <c r="G122" s="109"/>
     </row>
-    <row r="123" ht="12.75" customHeight="1" spans="1:7">
+    <row r="123" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A123" s="164"/>
       <c r="B123" s="167"/>
       <c r="E123" s="114"/>
       <c r="G123" s="109"/>
     </row>
-    <row r="124" ht="12.75" customHeight="1" spans="1:7">
+    <row r="124" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A124" s="164"/>
       <c r="B124" s="167"/>
       <c r="E124" s="114"/>
       <c r="G124" s="109"/>
     </row>
-    <row r="125" ht="12.75" customHeight="1" spans="1:7">
+    <row r="125" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A125" s="164"/>
       <c r="B125" s="167"/>
       <c r="E125" s="114"/>
       <c r="G125" s="109"/>
     </row>
-    <row r="126" ht="12.75" customHeight="1" spans="1:7">
+    <row r="126" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A126" s="164"/>
       <c r="B126" s="167"/>
       <c r="E126" s="114"/>
       <c r="G126" s="109"/>
     </row>
-    <row r="127" ht="12.75" customHeight="1" spans="1:7">
+    <row r="127" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A127" s="164"/>
       <c r="B127" s="167"/>
       <c r="E127" s="114"/>
       <c r="G127" s="109"/>
     </row>
-    <row r="128" ht="12.75" customHeight="1" spans="1:7">
+    <row r="128" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A128" s="164"/>
       <c r="B128" s="167"/>
       <c r="E128" s="114"/>
       <c r="G128" s="109"/>
     </row>
-    <row r="129" ht="12.75" customHeight="1" spans="1:7">
+    <row r="129" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A129" s="164"/>
       <c r="B129" s="167"/>
       <c r="E129" s="114"/>
       <c r="G129" s="109"/>
     </row>
-    <row r="130" ht="12.75" customHeight="1" spans="1:7">
+    <row r="130" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A130" s="164"/>
       <c r="B130" s="167"/>
       <c r="E130" s="114"/>
       <c r="G130" s="109"/>
     </row>
-    <row r="131" ht="12.75" customHeight="1" spans="1:7">
+    <row r="131" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A131" s="164"/>
       <c r="B131" s="167"/>
       <c r="E131" s="114"/>
       <c r="G131" s="109"/>
     </row>
-    <row r="132" ht="12.75" customHeight="1" spans="1:7">
+    <row r="132" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A132" s="164"/>
       <c r="B132" s="167"/>
       <c r="E132" s="114"/>
       <c r="G132" s="109"/>
     </row>
-    <row r="133" ht="12.75" customHeight="1" spans="1:7">
+    <row r="133" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A133" s="164"/>
       <c r="B133" s="167"/>
       <c r="E133" s="114"/>
       <c r="G133" s="109"/>
     </row>
-    <row r="134" ht="12.75" customHeight="1" spans="1:7">
+    <row r="134" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A134" s="164"/>
       <c r="B134" s="167"/>
       <c r="E134" s="114"/>
       <c r="G134" s="109"/>
     </row>
-    <row r="135" ht="12.75" customHeight="1" spans="1:7">
+    <row r="135" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A135" s="164"/>
       <c r="B135" s="167"/>
       <c r="E135" s="114"/>
       <c r="G135" s="109"/>
     </row>
-    <row r="136" ht="12.75" customHeight="1" spans="1:7">
+    <row r="136" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A136" s="164"/>
       <c r="B136" s="167"/>
       <c r="E136" s="114"/>
       <c r="G136" s="109"/>
     </row>
-    <row r="137" ht="12.75" customHeight="1" spans="1:7">
+    <row r="137" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A137" s="164"/>
       <c r="B137" s="167"/>
       <c r="E137" s="114"/>
       <c r="G137" s="109"/>
     </row>
-    <row r="138" ht="12.75" customHeight="1" spans="1:7">
+    <row r="138" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A138" s="164"/>
       <c r="B138" s="167"/>
       <c r="E138" s="114"/>
       <c r="G138" s="109"/>
     </row>
-    <row r="139" ht="12.75" customHeight="1" spans="1:7">
+    <row r="139" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A139" s="164"/>
       <c r="B139" s="167"/>
       <c r="E139" s="114"/>
       <c r="G139" s="109"/>
     </row>
-    <row r="140" ht="12.75" customHeight="1" spans="1:7">
+    <row r="140" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A140" s="164"/>
       <c r="B140" s="167"/>
       <c r="E140" s="114"/>
       <c r="G140" s="109"/>
     </row>
-    <row r="141" ht="12.75" customHeight="1" spans="1:7">
+    <row r="141" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A141" s="164"/>
       <c r="B141" s="167"/>
       <c r="E141" s="114"/>
       <c r="G141" s="109"/>
     </row>
-    <row r="142" ht="12.75" customHeight="1" spans="1:7">
+    <row r="142" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A142" s="164"/>
       <c r="B142" s="167"/>
       <c r="E142" s="114"/>
       <c r="G142" s="109"/>
     </row>
-    <row r="143" ht="12.75" customHeight="1" spans="1:7">
+    <row r="143" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A143" s="164"/>
       <c r="B143" s="167"/>
       <c r="E143" s="114"/>
       <c r="G143" s="109"/>
     </row>
-    <row r="144" ht="12.75" customHeight="1" spans="1:7">
+    <row r="144" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A144" s="164"/>
       <c r="B144" s="167"/>
       <c r="E144" s="114"/>
       <c r="G144" s="109"/>
     </row>
-    <row r="145" ht="12.75" customHeight="1" spans="1:7">
+    <row r="145" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A145" s="164"/>
       <c r="B145" s="167"/>
       <c r="E145" s="114"/>
       <c r="G145" s="109"/>
     </row>
-    <row r="146" ht="12.75" customHeight="1" spans="1:7">
+    <row r="146" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A146" s="164"/>
       <c r="B146" s="167"/>
       <c r="E146" s="114"/>
       <c r="G146" s="109"/>
     </row>
-    <row r="147" ht="12.75" customHeight="1" spans="1:7">
+    <row r="147" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A147" s="164"/>
       <c r="B147" s="167"/>
       <c r="E147" s="114"/>
       <c r="G147" s="109"/>
     </row>
-    <row r="148" ht="12.75" customHeight="1" spans="1:7">
+    <row r="148" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A148" s="164"/>
       <c r="B148" s="167"/>
       <c r="E148" s="114"/>
       <c r="G148" s="109"/>
     </row>
-    <row r="149" ht="12.75" customHeight="1" spans="1:7">
+    <row r="149" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A149" s="164"/>
       <c r="B149" s="167"/>
       <c r="E149" s="114"/>
       <c r="G149" s="109"/>
     </row>
-    <row r="150" ht="12.75" customHeight="1" spans="1:7">
+    <row r="150" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A150" s="164"/>
       <c r="B150" s="167"/>
       <c r="E150" s="114"/>
       <c r="G150" s="109"/>
     </row>
-    <row r="151" ht="12.75" customHeight="1" spans="1:7">
+    <row r="151" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A151" s="164"/>
       <c r="B151" s="167"/>
       <c r="E151" s="114"/>
       <c r="G151" s="109"/>
     </row>
-    <row r="152" ht="12.75" customHeight="1" spans="1:7">
+    <row r="152" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A152" s="164"/>
       <c r="B152" s="167"/>
       <c r="E152" s="114"/>
       <c r="G152" s="109"/>
     </row>
-    <row r="153" ht="12.75" customHeight="1" spans="1:7">
+    <row r="153" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A153" s="164"/>
       <c r="B153" s="167"/>
       <c r="E153" s="114"/>
       <c r="G153" s="109"/>
     </row>
-    <row r="154" ht="12.75" customHeight="1" spans="1:7">
+    <row r="154" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A154" s="164"/>
       <c r="B154" s="167"/>
       <c r="E154" s="114"/>
       <c r="G154" s="109"/>
     </row>
-    <row r="155" ht="12.75" customHeight="1" spans="1:7">
+    <row r="155" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A155" s="164"/>
       <c r="B155" s="167"/>
       <c r="E155" s="114"/>
       <c r="G155" s="109"/>
     </row>
-    <row r="156" ht="12.75" customHeight="1" spans="1:7">
+    <row r="156" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A156" s="164"/>
       <c r="B156" s="167"/>
       <c r="E156" s="114"/>
       <c r="G156" s="109"/>
     </row>
-    <row r="157" ht="12.75" customHeight="1" spans="1:7">
+    <row r="157" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A157" s="164"/>
       <c r="B157" s="167"/>
       <c r="E157" s="114"/>
       <c r="G157" s="109"/>
     </row>
-    <row r="158" ht="12.75" customHeight="1" spans="1:7">
+    <row r="158" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A158" s="164"/>
       <c r="B158" s="167"/>
       <c r="E158" s="114"/>
       <c r="G158" s="109"/>
     </row>
-    <row r="159" ht="12.75" customHeight="1" spans="1:7">
+    <row r="159" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A159" s="164"/>
       <c r="B159" s="167"/>
       <c r="E159" s="114"/>
       <c r="G159" s="109"/>
     </row>
-    <row r="160" ht="12.75" customHeight="1" spans="1:7">
+    <row r="160" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A160" s="164"/>
       <c r="B160" s="167"/>
       <c r="E160" s="114"/>
       <c r="G160" s="109"/>
     </row>
-    <row r="161" ht="12.75" customHeight="1" spans="1:7">
+    <row r="161" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A161" s="164"/>
       <c r="B161" s="167"/>
       <c r="E161" s="114"/>
       <c r="G161" s="109"/>
     </row>
-    <row r="162" ht="12.75" customHeight="1" spans="1:7">
+    <row r="162" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A162" s="164"/>
       <c r="B162" s="167"/>
       <c r="E162" s="114"/>
       <c r="G162" s="109"/>
     </row>
-    <row r="163" ht="12.75" customHeight="1" spans="1:7">
+    <row r="163" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A163" s="164"/>
       <c r="B163" s="167"/>
       <c r="E163" s="114"/>
       <c r="G163" s="109"/>
     </row>
-    <row r="164" ht="12.75" customHeight="1" spans="1:7">
+    <row r="164" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A164" s="164"/>
       <c r="B164" s="167"/>
       <c r="E164" s="114"/>
       <c r="G164" s="109"/>
     </row>
-    <row r="165" ht="12.75" customHeight="1" spans="1:7">
+    <row r="165" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A165" s="164"/>
       <c r="B165" s="167"/>
       <c r="E165" s="114"/>
       <c r="G165" s="109"/>
     </row>
-    <row r="166" ht="12.75" customHeight="1" spans="1:7">
+    <row r="166" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A166" s="164"/>
       <c r="B166" s="167"/>
       <c r="E166" s="114"/>
       <c r="G166" s="109"/>
     </row>
-    <row r="167" ht="12.75" customHeight="1" spans="1:7">
+    <row r="167" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A167" s="164"/>
       <c r="B167" s="167"/>
       <c r="E167" s="114"/>
       <c r="G167" s="109"/>
     </row>
-    <row r="168" ht="12.75" customHeight="1" spans="1:7">
+    <row r="168" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A168" s="164"/>
       <c r="B168" s="167"/>
       <c r="E168" s="114"/>
       <c r="G168" s="109"/>
     </row>
-    <row r="169" ht="12.75" customHeight="1" spans="1:7">
+    <row r="169" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A169" s="164"/>
       <c r="B169" s="167"/>
       <c r="E169" s="114"/>
       <c r="G169" s="109"/>
     </row>
-    <row r="170" ht="12.75" customHeight="1" spans="1:7">
+    <row r="170" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A170" s="164"/>
       <c r="B170" s="167"/>
       <c r="E170" s="114"/>
       <c r="G170" s="109"/>
     </row>
-    <row r="171" ht="12.75" customHeight="1" spans="1:7">
+    <row r="171" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A171" s="164"/>
       <c r="B171" s="167"/>
       <c r="E171" s="114"/>
       <c r="G171" s="109"/>
     </row>
-    <row r="172" ht="12.75" customHeight="1" spans="1:7">
+    <row r="172" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A172" s="164"/>
       <c r="B172" s="167"/>
       <c r="E172" s="114"/>
       <c r="G172" s="109"/>
     </row>
-    <row r="173" ht="12.75" customHeight="1" spans="1:7">
+    <row r="173" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A173" s="164"/>
       <c r="B173" s="167"/>
       <c r="E173" s="114"/>
       <c r="G173" s="109"/>
     </row>
-    <row r="174" ht="12.75" customHeight="1" spans="1:7">
+    <row r="174" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A174" s="164"/>
       <c r="B174" s="167"/>
       <c r="E174" s="114"/>
       <c r="G174" s="109"/>
     </row>
-    <row r="175" ht="12.75" customHeight="1" spans="1:7">
+    <row r="175" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A175" s="164"/>
       <c r="B175" s="167"/>
       <c r="E175" s="114"/>
       <c r="G175" s="109"/>
     </row>
-    <row r="176" ht="12.75" customHeight="1" spans="1:7">
+    <row r="176" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A176" s="164"/>
       <c r="B176" s="167"/>
       <c r="E176" s="114"/>
       <c r="G176" s="109"/>
     </row>
-    <row r="177" ht="12.75" customHeight="1" spans="1:7">
+    <row r="177" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A177" s="164"/>
       <c r="B177" s="167"/>
       <c r="E177" s="114"/>
       <c r="G177" s="109"/>
     </row>
-    <row r="178" ht="12.75" customHeight="1" spans="1:7">
+    <row r="178" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A178" s="164"/>
       <c r="B178" s="167"/>
       <c r="E178" s="114"/>
       <c r="G178" s="109"/>
     </row>
-    <row r="179" ht="12.75" customHeight="1" spans="1:7">
+    <row r="179" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A179" s="164"/>
       <c r="B179" s="167"/>
       <c r="E179" s="114"/>
       <c r="G179" s="109"/>
     </row>
-    <row r="180" ht="12.75" customHeight="1" spans="1:7">
+    <row r="180" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A180" s="164"/>
       <c r="B180" s="167"/>
       <c r="E180" s="114"/>
       <c r="G180" s="109"/>
     </row>
-    <row r="181" ht="12.75" customHeight="1" spans="1:7">
+    <row r="181" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A181" s="164"/>
       <c r="B181" s="167"/>
       <c r="E181" s="114"/>
       <c r="G181" s="109"/>
     </row>
-    <row r="182" ht="12.75" customHeight="1" spans="1:7">
+    <row r="182" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A182" s="164"/>
       <c r="B182" s="167"/>
       <c r="E182" s="114"/>
       <c r="G182" s="109"/>
     </row>
-    <row r="183" ht="12.75" customHeight="1" spans="1:7">
+    <row r="183" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A183" s="164"/>
       <c r="B183" s="167"/>
       <c r="E183" s="114"/>
       <c r="G183" s="109"/>
     </row>
-    <row r="184" ht="12.75" customHeight="1" spans="1:7">
+    <row r="184" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A184" s="164"/>
       <c r="B184" s="167"/>
       <c r="E184" s="114"/>
       <c r="G184" s="109"/>
     </row>
-    <row r="185" ht="12.75" customHeight="1" spans="1:7">
+    <row r="185" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A185" s="164"/>
       <c r="B185" s="167"/>
       <c r="E185" s="114"/>
       <c r="G185" s="109"/>
     </row>
-    <row r="186" ht="12.75" customHeight="1" spans="1:7">
+    <row r="186" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A186" s="164"/>
       <c r="B186" s="167"/>
       <c r="E186" s="114"/>
       <c r="G186" s="109"/>
     </row>
-    <row r="187" ht="12.75" customHeight="1" spans="1:7">
+    <row r="187" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A187" s="164"/>
       <c r="B187" s="167"/>
       <c r="E187" s="114"/>
       <c r="G187" s="109"/>
     </row>
-    <row r="188" ht="12.75" customHeight="1" spans="1:7">
+    <row r="188" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A188" s="164"/>
       <c r="B188" s="167"/>
       <c r="E188" s="114"/>
       <c r="G188" s="109"/>
     </row>
-    <row r="189" ht="12.75" customHeight="1" spans="1:7">
+    <row r="189" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A189" s="164"/>
       <c r="B189" s="167"/>
       <c r="E189" s="114"/>
       <c r="G189" s="109"/>
     </row>
-    <row r="190" ht="12.75" customHeight="1" spans="1:7">
+    <row r="190" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A190" s="164"/>
       <c r="B190" s="167"/>
       <c r="E190" s="114"/>
       <c r="G190" s="109"/>
     </row>
-    <row r="191" ht="12.75" customHeight="1" spans="1:7">
+    <row r="191" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A191" s="164"/>
       <c r="B191" s="167"/>
       <c r="E191" s="114"/>
       <c r="G191" s="109"/>
     </row>
-    <row r="192" ht="12.75" customHeight="1" spans="1:7">
+    <row r="192" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A192" s="164"/>
       <c r="B192" s="167"/>
       <c r="E192" s="114"/>
       <c r="G192" s="109"/>
     </row>
-    <row r="193" ht="12.75" customHeight="1" spans="1:7">
+    <row r="193" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A193" s="164"/>
       <c r="B193" s="167"/>
       <c r="E193" s="114"/>
       <c r="G193" s="109"/>
     </row>
-    <row r="194" ht="12.75" customHeight="1" spans="1:7">
+    <row r="194" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A194" s="164"/>
       <c r="B194" s="167"/>
       <c r="E194" s="114"/>
       <c r="G194" s="109"/>
     </row>
-    <row r="195" ht="12.75" customHeight="1" spans="1:7">
+    <row r="195" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A195" s="164"/>
       <c r="B195" s="167"/>
       <c r="E195" s="114"/>
       <c r="G195" s="109"/>
     </row>
-    <row r="196" ht="12.75" customHeight="1" spans="1:7">
+    <row r="196" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A196" s="164"/>
       <c r="B196" s="167"/>
       <c r="E196" s="114"/>
       <c r="G196" s="109"/>
     </row>
-    <row r="197" ht="12.75" customHeight="1" spans="1:7">
+    <row r="197" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A197" s="164"/>
       <c r="B197" s="167"/>
       <c r="E197" s="114"/>
       <c r="G197" s="109"/>
     </row>
-    <row r="198" ht="12.75" customHeight="1" spans="1:7">
+    <row r="198" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A198" s="164"/>
       <c r="B198" s="167"/>
       <c r="E198" s="114"/>
       <c r="G198" s="109"/>
     </row>
-    <row r="199" ht="12.75" customHeight="1" spans="1:7">
+    <row r="199" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A199" s="164"/>
       <c r="B199" s="167"/>
       <c r="E199" s="114"/>
       <c r="G199" s="109"/>
     </row>
-    <row r="200" ht="12.75" customHeight="1" spans="1:7">
+    <row r="200" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A200" s="164"/>
       <c r="B200" s="167"/>
       <c r="E200" s="114"/>
       <c r="G200" s="109"/>
     </row>
-    <row r="201" ht="12.75" customHeight="1" spans="1:7">
+    <row r="201" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A201" s="164"/>
       <c r="B201" s="167"/>
       <c r="E201" s="114"/>
       <c r="G201" s="109"/>
     </row>
-    <row r="202" ht="12.75" customHeight="1" spans="1:7">
+    <row r="202" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A202" s="164"/>
       <c r="B202" s="167"/>
       <c r="E202" s="114"/>
       <c r="G202" s="109"/>
     </row>
-    <row r="203" ht="12.75" customHeight="1" spans="1:7">
+    <row r="203" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A203" s="164"/>
       <c r="B203" s="167"/>
       <c r="E203" s="114"/>
       <c r="G203" s="109"/>
     </row>
-    <row r="204" ht="12.75" customHeight="1" spans="1:7">
+    <row r="204" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A204" s="164"/>
       <c r="B204" s="167"/>
       <c r="E204" s="114"/>
       <c r="G204" s="109"/>
     </row>
-    <row r="205" ht="12.75" customHeight="1" spans="1:7">
+    <row r="205" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A205" s="164"/>
       <c r="B205" s="167"/>
       <c r="E205" s="114"/>
       <c r="G205" s="109"/>
     </row>
-    <row r="206" ht="12.75" customHeight="1" spans="1:7">
+    <row r="206" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A206" s="164"/>
       <c r="B206" s="167"/>
       <c r="E206" s="114"/>
       <c r="G206" s="109"/>
     </row>
-    <row r="207" ht="12.75" customHeight="1" spans="1:7">
+    <row r="207" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A207" s="164"/>
       <c r="B207" s="167"/>
       <c r="E207" s="114"/>
       <c r="G207" s="109"/>
     </row>
-    <row r="208" ht="12.75" customHeight="1" spans="1:7">
+    <row r="208" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A208" s="164"/>
       <c r="B208" s="167"/>
       <c r="E208" s="114"/>
       <c r="G208" s="109"/>
     </row>
-    <row r="209" ht="12.75" customHeight="1" spans="1:7">
+    <row r="209" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A209" s="164"/>
       <c r="B209" s="167"/>
       <c r="E209" s="114"/>
       <c r="G209" s="109"/>
     </row>
-    <row r="210" ht="12.75" customHeight="1" spans="1:7">
+    <row r="210" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A210" s="164"/>
       <c r="B210" s="167"/>
       <c r="E210" s="114"/>
       <c r="G210" s="109"/>
     </row>
-    <row r="211" ht="12.75" customHeight="1" spans="1:7">
+    <row r="211" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A211" s="164"/>
       <c r="B211" s="167"/>
       <c r="E211" s="114"/>
       <c r="G211" s="109"/>
     </row>
-    <row r="212" ht="12.75" customHeight="1" spans="1:7">
+    <row r="212" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A212" s="164"/>
       <c r="B212" s="167"/>
       <c r="E212" s="114"/>
       <c r="G212" s="109"/>
     </row>
-    <row r="213" ht="12.75" customHeight="1" spans="1:7">
+    <row r="213" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A213" s="164"/>
       <c r="B213" s="167"/>
       <c r="E213" s="114"/>
       <c r="G213" s="109"/>
     </row>
-    <row r="214" ht="12.75" customHeight="1" spans="1:7">
+    <row r="214" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A214" s="164"/>
       <c r="B214" s="167"/>
       <c r="E214" s="114"/>
       <c r="G214" s="109"/>
     </row>
-    <row r="215" ht="12.75" customHeight="1" spans="1:7">
+    <row r="215" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A215" s="164"/>
       <c r="B215" s="167"/>
       <c r="E215" s="114"/>
       <c r="G215" s="109"/>
     </row>
-    <row r="216" ht="12.75" customHeight="1" spans="1:7">
+    <row r="216" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A216" s="164"/>
       <c r="B216" s="167"/>
       <c r="E216" s="114"/>
       <c r="G216" s="109"/>
     </row>
-    <row r="217" ht="12.75" customHeight="1" spans="1:7">
+    <row r="217" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A217" s="164"/>
       <c r="B217" s="167"/>
       <c r="E217" s="114"/>
       <c r="G217" s="109"/>
     </row>
-    <row r="218" ht="12.75" customHeight="1" spans="1:7">
+    <row r="218" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A218" s="164"/>
       <c r="B218" s="167"/>
       <c r="E218" s="114"/>
       <c r="G218" s="109"/>
     </row>
-    <row r="219" ht="12.75" customHeight="1" spans="1:7">
+    <row r="219" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A219" s="164"/>
       <c r="B219" s="167"/>
       <c r="E219" s="114"/>
       <c r="G219" s="109"/>
     </row>
-    <row r="220" ht="12.75" customHeight="1" spans="1:7">
+    <row r="220" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A220" s="164"/>
       <c r="B220" s="167"/>
       <c r="E220" s="114"/>
       <c r="G220" s="109"/>
     </row>
-    <row r="221" ht="12.75" customHeight="1" spans="1:7">
+    <row r="221" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A221" s="164"/>
       <c r="B221" s="167"/>
       <c r="E221" s="114"/>
       <c r="G221" s="109"/>
     </row>
-    <row r="222" ht="12.75" customHeight="1" spans="1:7">
+    <row r="222" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A222" s="164"/>
       <c r="B222" s="167"/>
       <c r="E222" s="114"/>
       <c r="G222" s="109"/>
     </row>
-    <row r="223" ht="12.75" customHeight="1" spans="1:7">
+    <row r="223" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A223" s="164"/>
       <c r="B223" s="167"/>
       <c r="E223" s="114"/>
       <c r="G223" s="109"/>
     </row>
-    <row r="224" ht="12.75" customHeight="1" spans="1:7">
+    <row r="224" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A224" s="164"/>
       <c r="B224" s="167"/>
       <c r="E224" s="114"/>
       <c r="G224" s="109"/>
     </row>
-    <row r="225" ht="12.75" customHeight="1" spans="1:7">
+    <row r="225" s="107" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A225" s="164"/>
       <c r="B225" s="167"/>
       <c r="E225" s="114"/>
       <c r="G225" s="109"/>
     </row>
-    <row r="226" ht="15.75" customHeight="1" spans="5:5">
+    <row r="226" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B226" s="109"/>
       <c r="E226" s="114"/>
     </row>
-    <row r="227" ht="15.75" customHeight="1" spans="5:5">
+    <row r="227" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B227" s="109"/>
       <c r="E227" s="114"/>
     </row>
-    <row r="228" ht="15.75" customHeight="1" spans="5:5">
+    <row r="228" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B228" s="109"/>
       <c r="E228" s="114"/>
     </row>
-    <row r="229" ht="15.75" customHeight="1" spans="5:5">
+    <row r="229" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B229" s="109"/>
       <c r="E229" s="114"/>
     </row>
-    <row r="230" ht="15.75" customHeight="1" spans="5:5">
+    <row r="230" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B230" s="109"/>
       <c r="E230" s="114"/>
     </row>
-    <row r="231" ht="15.75" customHeight="1" spans="5:5">
+    <row r="231" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B231" s="109"/>
       <c r="E231" s="114"/>
     </row>
-    <row r="232" ht="15.75" customHeight="1" spans="5:5">
+    <row r="232" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B232" s="109"/>
       <c r="E232" s="114"/>
     </row>
-    <row r="233" ht="15.75" customHeight="1" spans="5:5">
+    <row r="233" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B233" s="109"/>
       <c r="E233" s="114"/>
     </row>
-    <row r="234" ht="15.75" customHeight="1" spans="5:5">
+    <row r="234" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B234" s="109"/>
       <c r="E234" s="114"/>
     </row>
-    <row r="235" ht="15.75" customHeight="1" spans="5:5">
+    <row r="235" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B235" s="109"/>
       <c r="E235" s="114"/>
     </row>
-    <row r="236" ht="15.75" customHeight="1" spans="5:5">
+    <row r="236" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B236" s="109"/>
       <c r="E236" s="114"/>
     </row>
-    <row r="237" ht="15.75" customHeight="1" spans="5:5">
+    <row r="237" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B237" s="109"/>
       <c r="E237" s="114"/>
     </row>
-    <row r="238" ht="15.75" customHeight="1" spans="5:5">
+    <row r="238" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B238" s="109"/>
       <c r="E238" s="114"/>
     </row>
-    <row r="239" ht="15.75" customHeight="1" spans="5:5">
+    <row r="239" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B239" s="109"/>
       <c r="E239" s="114"/>
     </row>
-    <row r="240" ht="15.75" customHeight="1" spans="5:5">
+    <row r="240" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B240" s="109"/>
       <c r="E240" s="114"/>
     </row>
-    <row r="241" ht="15.75" customHeight="1" spans="5:5">
+    <row r="241" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B241" s="109"/>
       <c r="E241" s="114"/>
     </row>
-    <row r="242" ht="15.75" customHeight="1" spans="5:5">
+    <row r="242" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B242" s="109"/>
       <c r="E242" s="114"/>
     </row>
-    <row r="243" ht="15.75" customHeight="1" spans="5:5">
+    <row r="243" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B243" s="109"/>
       <c r="E243" s="114"/>
     </row>
-    <row r="244" ht="15.75" customHeight="1" spans="5:5">
+    <row r="244" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B244" s="109"/>
       <c r="E244" s="114"/>
     </row>
-    <row r="245" ht="15.75" customHeight="1" spans="5:5">
+    <row r="245" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B245" s="109"/>
       <c r="E245" s="114"/>
     </row>
-    <row r="246" ht="15.75" customHeight="1" spans="5:5">
+    <row r="246" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B246" s="109"/>
       <c r="E246" s="114"/>
     </row>
-    <row r="247" ht="15.75" customHeight="1" spans="5:5">
+    <row r="247" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B247" s="109"/>
       <c r="E247" s="114"/>
     </row>
-    <row r="248" ht="15.75" customHeight="1" spans="5:5">
+    <row r="248" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B248" s="109"/>
       <c r="E248" s="114"/>
     </row>
-    <row r="249" ht="15.75" customHeight="1" spans="5:5">
+    <row r="249" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B249" s="109"/>
       <c r="E249" s="114"/>
     </row>
-    <row r="250" ht="15.75" customHeight="1" spans="5:5">
+    <row r="250" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B250" s="109"/>
       <c r="E250" s="114"/>
     </row>
-    <row r="251" ht="15.75" customHeight="1" spans="5:5">
+    <row r="251" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B251" s="109"/>
       <c r="E251" s="114"/>
     </row>
-    <row r="252" ht="15.75" customHeight="1" spans="5:5">
+    <row r="252" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B252" s="109"/>
       <c r="E252" s="114"/>
     </row>
-    <row r="253" ht="15.75" customHeight="1" spans="5:5">
+    <row r="253" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B253" s="109"/>
       <c r="E253" s="114"/>
     </row>
-    <row r="254" ht="15.75" customHeight="1" spans="5:5">
+    <row r="254" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B254" s="109"/>
       <c r="E254" s="114"/>
     </row>
-    <row r="255" ht="15.75" customHeight="1" spans="5:5">
+    <row r="255" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B255" s="109"/>
       <c r="E255" s="114"/>
     </row>
-    <row r="256" ht="15.75" customHeight="1" spans="5:5">
+    <row r="256" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B256" s="109"/>
       <c r="E256" s="114"/>
     </row>
-    <row r="257" ht="15.75" customHeight="1" spans="5:5">
+    <row r="257" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B257" s="109"/>
       <c r="E257" s="114"/>
     </row>
-    <row r="258" ht="15.75" customHeight="1" spans="5:5">
+    <row r="258" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B258" s="109"/>
       <c r="E258" s="114"/>
     </row>
-    <row r="259" ht="15.75" customHeight="1" spans="5:5">
+    <row r="259" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B259" s="109"/>
       <c r="E259" s="114"/>
     </row>
-    <row r="260" ht="15.75" customHeight="1" spans="5:5">
+    <row r="260" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B260" s="109"/>
       <c r="E260" s="114"/>
     </row>
-    <row r="261" ht="15.75" customHeight="1" spans="5:5">
+    <row r="261" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B261" s="109"/>
       <c r="E261" s="114"/>
     </row>
-    <row r="262" ht="15.75" customHeight="1" spans="5:5">
+    <row r="262" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B262" s="109"/>
       <c r="E262" s="114"/>
     </row>
-    <row r="263" ht="15.75" customHeight="1" spans="5:5">
+    <row r="263" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B263" s="109"/>
       <c r="E263" s="114"/>
     </row>
-    <row r="264" ht="15.75" customHeight="1" spans="5:5">
+    <row r="264" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B264" s="109"/>
       <c r="E264" s="114"/>
     </row>
-    <row r="265" ht="15.75" customHeight="1" spans="5:5">
+    <row r="265" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B265" s="109"/>
       <c r="E265" s="114"/>
     </row>
-    <row r="266" ht="15.75" customHeight="1" spans="5:5">
+    <row r="266" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B266" s="109"/>
       <c r="E266" s="114"/>
     </row>
-    <row r="267" ht="15.75" customHeight="1" spans="5:5">
+    <row r="267" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B267" s="109"/>
       <c r="E267" s="114"/>
     </row>
-    <row r="268" ht="15.75" customHeight="1" spans="5:5">
+    <row r="268" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B268" s="109"/>
       <c r="E268" s="114"/>
     </row>
-    <row r="269" ht="15.75" customHeight="1" spans="5:5">
+    <row r="269" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B269" s="109"/>
       <c r="E269" s="114"/>
     </row>
-    <row r="270" ht="15.75" customHeight="1" spans="5:5">
+    <row r="270" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B270" s="109"/>
       <c r="E270" s="114"/>
     </row>
-    <row r="271" ht="15.75" customHeight="1" spans="5:5">
+    <row r="271" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B271" s="109"/>
       <c r="E271" s="114"/>
     </row>
-    <row r="272" ht="15.75" customHeight="1" spans="5:5">
+    <row r="272" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B272" s="109"/>
       <c r="E272" s="114"/>
     </row>
-    <row r="273" ht="15.75" customHeight="1" spans="5:5">
+    <row r="273" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B273" s="109"/>
       <c r="E273" s="114"/>
     </row>
-    <row r="274" ht="15.75" customHeight="1" spans="5:5">
+    <row r="274" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B274" s="109"/>
       <c r="E274" s="114"/>
     </row>
-    <row r="275" ht="15.75" customHeight="1" spans="5:5">
+    <row r="275" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B275" s="109"/>
       <c r="E275" s="114"/>
     </row>
-    <row r="276" ht="15.75" customHeight="1" spans="5:5">
+    <row r="276" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B276" s="109"/>
       <c r="E276" s="114"/>
     </row>
-    <row r="277" ht="15.75" customHeight="1" spans="5:5">
+    <row r="277" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B277" s="109"/>
       <c r="E277" s="114"/>
     </row>
-    <row r="278" ht="15.75" customHeight="1" spans="5:5">
+    <row r="278" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B278" s="109"/>
       <c r="E278" s="114"/>
     </row>
-    <row r="279" ht="15.75" customHeight="1" spans="5:5">
+    <row r="279" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B279" s="109"/>
       <c r="E279" s="114"/>
     </row>
-    <row r="280" ht="15.75" customHeight="1" spans="5:5">
+    <row r="280" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B280" s="109"/>
       <c r="E280" s="114"/>
     </row>
-    <row r="281" ht="15.75" customHeight="1" spans="5:5">
+    <row r="281" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B281" s="109"/>
       <c r="E281" s="114"/>
     </row>
-    <row r="282" ht="15.75" customHeight="1" spans="5:5">
+    <row r="282" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B282" s="109"/>
       <c r="E282" s="114"/>
     </row>
-    <row r="283" ht="15.75" customHeight="1" spans="5:5">
+    <row r="283" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B283" s="109"/>
       <c r="E283" s="114"/>
     </row>
-    <row r="284" ht="15.75" customHeight="1" spans="5:5">
+    <row r="284" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B284" s="109"/>
       <c r="E284" s="114"/>
     </row>
-    <row r="285" ht="15.75" customHeight="1" spans="5:5">
+    <row r="285" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B285" s="109"/>
       <c r="E285" s="114"/>
     </row>
-    <row r="286" ht="15.75" customHeight="1" spans="5:5">
+    <row r="286" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B286" s="109"/>
       <c r="E286" s="114"/>
     </row>
-    <row r="287" ht="15.75" customHeight="1" spans="5:5">
+    <row r="287" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B287" s="109"/>
       <c r="E287" s="114"/>
     </row>
-    <row r="288" ht="15.75" customHeight="1" spans="5:5">
+    <row r="288" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B288" s="109"/>
       <c r="E288" s="114"/>
     </row>
-    <row r="289" ht="15.75" customHeight="1" spans="5:5">
+    <row r="289" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B289" s="109"/>
       <c r="E289" s="114"/>
     </row>
-    <row r="290" ht="15.75" customHeight="1" spans="5:5">
+    <row r="290" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B290" s="109"/>
       <c r="E290" s="114"/>
     </row>
-    <row r="291" ht="15.75" customHeight="1" spans="5:5">
+    <row r="291" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B291" s="109"/>
       <c r="E291" s="114"/>
     </row>
-    <row r="292" ht="15.75" customHeight="1" spans="5:5">
+    <row r="292" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B292" s="109"/>
       <c r="E292" s="114"/>
     </row>
-    <row r="293" ht="15.75" customHeight="1" spans="5:5">
+    <row r="293" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B293" s="109"/>
       <c r="E293" s="114"/>
     </row>
-    <row r="294" ht="15.75" customHeight="1" spans="5:5">
+    <row r="294" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B294" s="109"/>
       <c r="E294" s="114"/>
     </row>
-    <row r="295" ht="15.75" customHeight="1" spans="5:5">
+    <row r="295" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B295" s="109"/>
       <c r="E295" s="114"/>
     </row>
-    <row r="296" ht="15.75" customHeight="1" spans="5:5">
+    <row r="296" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B296" s="109"/>
       <c r="E296" s="114"/>
     </row>
-    <row r="297" ht="15.75" customHeight="1" spans="5:5">
+    <row r="297" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B297" s="109"/>
       <c r="E297" s="114"/>
     </row>
-    <row r="298" ht="15.75" customHeight="1" spans="5:5">
+    <row r="298" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B298" s="109"/>
       <c r="E298" s="114"/>
     </row>
-    <row r="299" ht="15.75" customHeight="1" spans="5:5">
+    <row r="299" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B299" s="109"/>
       <c r="E299" s="114"/>
     </row>
-    <row r="300" ht="15.75" customHeight="1" spans="5:5">
+    <row r="300" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B300" s="109"/>
       <c r="E300" s="114"/>
     </row>
-    <row r="301" ht="15.75" customHeight="1" spans="5:5">
+    <row r="301" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B301" s="109"/>
       <c r="E301" s="114"/>
     </row>
-    <row r="302" ht="15.75" customHeight="1" spans="5:5">
+    <row r="302" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B302" s="109"/>
       <c r="E302" s="114"/>
     </row>
-    <row r="303" ht="15.75" customHeight="1" spans="5:5">
+    <row r="303" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B303" s="109"/>
       <c r="E303" s="114"/>
     </row>
-    <row r="304" ht="15.75" customHeight="1" spans="5:5">
+    <row r="304" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B304" s="109"/>
       <c r="E304" s="114"/>
     </row>
-    <row r="305" ht="15.75" customHeight="1" spans="5:5">
+    <row r="305" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B305" s="109"/>
       <c r="E305" s="114"/>
     </row>
-    <row r="306" ht="15.75" customHeight="1" spans="5:5">
+    <row r="306" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B306" s="109"/>
       <c r="E306" s="114"/>
     </row>
-    <row r="307" ht="15.75" customHeight="1" spans="5:5">
+    <row r="307" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B307" s="109"/>
       <c r="E307" s="114"/>
     </row>
-    <row r="308" ht="15.75" customHeight="1" spans="5:5">
+    <row r="308" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B308" s="109"/>
       <c r="E308" s="114"/>
     </row>
-    <row r="309" ht="15.75" customHeight="1" spans="5:5">
+    <row r="309" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B309" s="109"/>
       <c r="E309" s="114"/>
     </row>
-    <row r="310" ht="15.75" customHeight="1" spans="5:5">
+    <row r="310" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B310" s="109"/>
       <c r="E310" s="114"/>
     </row>
-    <row r="311" ht="15.75" customHeight="1" spans="5:5">
+    <row r="311" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B311" s="109"/>
       <c r="E311" s="114"/>
     </row>
-    <row r="312" ht="15.75" customHeight="1" spans="5:5">
+    <row r="312" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B312" s="109"/>
       <c r="E312" s="114"/>
     </row>
-    <row r="313" ht="15.75" customHeight="1" spans="5:5">
+    <row r="313" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B313" s="109"/>
       <c r="E313" s="114"/>
     </row>
-    <row r="314" ht="15.75" customHeight="1" spans="5:5">
+    <row r="314" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B314" s="109"/>
       <c r="E314" s="114"/>
     </row>
-    <row r="315" ht="15.75" customHeight="1" spans="5:5">
+    <row r="315" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B315" s="109"/>
       <c r="E315" s="114"/>
     </row>
-    <row r="316" ht="15.75" customHeight="1" spans="5:5">
+    <row r="316" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B316" s="109"/>
       <c r="E316" s="114"/>
     </row>
-    <row r="317" ht="15.75" customHeight="1" spans="5:5">
+    <row r="317" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B317" s="109"/>
       <c r="E317" s="114"/>
     </row>
-    <row r="318" ht="15.75" customHeight="1" spans="5:5">
+    <row r="318" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B318" s="109"/>
       <c r="E318" s="114"/>
     </row>
-    <row r="319" ht="15.75" customHeight="1" spans="5:5">
+    <row r="319" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B319" s="109"/>
       <c r="E319" s="114"/>
     </row>
-    <row r="320" ht="15.75" customHeight="1" spans="5:5">
+    <row r="320" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B320" s="109"/>
       <c r="E320" s="114"/>
     </row>
-    <row r="321" ht="15.75" customHeight="1" spans="5:5">
+    <row r="321" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B321" s="109"/>
       <c r="E321" s="114"/>
     </row>
-    <row r="322" ht="15.75" customHeight="1" spans="5:5">
+    <row r="322" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B322" s="109"/>
       <c r="E322" s="114"/>
     </row>
-    <row r="323" ht="15.75" customHeight="1" spans="5:5">
+    <row r="323" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B323" s="109"/>
       <c r="E323" s="114"/>
     </row>
-    <row r="324" ht="15.75" customHeight="1" spans="5:5">
+    <row r="324" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B324" s="109"/>
       <c r="E324" s="114"/>
     </row>
-    <row r="325" ht="15.75" customHeight="1" spans="5:5">
+    <row r="325" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B325" s="109"/>
       <c r="E325" s="114"/>
     </row>
-    <row r="326" ht="15.75" customHeight="1" spans="5:5">
+    <row r="326" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B326" s="109"/>
       <c r="E326" s="114"/>
     </row>
-    <row r="327" ht="15.75" customHeight="1" spans="5:5">
+    <row r="327" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B327" s="109"/>
       <c r="E327" s="114"/>
     </row>
-    <row r="328" ht="15.75" customHeight="1" spans="5:5">
+    <row r="328" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B328" s="109"/>
       <c r="E328" s="114"/>
     </row>
-    <row r="329" ht="15.75" customHeight="1" spans="5:5">
+    <row r="329" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B329" s="109"/>
       <c r="E329" s="114"/>
     </row>
-    <row r="330" ht="15.75" customHeight="1" spans="5:5">
+    <row r="330" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B330" s="109"/>
       <c r="E330" s="114"/>
     </row>
-    <row r="331" ht="15.75" customHeight="1" spans="5:5">
+    <row r="331" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B331" s="109"/>
       <c r="E331" s="114"/>
     </row>
-    <row r="332" ht="15.75" customHeight="1" spans="5:5">
+    <row r="332" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B332" s="109"/>
       <c r="E332" s="114"/>
     </row>
-    <row r="333" ht="15.75" customHeight="1" spans="5:5">
+    <row r="333" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B333" s="109"/>
       <c r="E333" s="114"/>
     </row>
-    <row r="334" ht="15.75" customHeight="1" spans="5:5">
+    <row r="334" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B334" s="109"/>
       <c r="E334" s="114"/>
     </row>
-    <row r="335" ht="15.75" customHeight="1" spans="5:5">
+    <row r="335" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B335" s="109"/>
       <c r="E335" s="114"/>
     </row>
-    <row r="336" ht="15.75" customHeight="1" spans="5:5">
+    <row r="336" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B336" s="109"/>
       <c r="E336" s="114"/>
     </row>
-    <row r="337" ht="15.75" customHeight="1" spans="5:5">
+    <row r="337" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B337" s="109"/>
       <c r="E337" s="114"/>
     </row>
-    <row r="338" ht="15.75" customHeight="1" spans="5:5">
+    <row r="338" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B338" s="109"/>
       <c r="E338" s="114"/>
     </row>
-    <row r="339" ht="15.75" customHeight="1" spans="5:5">
+    <row r="339" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B339" s="109"/>
       <c r="E339" s="114"/>
     </row>
-    <row r="340" ht="15.75" customHeight="1" spans="5:5">
+    <row r="340" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B340" s="109"/>
       <c r="E340" s="114"/>
     </row>
-    <row r="341" ht="15.75" customHeight="1" spans="5:5">
+    <row r="341" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B341" s="109"/>
       <c r="E341" s="114"/>
     </row>
-    <row r="342" ht="15.75" customHeight="1" spans="5:5">
+    <row r="342" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B342" s="109"/>
       <c r="E342" s="114"/>
     </row>
-    <row r="343" ht="15.75" customHeight="1" spans="5:5">
+    <row r="343" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B343" s="109"/>
       <c r="E343" s="114"/>
     </row>
-    <row r="344" ht="15.75" customHeight="1" spans="5:5">
+    <row r="344" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B344" s="109"/>
       <c r="E344" s="114"/>
     </row>
-    <row r="345" ht="15.75" customHeight="1" spans="5:5">
+    <row r="345" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B345" s="109"/>
       <c r="E345" s="114"/>
     </row>
-    <row r="346" ht="15.75" customHeight="1" spans="5:5">
+    <row r="346" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B346" s="109"/>
       <c r="E346" s="114"/>
     </row>
-    <row r="347" ht="15.75" customHeight="1" spans="5:5">
+    <row r="347" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B347" s="109"/>
       <c r="E347" s="114"/>
     </row>
-    <row r="348" ht="15.75" customHeight="1" spans="5:5">
+    <row r="348" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B348" s="109"/>
       <c r="E348" s="114"/>
     </row>
-    <row r="349" ht="15.75" customHeight="1" spans="5:5">
+    <row r="349" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B349" s="109"/>
       <c r="E349" s="114"/>
     </row>
-    <row r="350" ht="15.75" customHeight="1" spans="5:5">
+    <row r="350" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B350" s="109"/>
       <c r="E350" s="114"/>
     </row>
-    <row r="351" ht="15.75" customHeight="1" spans="5:5">
+    <row r="351" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B351" s="109"/>
       <c r="E351" s="114"/>
     </row>
-    <row r="352" ht="15.75" customHeight="1" spans="5:5">
+    <row r="352" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B352" s="109"/>
       <c r="E352" s="114"/>
     </row>
-    <row r="353" ht="15.75" customHeight="1" spans="5:5">
+    <row r="353" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B353" s="109"/>
       <c r="E353" s="114"/>
     </row>
-    <row r="354" ht="15.75" customHeight="1" spans="5:5">
+    <row r="354" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B354" s="109"/>
       <c r="E354" s="114"/>
     </row>
-    <row r="355" ht="15.75" customHeight="1" spans="5:5">
+    <row r="355" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B355" s="109"/>
       <c r="E355" s="114"/>
     </row>
-    <row r="356" ht="15.75" customHeight="1" spans="5:5">
+    <row r="356" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B356" s="109"/>
       <c r="E356" s="114"/>
     </row>
-    <row r="357" ht="15.75" customHeight="1" spans="5:5">
+    <row r="357" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B357" s="109"/>
       <c r="E357" s="114"/>
     </row>
-    <row r="358" ht="15.75" customHeight="1" spans="5:5">
+    <row r="358" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B358" s="109"/>
       <c r="E358" s="114"/>
     </row>
-    <row r="359" ht="15.75" customHeight="1" spans="5:5">
+    <row r="359" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B359" s="109"/>
       <c r="E359" s="114"/>
     </row>
-    <row r="360" ht="15.75" customHeight="1" spans="5:5">
+    <row r="360" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B360" s="109"/>
       <c r="E360" s="114"/>
     </row>
-    <row r="361" ht="15.75" customHeight="1" spans="5:5">
+    <row r="361" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B361" s="109"/>
       <c r="E361" s="114"/>
     </row>
-    <row r="362" ht="15.75" customHeight="1" spans="5:5">
+    <row r="362" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B362" s="109"/>
       <c r="E362" s="114"/>
     </row>
-    <row r="363" ht="15.75" customHeight="1" spans="5:5">
+    <row r="363" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B363" s="109"/>
       <c r="E363" s="114"/>
     </row>
-    <row r="364" ht="15.75" customHeight="1" spans="5:5">
+    <row r="364" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B364" s="109"/>
       <c r="E364" s="114"/>
     </row>
-    <row r="365" ht="15.75" customHeight="1" spans="5:5">
+    <row r="365" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B365" s="109"/>
       <c r="E365" s="114"/>
     </row>
-    <row r="366" ht="15.75" customHeight="1" spans="5:5">
+    <row r="366" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B366" s="109"/>
       <c r="E366" s="114"/>
     </row>
-    <row r="367" ht="15.75" customHeight="1" spans="5:5">
+    <row r="367" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B367" s="109"/>
       <c r="E367" s="114"/>
     </row>
-    <row r="368" ht="15.75" customHeight="1" spans="5:5">
+    <row r="368" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B368" s="109"/>
       <c r="E368" s="114"/>
     </row>
-    <row r="369" ht="15.75" customHeight="1" spans="5:5">
+    <row r="369" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B369" s="109"/>
       <c r="E369" s="114"/>
     </row>
-    <row r="370" ht="15.75" customHeight="1" spans="5:5">
+    <row r="370" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B370" s="109"/>
       <c r="E370" s="114"/>
     </row>
-    <row r="371" ht="15.75" customHeight="1" spans="5:5">
+    <row r="371" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B371" s="109"/>
       <c r="E371" s="114"/>
     </row>
-    <row r="372" ht="15.75" customHeight="1" spans="5:5">
+    <row r="372" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B372" s="109"/>
       <c r="E372" s="114"/>
     </row>
-    <row r="373" ht="15.75" customHeight="1" spans="5:5">
+    <row r="373" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B373" s="109"/>
       <c r="E373" s="114"/>
     </row>
-    <row r="374" ht="15.75" customHeight="1" spans="5:5">
+    <row r="374" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B374" s="109"/>
       <c r="E374" s="114"/>
     </row>
-    <row r="375" ht="15.75" customHeight="1" spans="5:5">
+    <row r="375" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B375" s="109"/>
       <c r="E375" s="114"/>
     </row>
-    <row r="376" ht="15.75" customHeight="1" spans="5:5">
+    <row r="376" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B376" s="109"/>
       <c r="E376" s="114"/>
     </row>
-    <row r="377" ht="15.75" customHeight="1" spans="5:5">
+    <row r="377" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B377" s="109"/>
       <c r="E377" s="114"/>
     </row>
-    <row r="378" ht="15.75" customHeight="1" spans="5:5">
+    <row r="378" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B378" s="109"/>
       <c r="E378" s="114"/>
     </row>
-    <row r="379" ht="15.75" customHeight="1" spans="5:5">
+    <row r="379" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B379" s="109"/>
       <c r="E379" s="114"/>
     </row>
-    <row r="380" ht="15.75" customHeight="1" spans="5:5">
+    <row r="380" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B380" s="109"/>
       <c r="E380" s="114"/>
     </row>
-    <row r="381" ht="15.75" customHeight="1" spans="5:5">
+    <row r="381" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B381" s="109"/>
       <c r="E381" s="114"/>
     </row>
-    <row r="382" ht="15.75" customHeight="1" spans="5:5">
+    <row r="382" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B382" s="109"/>
       <c r="E382" s="114"/>
     </row>
-    <row r="383" ht="15.75" customHeight="1" spans="5:5">
+    <row r="383" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B383" s="109"/>
       <c r="E383" s="114"/>
     </row>
-    <row r="384" ht="15.75" customHeight="1" spans="5:5">
+    <row r="384" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B384" s="109"/>
       <c r="E384" s="114"/>
     </row>
-    <row r="385" ht="15.75" customHeight="1" spans="5:5">
+    <row r="385" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B385" s="109"/>
       <c r="E385" s="114"/>
     </row>
-    <row r="386" ht="15.75" customHeight="1" spans="5:5">
+    <row r="386" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B386" s="109"/>
       <c r="E386" s="114"/>
     </row>
-    <row r="387" ht="15.75" customHeight="1" spans="5:5">
+    <row r="387" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B387" s="109"/>
       <c r="E387" s="114"/>
     </row>
-    <row r="388" ht="15.75" customHeight="1" spans="5:5">
+    <row r="388" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B388" s="109"/>
       <c r="E388" s="114"/>
     </row>
-    <row r="389" ht="15.75" customHeight="1" spans="5:5">
+    <row r="389" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B389" s="109"/>
       <c r="E389" s="114"/>
     </row>
-    <row r="390" ht="15.75" customHeight="1" spans="5:5">
+    <row r="390" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B390" s="109"/>
       <c r="E390" s="114"/>
     </row>
-    <row r="391" ht="15.75" customHeight="1" spans="5:5">
+    <row r="391" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B391" s="109"/>
       <c r="E391" s="114"/>
     </row>
-    <row r="392" ht="15.75" customHeight="1" spans="5:5">
+    <row r="392" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B392" s="109"/>
       <c r="E392" s="114"/>
     </row>
-    <row r="393" ht="15.75" customHeight="1" spans="5:5">
+    <row r="393" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B393" s="109"/>
       <c r="E393" s="114"/>
     </row>
-    <row r="394" ht="15.75" customHeight="1" spans="5:5">
+    <row r="394" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B394" s="109"/>
       <c r="E394" s="114"/>
     </row>
-    <row r="395" ht="15.75" customHeight="1" spans="5:5">
+    <row r="395" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B395" s="109"/>
       <c r="E395" s="114"/>
     </row>
-    <row r="396" ht="15.75" customHeight="1" spans="5:5">
+    <row r="396" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B396" s="109"/>
       <c r="E396" s="114"/>
     </row>
-    <row r="397" ht="15.75" customHeight="1" spans="5:5">
+    <row r="397" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B397" s="109"/>
       <c r="E397" s="114"/>
     </row>
-    <row r="398" ht="15.75" customHeight="1" spans="5:5">
+    <row r="398" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B398" s="109"/>
       <c r="E398" s="114"/>
     </row>
-    <row r="399" ht="15.75" customHeight="1" spans="5:5">
+    <row r="399" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B399" s="109"/>
       <c r="E399" s="114"/>
     </row>
-    <row r="400" ht="15.75" customHeight="1" spans="5:5">
+    <row r="400" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B400" s="109"/>
       <c r="E400" s="114"/>
     </row>
-    <row r="401" ht="15.75" customHeight="1" spans="5:5">
+    <row r="401" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B401" s="109"/>
       <c r="E401" s="114"/>
     </row>
-    <row r="402" ht="15.75" customHeight="1" spans="5:5">
+    <row r="402" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B402" s="109"/>
       <c r="E402" s="114"/>
     </row>
-    <row r="403" ht="15.75" customHeight="1" spans="5:5">
+    <row r="403" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B403" s="109"/>
       <c r="E403" s="114"/>
     </row>
-    <row r="404" ht="15.75" customHeight="1" spans="5:5">
+    <row r="404" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B404" s="109"/>
       <c r="E404" s="114"/>
     </row>
-    <row r="405" ht="15.75" customHeight="1" spans="5:5">
+    <row r="405" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B405" s="109"/>
       <c r="E405" s="114"/>
     </row>
-    <row r="406" ht="15.75" customHeight="1" spans="5:5">
+    <row r="406" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B406" s="109"/>
       <c r="E406" s="114"/>
     </row>
-    <row r="407" ht="15.75" customHeight="1" spans="5:5">
+    <row r="407" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B407" s="109"/>
       <c r="E407" s="114"/>
     </row>
-    <row r="408" ht="15.75" customHeight="1" spans="5:5">
+    <row r="408" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B408" s="109"/>
       <c r="E408" s="114"/>
     </row>
-    <row r="409" ht="15.75" customHeight="1" spans="5:5">
+    <row r="409" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B409" s="109"/>
       <c r="E409" s="114"/>
     </row>
-    <row r="410" ht="15.75" customHeight="1" spans="5:5">
+    <row r="410" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B410" s="109"/>
       <c r="E410" s="114"/>
     </row>
-    <row r="411" ht="15.75" customHeight="1" spans="5:5">
+    <row r="411" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B411" s="109"/>
       <c r="E411" s="114"/>
     </row>
-    <row r="412" ht="15.75" customHeight="1" spans="5:5">
+    <row r="412" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B412" s="109"/>
       <c r="E412" s="114"/>
     </row>
-    <row r="413" ht="15.75" customHeight="1" spans="5:5">
+    <row r="413" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B413" s="109"/>
       <c r="E413" s="114"/>
     </row>
-    <row r="414" ht="15.75" customHeight="1" spans="5:5">
+    <row r="414" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B414" s="109"/>
       <c r="E414" s="114"/>
     </row>
-    <row r="415" ht="15.75" customHeight="1" spans="5:5">
+    <row r="415" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B415" s="109"/>
       <c r="E415" s="114"/>
     </row>
-    <row r="416" ht="15.75" customHeight="1" spans="5:5">
+    <row r="416" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B416" s="109"/>
       <c r="E416" s="114"/>
     </row>
-    <row r="417" ht="15.75" customHeight="1" spans="5:5">
+    <row r="417" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B417" s="109"/>
       <c r="E417" s="114"/>
     </row>
-    <row r="418" ht="15.75" customHeight="1" spans="5:5">
+    <row r="418" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B418" s="109"/>
       <c r="E418" s="114"/>
     </row>
-    <row r="419" ht="15.75" customHeight="1" spans="5:5">
+    <row r="419" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B419" s="109"/>
       <c r="E419" s="114"/>
     </row>
-    <row r="420" ht="15.75" customHeight="1" spans="5:5">
+    <row r="420" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B420" s="109"/>
       <c r="E420" s="114"/>
     </row>
-    <row r="421" ht="15.75" customHeight="1" spans="5:5">
+    <row r="421" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B421" s="109"/>
       <c r="E421" s="114"/>
     </row>
-    <row r="422" ht="15.75" customHeight="1" spans="5:5">
+    <row r="422" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B422" s="109"/>
       <c r="E422" s="114"/>
     </row>
-    <row r="423" ht="15.75" customHeight="1" spans="5:5">
+    <row r="423" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B423" s="109"/>
       <c r="E423" s="114"/>
     </row>
-    <row r="424" ht="15.75" customHeight="1" spans="5:5">
+    <row r="424" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B424" s="109"/>
       <c r="E424" s="114"/>
     </row>
-    <row r="425" ht="15.75" customHeight="1" spans="5:5">
+    <row r="425" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B425" s="109"/>
       <c r="E425" s="114"/>
     </row>
-    <row r="426" ht="15.75" customHeight="1" spans="5:5">
+    <row r="426" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B426" s="109"/>
       <c r="E426" s="114"/>
     </row>
-    <row r="427" ht="15.75" customHeight="1" spans="5:5">
+    <row r="427" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B427" s="109"/>
       <c r="E427" s="114"/>
     </row>
-    <row r="428" ht="15.75" customHeight="1" spans="5:5">
+    <row r="428" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B428" s="109"/>
       <c r="E428" s="114"/>
     </row>
-    <row r="429" ht="15.75" customHeight="1" spans="5:5">
+    <row r="429" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B429" s="109"/>
       <c r="E429" s="114"/>
     </row>
-    <row r="430" ht="15.75" customHeight="1" spans="5:5">
+    <row r="430" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B430" s="109"/>
       <c r="E430" s="114"/>
     </row>
-    <row r="431" ht="15.75" customHeight="1" spans="5:5">
+    <row r="431" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B431" s="109"/>
       <c r="E431" s="114"/>
     </row>
-    <row r="432" ht="15.75" customHeight="1" spans="5:5">
+    <row r="432" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B432" s="109"/>
       <c r="E432" s="114"/>
     </row>
-    <row r="433" ht="15.75" customHeight="1" spans="5:5">
+    <row r="433" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B433" s="109"/>
       <c r="E433" s="114"/>
     </row>
-    <row r="434" ht="15.75" customHeight="1" spans="5:5">
+    <row r="434" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B434" s="109"/>
       <c r="E434" s="114"/>
     </row>
-    <row r="435" ht="15.75" customHeight="1" spans="5:5">
+    <row r="435" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B435" s="109"/>
       <c r="E435" s="114"/>
     </row>
-    <row r="436" ht="15.75" customHeight="1" spans="5:5">
+    <row r="436" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B436" s="109"/>
       <c r="E436" s="114"/>
     </row>
-    <row r="437" ht="15.75" customHeight="1" spans="5:5">
+    <row r="437" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B437" s="109"/>
       <c r="E437" s="114"/>
     </row>
-    <row r="438" ht="15.75" customHeight="1" spans="5:5">
+    <row r="438" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B438" s="109"/>
       <c r="E438" s="114"/>
     </row>
-    <row r="439" ht="15.75" customHeight="1" spans="5:5">
+    <row r="439" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B439" s="109"/>
       <c r="E439" s="114"/>
     </row>
-    <row r="440" ht="15.75" customHeight="1" spans="5:5">
+    <row r="440" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B440" s="109"/>
       <c r="E440" s="114"/>
     </row>
-    <row r="441" ht="15.75" customHeight="1" spans="5:5">
+    <row r="441" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B441" s="109"/>
       <c r="E441" s="114"/>
     </row>
-    <row r="442" ht="15.75" customHeight="1" spans="5:5">
+    <row r="442" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B442" s="109"/>
       <c r="E442" s="114"/>
     </row>
-    <row r="443" ht="15.75" customHeight="1" spans="5:5">
+    <row r="443" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B443" s="109"/>
       <c r="E443" s="114"/>
     </row>
-    <row r="444" ht="15.75" customHeight="1" spans="5:5">
+    <row r="444" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B444" s="109"/>
       <c r="E444" s="114"/>
     </row>
-    <row r="445" ht="15.75" customHeight="1" spans="5:5">
+    <row r="445" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B445" s="109"/>
       <c r="E445" s="114"/>
     </row>
-    <row r="446" ht="15.75" customHeight="1" spans="5:5">
+    <row r="446" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B446" s="109"/>
       <c r="E446" s="114"/>
     </row>
-    <row r="447" ht="15.75" customHeight="1" spans="5:5">
+    <row r="447" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B447" s="109"/>
       <c r="E447" s="114"/>
     </row>
-    <row r="448" ht="15.75" customHeight="1" spans="5:5">
+    <row r="448" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B448" s="109"/>
       <c r="E448" s="114"/>
     </row>
-    <row r="449" ht="15.75" customHeight="1" spans="5:5">
+    <row r="449" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B449" s="109"/>
       <c r="E449" s="114"/>
     </row>
-    <row r="450" ht="15.75" customHeight="1" spans="5:5">
+    <row r="450" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B450" s="109"/>
       <c r="E450" s="114"/>
     </row>
-    <row r="451" ht="15.75" customHeight="1" spans="5:5">
+    <row r="451" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B451" s="109"/>
       <c r="E451" s="114"/>
     </row>
-    <row r="452" ht="15.75" customHeight="1" spans="5:5">
+    <row r="452" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B452" s="109"/>
       <c r="E452" s="114"/>
     </row>
-    <row r="453" ht="15.75" customHeight="1" spans="5:5">
+    <row r="453" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B453" s="109"/>
       <c r="E453" s="114"/>
     </row>
-    <row r="454" ht="15.75" customHeight="1" spans="5:5">
+    <row r="454" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B454" s="109"/>
       <c r="E454" s="114"/>
     </row>
-    <row r="455" ht="15.75" customHeight="1" spans="5:5">
+    <row r="455" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B455" s="109"/>
       <c r="E455" s="114"/>
     </row>
-    <row r="456" ht="15.75" customHeight="1" spans="5:5">
+    <row r="456" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B456" s="109"/>
       <c r="E456" s="114"/>
     </row>
-    <row r="457" ht="15.75" customHeight="1" spans="5:5">
+    <row r="457" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B457" s="109"/>
       <c r="E457" s="114"/>
     </row>
-    <row r="458" ht="15.75" customHeight="1" spans="5:5">
+    <row r="458" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B458" s="109"/>
       <c r="E458" s="114"/>
     </row>
-    <row r="459" ht="15.75" customHeight="1" spans="5:5">
+    <row r="459" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B459" s="109"/>
       <c r="E459" s="114"/>
     </row>
-    <row r="460" ht="15.75" customHeight="1" spans="5:5">
+    <row r="460" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B460" s="109"/>
       <c r="E460" s="114"/>
     </row>
-    <row r="461" ht="15.75" customHeight="1" spans="5:5">
+    <row r="461" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B461" s="109"/>
       <c r="E461" s="114"/>
     </row>
-    <row r="462" ht="15.75" customHeight="1" spans="5:5">
+    <row r="462" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B462" s="109"/>
       <c r="E462" s="114"/>
     </row>
-    <row r="463" ht="15.75" customHeight="1" spans="5:5">
+    <row r="463" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B463" s="109"/>
       <c r="E463" s="114"/>
     </row>
-    <row r="464" ht="15.75" customHeight="1" spans="5:5">
+    <row r="464" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B464" s="109"/>
       <c r="E464" s="114"/>
     </row>
-    <row r="465" ht="15.75" customHeight="1" spans="5:5">
+    <row r="465" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B465" s="109"/>
       <c r="E465" s="114"/>
     </row>
-    <row r="466" ht="15.75" customHeight="1" spans="5:5">
+    <row r="466" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B466" s="109"/>
       <c r="E466" s="114"/>
     </row>
-    <row r="467" ht="15.75" customHeight="1" spans="5:5">
+    <row r="467" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B467" s="109"/>
       <c r="E467" s="114"/>
     </row>
-    <row r="468" ht="15.75" customHeight="1" spans="5:5">
+    <row r="468" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B468" s="109"/>
       <c r="E468" s="114"/>
     </row>
-    <row r="469" ht="15.75" customHeight="1" spans="5:5">
+    <row r="469" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B469" s="109"/>
       <c r="E469" s="114"/>
     </row>
-    <row r="470" ht="15.75" customHeight="1" spans="5:5">
+    <row r="470" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B470" s="109"/>
       <c r="E470" s="114"/>
     </row>
-    <row r="471" ht="15.75" customHeight="1" spans="5:5">
+    <row r="471" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B471" s="109"/>
       <c r="E471" s="114"/>
     </row>
-    <row r="472" ht="15.75" customHeight="1" spans="5:5">
+    <row r="472" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B472" s="109"/>
       <c r="E472" s="114"/>
     </row>
-    <row r="473" ht="15.75" customHeight="1" spans="5:5">
+    <row r="473" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B473" s="109"/>
       <c r="E473" s="114"/>
     </row>
-    <row r="474" ht="15.75" customHeight="1" spans="5:5">
+    <row r="474" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B474" s="109"/>
       <c r="E474" s="114"/>
     </row>
-    <row r="475" ht="15.75" customHeight="1" spans="5:5">
+    <row r="475" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B475" s="109"/>
       <c r="E475" s="114"/>
     </row>
-    <row r="476" ht="15.75" customHeight="1" spans="5:5">
+    <row r="476" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B476" s="109"/>
       <c r="E476" s="114"/>
     </row>
-    <row r="477" ht="15.75" customHeight="1" spans="5:5">
+    <row r="477" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B477" s="109"/>
       <c r="E477" s="114"/>
     </row>
-    <row r="478" ht="15.75" customHeight="1" spans="5:5">
+    <row r="478" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B478" s="109"/>
       <c r="E478" s="114"/>
     </row>
-    <row r="479" ht="15.75" customHeight="1" spans="5:5">
+    <row r="479" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B479" s="109"/>
       <c r="E479" s="114"/>
     </row>
-    <row r="480" ht="15.75" customHeight="1" spans="5:5">
+    <row r="480" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B480" s="109"/>
       <c r="E480" s="114"/>
     </row>
-    <row r="481" ht="15.75" customHeight="1" spans="5:5">
+    <row r="481" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B481" s="109"/>
       <c r="E481" s="114"/>
     </row>
-    <row r="482" ht="15.75" customHeight="1" spans="5:5">
+    <row r="482" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B482" s="109"/>
       <c r="E482" s="114"/>
     </row>
-    <row r="483" ht="15.75" customHeight="1" spans="5:5">
+    <row r="483" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B483" s="109"/>
       <c r="E483" s="114"/>
     </row>
-    <row r="484" ht="15.75" customHeight="1" spans="5:5">
+    <row r="484" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B484" s="109"/>
       <c r="E484" s="114"/>
     </row>
-    <row r="485" ht="15.75" customHeight="1" spans="5:5">
+    <row r="485" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B485" s="109"/>
       <c r="E485" s="114"/>
     </row>
-    <row r="486" ht="15.75" customHeight="1" spans="5:5">
+    <row r="486" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B486" s="109"/>
       <c r="E486" s="114"/>
     </row>
-    <row r="487" ht="15.75" customHeight="1" spans="5:5">
+    <row r="487" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B487" s="109"/>
       <c r="E487" s="114"/>
     </row>
-    <row r="488" ht="15.75" customHeight="1" spans="5:5">
+    <row r="488" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B488" s="109"/>
       <c r="E488" s="114"/>
     </row>
-    <row r="489" ht="15.75" customHeight="1" spans="5:5">
+    <row r="489" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B489" s="109"/>
       <c r="E489" s="114"/>
     </row>
-    <row r="490" ht="15.75" customHeight="1" spans="5:5">
+    <row r="490" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B490" s="109"/>
       <c r="E490" s="114"/>
     </row>
-    <row r="491" ht="15.75" customHeight="1" spans="5:5">
+    <row r="491" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B491" s="109"/>
       <c r="E491" s="114"/>
     </row>
-    <row r="492" ht="15.75" customHeight="1" spans="5:5">
+    <row r="492" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B492" s="109"/>
       <c r="E492" s="114"/>
     </row>
-    <row r="493" ht="15.75" customHeight="1" spans="5:5">
+    <row r="493" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B493" s="109"/>
       <c r="E493" s="114"/>
     </row>
-    <row r="494" ht="15.75" customHeight="1" spans="5:5">
+    <row r="494" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B494" s="109"/>
       <c r="E494" s="114"/>
     </row>
-    <row r="495" ht="15.75" customHeight="1" spans="5:5">
+    <row r="495" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B495" s="109"/>
       <c r="E495" s="114"/>
     </row>
-    <row r="496" ht="15.75" customHeight="1" spans="5:5">
+    <row r="496" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B496" s="109"/>
       <c r="E496" s="114"/>
     </row>
-    <row r="497" ht="15.75" customHeight="1" spans="5:5">
+    <row r="497" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B497" s="109"/>
       <c r="E497" s="114"/>
     </row>
-    <row r="498" ht="15.75" customHeight="1" spans="5:5">
+    <row r="498" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B498" s="109"/>
       <c r="E498" s="114"/>
     </row>
-    <row r="499" ht="15.75" customHeight="1" spans="5:5">
+    <row r="499" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B499" s="109"/>
       <c r="E499" s="114"/>
     </row>
-    <row r="500" ht="15.75" customHeight="1" spans="5:5">
+    <row r="500" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B500" s="109"/>
       <c r="E500" s="114"/>
     </row>
-    <row r="501" ht="15.75" customHeight="1" spans="5:5">
+    <row r="501" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B501" s="109"/>
       <c r="E501" s="114"/>
     </row>
-    <row r="502" ht="15.75" customHeight="1" spans="5:5">
+    <row r="502" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B502" s="109"/>
       <c r="E502" s="114"/>
     </row>
-    <row r="503" ht="15.75" customHeight="1" spans="5:5">
+    <row r="503" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B503" s="109"/>
       <c r="E503" s="114"/>
     </row>
-    <row r="504" ht="15.75" customHeight="1" spans="5:5">
+    <row r="504" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B504" s="109"/>
       <c r="E504" s="114"/>
     </row>
-    <row r="505" ht="15.75" customHeight="1" spans="5:5">
+    <row r="505" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B505" s="109"/>
       <c r="E505" s="114"/>
     </row>
-    <row r="506" ht="15.75" customHeight="1" spans="5:5">
+    <row r="506" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B506" s="109"/>
       <c r="E506" s="114"/>
     </row>
-    <row r="507" ht="15.75" customHeight="1" spans="5:5">
+    <row r="507" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B507" s="109"/>
       <c r="E507" s="114"/>
     </row>
-    <row r="508" ht="15.75" customHeight="1" spans="5:5">
+    <row r="508" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B508" s="109"/>
       <c r="E508" s="114"/>
     </row>
-    <row r="509" ht="15.75" customHeight="1" spans="5:5">
+    <row r="509" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B509" s="109"/>
       <c r="E509" s="114"/>
     </row>
-    <row r="510" ht="15.75" customHeight="1" spans="5:5">
+    <row r="510" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B510" s="109"/>
       <c r="E510" s="114"/>
     </row>
-    <row r="511" ht="15.75" customHeight="1" spans="5:5">
+    <row r="511" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B511" s="109"/>
       <c r="E511" s="114"/>
     </row>
-    <row r="512" ht="15.75" customHeight="1" spans="5:5">
+    <row r="512" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B512" s="109"/>
       <c r="E512" s="114"/>
     </row>
-    <row r="513" ht="15.75" customHeight="1" spans="5:5">
+    <row r="513" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B513" s="109"/>
       <c r="E513" s="114"/>
     </row>
-    <row r="514" ht="15.75" customHeight="1" spans="5:5">
+    <row r="514" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B514" s="109"/>
       <c r="E514" s="114"/>
     </row>
-    <row r="515" ht="15.75" customHeight="1" spans="5:5">
+    <row r="515" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B515" s="109"/>
       <c r="E515" s="114"/>
     </row>
-    <row r="516" ht="15.75" customHeight="1" spans="5:5">
+    <row r="516" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B516" s="109"/>
       <c r="E516" s="114"/>
     </row>
-    <row r="517" ht="15.75" customHeight="1" spans="5:5">
+    <row r="517" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B517" s="109"/>
       <c r="E517" s="114"/>
     </row>
-    <row r="518" ht="15.75" customHeight="1" spans="5:5">
+    <row r="518" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B518" s="109"/>
       <c r="E518" s="114"/>
     </row>
-    <row r="519" ht="15.75" customHeight="1" spans="5:5">
+    <row r="519" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B519" s="109"/>
       <c r="E519" s="114"/>
     </row>
-    <row r="520" ht="15.75" customHeight="1" spans="5:5">
+    <row r="520" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B520" s="109"/>
       <c r="E520" s="114"/>
     </row>
-    <row r="521" ht="15.75" customHeight="1" spans="5:5">
+    <row r="521" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B521" s="109"/>
       <c r="E521" s="114"/>
     </row>
-    <row r="522" ht="15.75" customHeight="1" spans="5:5">
+    <row r="522" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B522" s="109"/>
       <c r="E522" s="114"/>
     </row>
-    <row r="523" ht="15.75" customHeight="1" spans="5:5">
+    <row r="523" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B523" s="109"/>
       <c r="E523" s="114"/>
     </row>
-    <row r="524" ht="15.75" customHeight="1" spans="5:5">
+    <row r="524" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B524" s="109"/>
       <c r="E524" s="114"/>
     </row>
-    <row r="525" ht="15.75" customHeight="1" spans="5:5">
+    <row r="525" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B525" s="109"/>
       <c r="E525" s="114"/>
     </row>
-    <row r="526" ht="15.75" customHeight="1" spans="5:5">
+    <row r="526" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B526" s="109"/>
       <c r="E526" s="114"/>
     </row>
-    <row r="527" ht="15.75" customHeight="1" spans="5:5">
+    <row r="527" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B527" s="109"/>
       <c r="E527" s="114"/>
     </row>
-    <row r="528" ht="15.75" customHeight="1" spans="5:5">
+    <row r="528" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B528" s="109"/>
       <c r="E528" s="114"/>
     </row>
-    <row r="529" ht="15.75" customHeight="1" spans="5:5">
+    <row r="529" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B529" s="109"/>
       <c r="E529" s="114"/>
     </row>
-    <row r="530" ht="15.75" customHeight="1" spans="5:5">
+    <row r="530" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B530" s="109"/>
       <c r="E530" s="114"/>
     </row>
-    <row r="531" ht="15.75" customHeight="1" spans="5:5">
+    <row r="531" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B531" s="109"/>
       <c r="E531" s="114"/>
     </row>
-    <row r="532" ht="15.75" customHeight="1" spans="5:5">
+    <row r="532" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B532" s="109"/>
       <c r="E532" s="114"/>
     </row>
-    <row r="533" ht="15.75" customHeight="1" spans="5:5">
+    <row r="533" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B533" s="109"/>
       <c r="E533" s="114"/>
     </row>
-    <row r="534" ht="15.75" customHeight="1" spans="5:5">
+    <row r="534" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B534" s="109"/>
       <c r="E534" s="114"/>
     </row>
-    <row r="535" ht="15.75" customHeight="1" spans="5:5">
+    <row r="535" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B535" s="109"/>
       <c r="E535" s="114"/>
     </row>
-    <row r="536" ht="15.75" customHeight="1" spans="5:5">
+    <row r="536" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B536" s="109"/>
       <c r="E536" s="114"/>
     </row>
-    <row r="537" ht="15.75" customHeight="1" spans="5:5">
+    <row r="537" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B537" s="109"/>
       <c r="E537" s="114"/>
     </row>
-    <row r="538" ht="15.75" customHeight="1" spans="5:5">
+    <row r="538" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B538" s="109"/>
       <c r="E538" s="114"/>
     </row>
-    <row r="539" ht="15.75" customHeight="1" spans="5:5">
+    <row r="539" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B539" s="109"/>
       <c r="E539" s="114"/>
     </row>
-    <row r="540" ht="15.75" customHeight="1" spans="5:5">
+    <row r="540" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B540" s="109"/>
       <c r="E540" s="114"/>
     </row>
-    <row r="541" ht="15.75" customHeight="1" spans="5:5">
+    <row r="541" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B541" s="109"/>
       <c r="E541" s="114"/>
     </row>
-    <row r="542" ht="15.75" customHeight="1" spans="5:5">
+    <row r="542" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B542" s="109"/>
       <c r="E542" s="114"/>
     </row>
-    <row r="543" ht="15.75" customHeight="1" spans="5:5">
+    <row r="543" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B543" s="109"/>
       <c r="E543" s="114"/>
     </row>
-    <row r="544" ht="15.75" customHeight="1" spans="5:5">
+    <row r="544" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B544" s="109"/>
       <c r="E544" s="114"/>
     </row>
-    <row r="545" ht="15.75" customHeight="1" spans="5:5">
+    <row r="545" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B545" s="109"/>
       <c r="E545" s="114"/>
     </row>
-    <row r="546" ht="15.75" customHeight="1" spans="5:5">
+    <row r="546" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B546" s="109"/>
       <c r="E546" s="114"/>
     </row>
-    <row r="547" ht="15.75" customHeight="1" spans="5:5">
+    <row r="547" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B547" s="109"/>
       <c r="E547" s="114"/>
     </row>
-    <row r="548" ht="15.75" customHeight="1" spans="5:5">
+    <row r="548" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B548" s="109"/>
       <c r="E548" s="114"/>
     </row>
-    <row r="549" ht="15.75" customHeight="1" spans="5:5">
+    <row r="549" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B549" s="109"/>
       <c r="E549" s="114"/>
     </row>
-    <row r="550" ht="15.75" customHeight="1" spans="5:5">
+    <row r="550" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B550" s="109"/>
       <c r="E550" s="114"/>
     </row>
-    <row r="551" ht="15.75" customHeight="1" spans="5:5">
+    <row r="551" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B551" s="109"/>
       <c r="E551" s="114"/>
     </row>
-    <row r="552" ht="15.75" customHeight="1" spans="5:5">
+    <row r="552" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B552" s="109"/>
       <c r="E552" s="114"/>
     </row>
-    <row r="553" ht="15.75" customHeight="1" spans="5:5">
+    <row r="553" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B553" s="109"/>
       <c r="E553" s="114"/>
     </row>
-    <row r="554" ht="15.75" customHeight="1" spans="5:5">
+    <row r="554" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B554" s="109"/>
       <c r="E554" s="114"/>
     </row>
-    <row r="555" ht="15.75" customHeight="1" spans="5:5">
+    <row r="555" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B555" s="109"/>
       <c r="E555" s="114"/>
     </row>
-    <row r="556" ht="15.75" customHeight="1" spans="5:5">
+    <row r="556" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B556" s="109"/>
       <c r="E556" s="114"/>
     </row>
-    <row r="557" ht="15.75" customHeight="1" spans="5:5">
+    <row r="557" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B557" s="109"/>
       <c r="E557" s="114"/>
     </row>
-    <row r="558" ht="15.75" customHeight="1" spans="5:5">
+    <row r="558" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B558" s="109"/>
       <c r="E558" s="114"/>
     </row>
-    <row r="559" ht="15.75" customHeight="1" spans="5:5">
+    <row r="559" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B559" s="109"/>
       <c r="E559" s="114"/>
     </row>
-    <row r="560" ht="15.75" customHeight="1" spans="5:5">
+    <row r="560" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B560" s="109"/>
       <c r="E560" s="114"/>
     </row>
-    <row r="561" ht="15.75" customHeight="1" spans="5:5">
+    <row r="561" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B561" s="109"/>
       <c r="E561" s="114"/>
     </row>
-    <row r="562" ht="15.75" customHeight="1" spans="5:5">
+    <row r="562" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B562" s="109"/>
       <c r="E562" s="114"/>
     </row>
-    <row r="563" ht="15.75" customHeight="1" spans="5:5">
+    <row r="563" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B563" s="109"/>
       <c r="E563" s="114"/>
     </row>
-    <row r="564" ht="15.75" customHeight="1" spans="5:5">
+    <row r="564" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B564" s="109"/>
       <c r="E564" s="114"/>
     </row>
-    <row r="565" ht="15.75" customHeight="1" spans="5:5">
+    <row r="565" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B565" s="109"/>
       <c r="E565" s="114"/>
     </row>
-    <row r="566" ht="15.75" customHeight="1" spans="5:5">
+    <row r="566" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B566" s="109"/>
       <c r="E566" s="114"/>
     </row>
-    <row r="567" ht="15.75" customHeight="1" spans="5:5">
+    <row r="567" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B567" s="109"/>
       <c r="E567" s="114"/>
     </row>
-    <row r="568" ht="15.75" customHeight="1" spans="5:5">
+    <row r="568" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B568" s="109"/>
       <c r="E568" s="114"/>
     </row>
-    <row r="569" ht="15.75" customHeight="1" spans="5:5">
+    <row r="569" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B569" s="109"/>
       <c r="E569" s="114"/>
     </row>
-    <row r="570" ht="15.75" customHeight="1" spans="5:5">
+    <row r="570" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B570" s="109"/>
       <c r="E570" s="114"/>
     </row>
-    <row r="571" ht="15.75" customHeight="1" spans="5:5">
+    <row r="571" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B571" s="109"/>
       <c r="E571" s="114"/>
     </row>
-    <row r="572" ht="15.75" customHeight="1" spans="5:5">
+    <row r="572" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B572" s="109"/>
       <c r="E572" s="114"/>
     </row>
-    <row r="573" ht="15.75" customHeight="1" spans="5:5">
+    <row r="573" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B573" s="109"/>
       <c r="E573" s="114"/>
     </row>
-    <row r="574" ht="15.75" customHeight="1" spans="5:5">
+    <row r="574" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B574" s="109"/>
       <c r="E574" s="114"/>
     </row>
-    <row r="575" ht="15.75" customHeight="1" spans="5:5">
+    <row r="575" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B575" s="109"/>
       <c r="E575" s="114"/>
     </row>
-    <row r="576" ht="15.75" customHeight="1" spans="5:5">
+    <row r="576" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B576" s="109"/>
       <c r="E576" s="114"/>
     </row>
-    <row r="577" ht="15.75" customHeight="1" spans="5:5">
+    <row r="577" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B577" s="109"/>
       <c r="E577" s="114"/>
     </row>
-    <row r="578" ht="15.75" customHeight="1" spans="5:5">
+    <row r="578" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B578" s="109"/>
       <c r="E578" s="114"/>
     </row>
-    <row r="579" ht="15.75" customHeight="1" spans="5:5">
+    <row r="579" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B579" s="109"/>
       <c r="E579" s="114"/>
     </row>
-    <row r="580" ht="15.75" customHeight="1" spans="5:5">
+    <row r="580" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B580" s="109"/>
       <c r="E580" s="114"/>
     </row>
-    <row r="581" ht="15.75" customHeight="1" spans="5:5">
+    <row r="581" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B581" s="109"/>
       <c r="E581" s="114"/>
     </row>
-    <row r="582" ht="15.75" customHeight="1" spans="5:5">
+    <row r="582" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B582" s="109"/>
       <c r="E582" s="114"/>
     </row>
-    <row r="583" ht="15.75" customHeight="1" spans="5:5">
+    <row r="583" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B583" s="109"/>
       <c r="E583" s="114"/>
     </row>
-    <row r="584" ht="15.75" customHeight="1" spans="5:5">
+    <row r="584" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B584" s="109"/>
       <c r="E584" s="114"/>
     </row>
-    <row r="585" ht="15.75" customHeight="1" spans="5:5">
+    <row r="585" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B585" s="109"/>
       <c r="E585" s="114"/>
     </row>
-    <row r="586" ht="15.75" customHeight="1" spans="5:5">
+    <row r="586" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B586" s="109"/>
       <c r="E586" s="114"/>
     </row>
-    <row r="587" ht="15.75" customHeight="1" spans="5:5">
+    <row r="587" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B587" s="109"/>
       <c r="E587" s="114"/>
     </row>
-    <row r="588" ht="15.75" customHeight="1" spans="5:5">
+    <row r="588" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B588" s="109"/>
       <c r="E588" s="114"/>
     </row>
-    <row r="589" ht="15.75" customHeight="1" spans="5:5">
+    <row r="589" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B589" s="109"/>
       <c r="E589" s="114"/>
     </row>
-    <row r="590" ht="15.75" customHeight="1" spans="5:5">
+    <row r="590" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B590" s="109"/>
       <c r="E590" s="114"/>
     </row>
-    <row r="591" ht="15.75" customHeight="1" spans="5:5">
+    <row r="591" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B591" s="109"/>
       <c r="E591" s="114"/>
     </row>
-    <row r="592" ht="15.75" customHeight="1" spans="5:5">
+    <row r="592" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B592" s="109"/>
       <c r="E592" s="114"/>
     </row>
-    <row r="593" ht="15.75" customHeight="1" spans="5:5">
+    <row r="593" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B593" s="109"/>
       <c r="E593" s="114"/>
     </row>
-    <row r="594" ht="15.75" customHeight="1" spans="5:5">
+    <row r="594" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B594" s="109"/>
       <c r="E594" s="114"/>
     </row>
-    <row r="595" ht="15.75" customHeight="1" spans="5:5">
+    <row r="595" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B595" s="109"/>
       <c r="E595" s="114"/>
     </row>
-    <row r="596" ht="15.75" customHeight="1" spans="5:5">
+    <row r="596" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B596" s="109"/>
       <c r="E596" s="114"/>
     </row>
-    <row r="597" ht="15.75" customHeight="1" spans="5:5">
+    <row r="597" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B597" s="109"/>
       <c r="E597" s="114"/>
     </row>
-    <row r="598" ht="15.75" customHeight="1" spans="5:5">
+    <row r="598" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B598" s="109"/>
       <c r="E598" s="114"/>
     </row>
-    <row r="599" ht="15.75" customHeight="1" spans="5:5">
+    <row r="599" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B599" s="109"/>
       <c r="E599" s="114"/>
     </row>
-    <row r="600" ht="15.75" customHeight="1" spans="5:5">
+    <row r="600" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B600" s="109"/>
       <c r="E600" s="114"/>
     </row>
-    <row r="601" ht="15.75" customHeight="1" spans="5:5">
+    <row r="601" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B601" s="109"/>
       <c r="E601" s="114"/>
     </row>
-    <row r="602" ht="15.75" customHeight="1" spans="5:5">
+    <row r="602" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B602" s="109"/>
       <c r="E602" s="114"/>
     </row>
-    <row r="603" ht="15.75" customHeight="1" spans="5:5">
+    <row r="603" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B603" s="109"/>
       <c r="E603" s="114"/>
     </row>
-    <row r="604" ht="15.75" customHeight="1" spans="5:5">
+    <row r="604" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B604" s="109"/>
       <c r="E604" s="114"/>
     </row>
-    <row r="605" ht="15.75" customHeight="1" spans="5:5">
+    <row r="605" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B605" s="109"/>
       <c r="E605" s="114"/>
     </row>
-    <row r="606" ht="15.75" customHeight="1" spans="5:5">
+    <row r="606" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B606" s="109"/>
       <c r="E606" s="114"/>
     </row>
-    <row r="607" ht="15.75" customHeight="1" spans="5:5">
+    <row r="607" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B607" s="109"/>
       <c r="E607" s="114"/>
     </row>
-    <row r="608" ht="15.75" customHeight="1" spans="5:5">
+    <row r="608" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B608" s="109"/>
       <c r="E608" s="114"/>
     </row>
-    <row r="609" ht="15.75" customHeight="1" spans="5:5">
+    <row r="609" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B609" s="109"/>
       <c r="E609" s="114"/>
     </row>
-    <row r="610" ht="15.75" customHeight="1" spans="5:5">
+    <row r="610" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B610" s="109"/>
       <c r="E610" s="114"/>
     </row>
-    <row r="611" ht="15.75" customHeight="1" spans="5:5">
+    <row r="611" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B611" s="109"/>
       <c r="E611" s="114"/>
     </row>
-    <row r="612" ht="15.75" customHeight="1" spans="5:5">
+    <row r="612" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B612" s="109"/>
       <c r="E612" s="114"/>
     </row>
-    <row r="613" ht="15.75" customHeight="1" spans="5:5">
+    <row r="613" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B613" s="109"/>
       <c r="E613" s="114"/>
     </row>
-    <row r="614" ht="15.75" customHeight="1" spans="5:5">
+    <row r="614" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B614" s="109"/>
       <c r="E614" s="114"/>
     </row>
-    <row r="615" ht="15.75" customHeight="1" spans="5:5">
+    <row r="615" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B615" s="109"/>
       <c r="E615" s="114"/>
     </row>
-    <row r="616" ht="15.75" customHeight="1" spans="5:5">
+    <row r="616" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B616" s="109"/>
       <c r="E616" s="114"/>
     </row>
-    <row r="617" ht="15.75" customHeight="1" spans="5:5">
+    <row r="617" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B617" s="109"/>
       <c r="E617" s="114"/>
     </row>
-    <row r="618" ht="15.75" customHeight="1" spans="5:5">
+    <row r="618" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B618" s="109"/>
       <c r="E618" s="114"/>
     </row>
-    <row r="619" ht="15.75" customHeight="1" spans="5:5">
+    <row r="619" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B619" s="109"/>
       <c r="E619" s="114"/>
     </row>
-    <row r="620" ht="15.75" customHeight="1" spans="5:5">
+    <row r="620" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B620" s="109"/>
       <c r="E620" s="114"/>
     </row>
-    <row r="621" ht="15.75" customHeight="1" spans="5:5">
+    <row r="621" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B621" s="109"/>
       <c r="E621" s="114"/>
     </row>
-    <row r="622" ht="15.75" customHeight="1" spans="5:5">
+    <row r="622" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B622" s="109"/>
       <c r="E622" s="114"/>
     </row>
-    <row r="623" ht="15.75" customHeight="1" spans="5:5">
+    <row r="623" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B623" s="109"/>
       <c r="E623" s="114"/>
     </row>
-    <row r="624" ht="15.75" customHeight="1" spans="5:5">
+    <row r="624" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B624" s="109"/>
       <c r="E624" s="114"/>
     </row>
-    <row r="625" ht="15.75" customHeight="1" spans="5:5">
+    <row r="625" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B625" s="109"/>
       <c r="E625" s="114"/>
     </row>
-    <row r="626" ht="15.75" customHeight="1" spans="5:5">
+    <row r="626" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B626" s="109"/>
       <c r="E626" s="114"/>
     </row>
-    <row r="627" ht="15.75" customHeight="1" spans="5:5">
+    <row r="627" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B627" s="109"/>
       <c r="E627" s="114"/>
     </row>
-    <row r="628" ht="15.75" customHeight="1" spans="5:5">
+    <row r="628" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B628" s="109"/>
       <c r="E628" s="114"/>
     </row>
-    <row r="629" ht="15.75" customHeight="1" spans="5:5">
+    <row r="629" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B629" s="109"/>
       <c r="E629" s="114"/>
     </row>
-    <row r="630" ht="15.75" customHeight="1" spans="5:5">
+    <row r="630" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B630" s="109"/>
       <c r="E630" s="114"/>
     </row>
-    <row r="631" ht="15.75" customHeight="1" spans="5:5">
+    <row r="631" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B631" s="109"/>
       <c r="E631" s="114"/>
     </row>
-    <row r="632" ht="15.75" customHeight="1" spans="5:5">
+    <row r="632" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B632" s="109"/>
       <c r="E632" s="114"/>
     </row>
-    <row r="633" ht="15.75" customHeight="1" spans="5:5">
+    <row r="633" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B633" s="109"/>
       <c r="E633" s="114"/>
     </row>
-    <row r="634" ht="15.75" customHeight="1" spans="5:5">
+    <row r="634" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B634" s="109"/>
       <c r="E634" s="114"/>
     </row>
-    <row r="635" ht="15.75" customHeight="1" spans="5:5">
+    <row r="635" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B635" s="109"/>
       <c r="E635" s="114"/>
     </row>
-    <row r="636" ht="15.75" customHeight="1" spans="5:5">
+    <row r="636" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B636" s="109"/>
       <c r="E636" s="114"/>
     </row>
-    <row r="637" ht="15.75" customHeight="1" spans="5:5">
+    <row r="637" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B637" s="109"/>
       <c r="E637" s="114"/>
     </row>
-    <row r="638" ht="15.75" customHeight="1" spans="5:5">
+    <row r="638" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B638" s="109"/>
       <c r="E638" s="114"/>
     </row>
-    <row r="639" ht="15.75" customHeight="1" spans="5:5">
+    <row r="639" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B639" s="109"/>
       <c r="E639" s="114"/>
     </row>
-    <row r="640" ht="15.75" customHeight="1" spans="5:5">
+    <row r="640" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B640" s="109"/>
       <c r="E640" s="114"/>
     </row>
-    <row r="641" ht="15.75" customHeight="1" spans="5:5">
+    <row r="641" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B641" s="109"/>
       <c r="E641" s="114"/>
     </row>
-    <row r="642" ht="15.75" customHeight="1" spans="5:5">
+    <row r="642" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B642" s="109"/>
       <c r="E642" s="114"/>
     </row>
-    <row r="643" ht="15.75" customHeight="1" spans="5:5">
+    <row r="643" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B643" s="109"/>
       <c r="E643" s="114"/>
     </row>
-    <row r="644" ht="15.75" customHeight="1" spans="5:5">
+    <row r="644" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B644" s="109"/>
       <c r="E644" s="114"/>
     </row>
-    <row r="645" ht="15.75" customHeight="1" spans="5:5">
+    <row r="645" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B645" s="109"/>
       <c r="E645" s="114"/>
     </row>
-    <row r="646" ht="15.75" customHeight="1" spans="5:5">
+    <row r="646" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B646" s="109"/>
       <c r="E646" s="114"/>
     </row>
-    <row r="647" ht="15.75" customHeight="1" spans="5:5">
+    <row r="647" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B647" s="109"/>
       <c r="E647" s="114"/>
     </row>
-    <row r="648" ht="15.75" customHeight="1" spans="5:5">
+    <row r="648" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B648" s="109"/>
       <c r="E648" s="114"/>
     </row>
-    <row r="649" ht="15.75" customHeight="1" spans="5:5">
+    <row r="649" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B649" s="109"/>
       <c r="E649" s="114"/>
     </row>
-    <row r="650" ht="15.75" customHeight="1" spans="5:5">
+    <row r="650" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B650" s="109"/>
       <c r="E650" s="114"/>
     </row>
-    <row r="651" ht="15.75" customHeight="1" spans="5:5">
+    <row r="651" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B651" s="109"/>
       <c r="E651" s="114"/>
     </row>
-    <row r="652" ht="15.75" customHeight="1" spans="5:5">
+    <row r="652" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B652" s="109"/>
       <c r="E652" s="114"/>
     </row>
-    <row r="653" ht="15.75" customHeight="1" spans="5:5">
+    <row r="653" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B653" s="109"/>
       <c r="E653" s="114"/>
     </row>
-    <row r="654" ht="15.75" customHeight="1" spans="5:5">
+    <row r="654" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B654" s="109"/>
       <c r="E654" s="114"/>
     </row>
-    <row r="655" ht="15.75" customHeight="1" spans="5:5">
+    <row r="655" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B655" s="109"/>
       <c r="E655" s="114"/>
     </row>
-    <row r="656" ht="15.75" customHeight="1" spans="5:5">
+    <row r="656" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B656" s="109"/>
       <c r="E656" s="114"/>
     </row>
-    <row r="657" ht="15.75" customHeight="1" spans="5:5">
+    <row r="657" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B657" s="109"/>
       <c r="E657" s="114"/>
     </row>
-    <row r="658" ht="15.75" customHeight="1" spans="5:5">
+    <row r="658" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B658" s="109"/>
       <c r="E658" s="114"/>
     </row>
-    <row r="659" ht="15.75" customHeight="1" spans="5:5">
+    <row r="659" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B659" s="109"/>
       <c r="E659" s="114"/>
     </row>
-    <row r="660" ht="15.75" customHeight="1" spans="5:5">
+    <row r="660" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B660" s="109"/>
       <c r="E660" s="114"/>
     </row>
-    <row r="661" ht="15.75" customHeight="1" spans="5:5">
+    <row r="661" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B661" s="109"/>
       <c r="E661" s="114"/>
     </row>
-    <row r="662" ht="15.75" customHeight="1" spans="5:5">
+    <row r="662" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B662" s="109"/>
       <c r="E662" s="114"/>
     </row>
-    <row r="663" ht="15.75" customHeight="1" spans="5:5">
+    <row r="663" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B663" s="109"/>
       <c r="E663" s="114"/>
     </row>
-    <row r="664" ht="15.75" customHeight="1" spans="5:5">
+    <row r="664" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B664" s="109"/>
       <c r="E664" s="114"/>
     </row>
-    <row r="665" ht="15.75" customHeight="1" spans="5:5">
+    <row r="665" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B665" s="109"/>
       <c r="E665" s="114"/>
     </row>
-    <row r="666" ht="15.75" customHeight="1" spans="5:5">
+    <row r="666" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B666" s="109"/>
       <c r="E666" s="114"/>
     </row>
-    <row r="667" ht="15.75" customHeight="1" spans="5:5">
+    <row r="667" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B667" s="109"/>
       <c r="E667" s="114"/>
     </row>
-    <row r="668" ht="15.75" customHeight="1" spans="5:5">
+    <row r="668" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B668" s="109"/>
       <c r="E668" s="114"/>
     </row>
-    <row r="669" ht="15.75" customHeight="1" spans="5:5">
+    <row r="669" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B669" s="109"/>
       <c r="E669" s="114"/>
     </row>
-    <row r="670" ht="15.75" customHeight="1" spans="5:5">
+    <row r="670" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B670" s="109"/>
       <c r="E670" s="114"/>
     </row>
-    <row r="671" ht="15.75" customHeight="1" spans="5:5">
+    <row r="671" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B671" s="109"/>
       <c r="E671" s="114"/>
     </row>
-    <row r="672" ht="15.75" customHeight="1" spans="5:5">
+    <row r="672" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B672" s="109"/>
       <c r="E672" s="114"/>
     </row>
-    <row r="673" ht="15.75" customHeight="1" spans="5:5">
+    <row r="673" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B673" s="109"/>
       <c r="E673" s="114"/>
     </row>
-    <row r="674" ht="15.75" customHeight="1" spans="5:5">
+    <row r="674" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B674" s="109"/>
       <c r="E674" s="114"/>
     </row>
-    <row r="675" ht="15.75" customHeight="1" spans="5:5">
+    <row r="675" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B675" s="109"/>
       <c r="E675" s="114"/>
     </row>
-    <row r="676" ht="15.75" customHeight="1" spans="5:5">
+    <row r="676" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B676" s="109"/>
       <c r="E676" s="114"/>
     </row>
-    <row r="677" ht="15.75" customHeight="1" spans="5:5">
+    <row r="677" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B677" s="109"/>
       <c r="E677" s="114"/>
     </row>
-    <row r="678" ht="15.75" customHeight="1" spans="5:5">
+    <row r="678" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B678" s="109"/>
       <c r="E678" s="114"/>
     </row>
-    <row r="679" ht="15.75" customHeight="1" spans="5:5">
+    <row r="679" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B679" s="109"/>
       <c r="E679" s="114"/>
     </row>
-    <row r="680" ht="15.75" customHeight="1" spans="5:5">
+    <row r="680" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B680" s="109"/>
       <c r="E680" s="114"/>
     </row>
-    <row r="681" ht="15.75" customHeight="1" spans="5:5">
+    <row r="681" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B681" s="109"/>
       <c r="E681" s="114"/>
     </row>
-    <row r="682" ht="15.75" customHeight="1" spans="5:5">
+    <row r="682" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B682" s="109"/>
       <c r="E682" s="114"/>
     </row>
-    <row r="683" ht="15.75" customHeight="1" spans="5:5">
+    <row r="683" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B683" s="109"/>
       <c r="E683" s="114"/>
     </row>
-    <row r="684" ht="15.75" customHeight="1" spans="5:5">
+    <row r="684" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B684" s="109"/>
       <c r="E684" s="114"/>
     </row>
-    <row r="685" ht="15.75" customHeight="1" spans="5:5">
+    <row r="685" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B685" s="109"/>
       <c r="E685" s="114"/>
     </row>
-    <row r="686" ht="15.75" customHeight="1" spans="5:5">
+    <row r="686" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B686" s="109"/>
       <c r="E686" s="114"/>
     </row>
-    <row r="687" ht="15.75" customHeight="1" spans="5:5">
+    <row r="687" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B687" s="109"/>
       <c r="E687" s="114"/>
     </row>
-    <row r="688" ht="15.75" customHeight="1" spans="5:5">
+    <row r="688" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B688" s="109"/>
       <c r="E688" s="114"/>
     </row>
-    <row r="689" ht="15.75" customHeight="1" spans="5:5">
+    <row r="689" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B689" s="109"/>
       <c r="E689" s="114"/>
     </row>
-    <row r="690" ht="15.75" customHeight="1" spans="5:5">
+    <row r="690" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B690" s="109"/>
       <c r="E690" s="114"/>
     </row>
-    <row r="691" ht="15.75" customHeight="1" spans="5:5">
+    <row r="691" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B691" s="109"/>
       <c r="E691" s="114"/>
     </row>
-    <row r="692" ht="15.75" customHeight="1" spans="5:5">
+    <row r="692" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B692" s="109"/>
       <c r="E692" s="114"/>
     </row>
-    <row r="693" ht="15.75" customHeight="1" spans="5:5">
+    <row r="693" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B693" s="109"/>
       <c r="E693" s="114"/>
     </row>
-    <row r="694" ht="15.75" customHeight="1" spans="5:5">
+    <row r="694" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B694" s="109"/>
       <c r="E694" s="114"/>
     </row>
-    <row r="695" ht="15.75" customHeight="1" spans="5:5">
+    <row r="695" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B695" s="109"/>
       <c r="E695" s="114"/>
     </row>
-    <row r="696" ht="15.75" customHeight="1" spans="5:5">
+    <row r="696" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B696" s="109"/>
       <c r="E696" s="114"/>
     </row>
-    <row r="697" ht="15.75" customHeight="1" spans="5:5">
+    <row r="697" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B697" s="109"/>
       <c r="E697" s="114"/>
     </row>
-    <row r="698" ht="15.75" customHeight="1" spans="5:5">
+    <row r="698" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B698" s="109"/>
       <c r="E698" s="114"/>
     </row>
-    <row r="699" ht="15.75" customHeight="1" spans="5:5">
+    <row r="699" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B699" s="109"/>
       <c r="E699" s="114"/>
     </row>
-    <row r="700" ht="15.75" customHeight="1" spans="5:5">
+    <row r="700" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B700" s="109"/>
       <c r="E700" s="114"/>
     </row>
-    <row r="701" ht="15.75" customHeight="1" spans="5:5">
+    <row r="701" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B701" s="109"/>
       <c r="E701" s="114"/>
     </row>
-    <row r="702" ht="15.75" customHeight="1" spans="5:5">
+    <row r="702" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B702" s="109"/>
       <c r="E702" s="114"/>
     </row>
-    <row r="703" ht="15.75" customHeight="1" spans="5:5">
+    <row r="703" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B703" s="109"/>
       <c r="E703" s="114"/>
     </row>
-    <row r="704" ht="15.75" customHeight="1" spans="5:5">
+    <row r="704" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B704" s="109"/>
       <c r="E704" s="114"/>
     </row>
-    <row r="705" ht="15.75" customHeight="1" spans="5:5">
+    <row r="705" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B705" s="109"/>
       <c r="E705" s="114"/>
     </row>
-    <row r="706" ht="15.75" customHeight="1" spans="5:5">
+    <row r="706" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B706" s="109"/>
       <c r="E706" s="114"/>
     </row>
-    <row r="707" ht="15.75" customHeight="1" spans="5:5">
+    <row r="707" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B707" s="109"/>
       <c r="E707" s="114"/>
     </row>
-    <row r="708" ht="15.75" customHeight="1" spans="5:5">
+    <row r="708" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B708" s="109"/>
       <c r="E708" s="114"/>
     </row>
-    <row r="709" ht="15.75" customHeight="1" spans="5:5">
+    <row r="709" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B709" s="109"/>
       <c r="E709" s="114"/>
     </row>
-    <row r="710" ht="15.75" customHeight="1" spans="5:5">
+    <row r="710" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B710" s="109"/>
       <c r="E710" s="114"/>
     </row>
-    <row r="711" ht="15.75" customHeight="1" spans="5:5">
+    <row r="711" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B711" s="109"/>
       <c r="E711" s="114"/>
     </row>
-    <row r="712" ht="15.75" customHeight="1" spans="5:5">
+    <row r="712" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B712" s="109"/>
       <c r="E712" s="114"/>
     </row>
-    <row r="713" ht="15.75" customHeight="1" spans="5:5">
+    <row r="713" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B713" s="109"/>
       <c r="E713" s="114"/>
     </row>
-    <row r="714" ht="15.75" customHeight="1" spans="5:5">
+    <row r="714" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B714" s="109"/>
       <c r="E714" s="114"/>
     </row>
-    <row r="715" ht="15.75" customHeight="1" spans="5:5">
+    <row r="715" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B715" s="109"/>
       <c r="E715" s="114"/>
     </row>
-    <row r="716" ht="15.75" customHeight="1" spans="5:5">
+    <row r="716" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B716" s="109"/>
       <c r="E716" s="114"/>
     </row>
-    <row r="717" ht="15.75" customHeight="1" spans="5:5">
+    <row r="717" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B717" s="109"/>
       <c r="E717" s="114"/>
     </row>
-    <row r="718" ht="15.75" customHeight="1" spans="5:5">
+    <row r="718" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B718" s="109"/>
       <c r="E718" s="114"/>
     </row>
-    <row r="719" ht="15.75" customHeight="1" spans="5:5">
+    <row r="719" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B719" s="109"/>
       <c r="E719" s="114"/>
     </row>
-    <row r="720" ht="15.75" customHeight="1" spans="5:5">
+    <row r="720" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B720" s="109"/>
       <c r="E720" s="114"/>
     </row>
-    <row r="721" ht="15.75" customHeight="1" spans="5:5">
+    <row r="721" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B721" s="109"/>
       <c r="E721" s="114"/>
     </row>
-    <row r="722" ht="15.75" customHeight="1" spans="5:5">
+    <row r="722" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B722" s="109"/>
       <c r="E722" s="114"/>
     </row>
-    <row r="723" ht="15.75" customHeight="1" spans="5:5">
+    <row r="723" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B723" s="109"/>
       <c r="E723" s="114"/>
     </row>
-    <row r="724" ht="15.75" customHeight="1" spans="5:5">
+    <row r="724" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B724" s="109"/>
       <c r="E724" s="114"/>
     </row>
-    <row r="725" ht="15.75" customHeight="1" spans="5:5">
+    <row r="725" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B725" s="109"/>
       <c r="E725" s="114"/>
     </row>
-    <row r="726" ht="15.75" customHeight="1" spans="5:5">
+    <row r="726" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B726" s="109"/>
       <c r="E726" s="114"/>
     </row>
-    <row r="727" ht="15.75" customHeight="1" spans="5:5">
+    <row r="727" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B727" s="109"/>
       <c r="E727" s="114"/>
     </row>
-    <row r="728" ht="15.75" customHeight="1" spans="5:5">
+    <row r="728" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B728" s="109"/>
       <c r="E728" s="114"/>
     </row>
-    <row r="729" ht="15.75" customHeight="1" spans="5:5">
+    <row r="729" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B729" s="109"/>
       <c r="E729" s="114"/>
     </row>
-    <row r="730" ht="15.75" customHeight="1" spans="5:5">
+    <row r="730" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B730" s="109"/>
       <c r="E730" s="114"/>
     </row>
-    <row r="731" ht="15.75" customHeight="1" spans="5:5">
+    <row r="731" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B731" s="109"/>
       <c r="E731" s="114"/>
     </row>
-    <row r="732" ht="15.75" customHeight="1" spans="5:5">
+    <row r="732" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B732" s="109"/>
       <c r="E732" s="114"/>
     </row>
-    <row r="733" ht="15.75" customHeight="1" spans="5:5">
+    <row r="733" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B733" s="109"/>
       <c r="E733" s="114"/>
     </row>
-    <row r="734" ht="15.75" customHeight="1" spans="5:5">
+    <row r="734" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B734" s="109"/>
       <c r="E734" s="114"/>
     </row>
-    <row r="735" ht="15.75" customHeight="1" spans="5:5">
+    <row r="735" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B735" s="109"/>
       <c r="E735" s="114"/>
     </row>
-    <row r="736" ht="15.75" customHeight="1" spans="5:5">
+    <row r="736" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B736" s="109"/>
       <c r="E736" s="114"/>
     </row>
-    <row r="737" ht="15.75" customHeight="1" spans="5:5">
+    <row r="737" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B737" s="109"/>
       <c r="E737" s="114"/>
     </row>
-    <row r="738" ht="15.75" customHeight="1" spans="5:5">
+    <row r="738" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B738" s="109"/>
       <c r="E738" s="114"/>
     </row>
-    <row r="739" ht="15.75" customHeight="1" spans="5:5">
+    <row r="739" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B739" s="109"/>
       <c r="E739" s="114"/>
     </row>
-    <row r="740" ht="15.75" customHeight="1" spans="5:5">
+    <row r="740" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B740" s="109"/>
       <c r="E740" s="114"/>
     </row>
-    <row r="741" ht="15.75" customHeight="1" spans="5:5">
+    <row r="741" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B741" s="109"/>
       <c r="E741" s="114"/>
     </row>
-    <row r="742" ht="15.75" customHeight="1" spans="5:5">
+    <row r="742" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B742" s="109"/>
       <c r="E742" s="114"/>
     </row>
-    <row r="743" ht="15.75" customHeight="1" spans="5:5">
+    <row r="743" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B743" s="109"/>
       <c r="E743" s="114"/>
     </row>
-    <row r="744" ht="15.75" customHeight="1" spans="5:5">
+    <row r="744" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B744" s="109"/>
       <c r="E744" s="114"/>
     </row>
-    <row r="745" ht="15.75" customHeight="1" spans="5:5">
+    <row r="745" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B745" s="109"/>
       <c r="E745" s="114"/>
     </row>
-    <row r="746" ht="15.75" customHeight="1" spans="5:5">
+    <row r="746" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B746" s="109"/>
       <c r="E746" s="114"/>
     </row>
-    <row r="747" ht="15.75" customHeight="1" spans="5:5">
+    <row r="747" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B747" s="109"/>
       <c r="E747" s="114"/>
     </row>
-    <row r="748" ht="15.75" customHeight="1" spans="5:5">
+    <row r="748" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B748" s="109"/>
       <c r="E748" s="114"/>
     </row>
-    <row r="749" ht="15.75" customHeight="1" spans="5:5">
+    <row r="749" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B749" s="109"/>
       <c r="E749" s="114"/>
     </row>
-    <row r="750" ht="15.75" customHeight="1" spans="5:5">
+    <row r="750" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B750" s="109"/>
       <c r="E750" s="114"/>
     </row>
-    <row r="751" ht="15.75" customHeight="1" spans="5:5">
+    <row r="751" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B751" s="109"/>
       <c r="E751" s="114"/>
     </row>
-    <row r="752" ht="15.75" customHeight="1" spans="5:5">
+    <row r="752" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B752" s="109"/>
       <c r="E752" s="114"/>
     </row>
-    <row r="753" ht="15.75" customHeight="1" spans="5:5">
+    <row r="753" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B753" s="109"/>
       <c r="E753" s="114"/>
     </row>
-    <row r="754" ht="15.75" customHeight="1" spans="5:5">
+    <row r="754" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B754" s="109"/>
       <c r="E754" s="114"/>
     </row>
-    <row r="755" ht="15.75" customHeight="1" spans="5:5">
+    <row r="755" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B755" s="109"/>
       <c r="E755" s="114"/>
     </row>
-    <row r="756" ht="15.75" customHeight="1" spans="5:5">
+    <row r="756" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B756" s="109"/>
       <c r="E756" s="114"/>
     </row>
-    <row r="757" ht="15.75" customHeight="1" spans="5:5">
+    <row r="757" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B757" s="109"/>
       <c r="E757" s="114"/>
     </row>
-    <row r="758" ht="15.75" customHeight="1" spans="5:5">
+    <row r="758" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B758" s="109"/>
       <c r="E758" s="114"/>
     </row>
-    <row r="759" ht="15.75" customHeight="1" spans="5:5">
+    <row r="759" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B759" s="109"/>
       <c r="E759" s="114"/>
     </row>
-    <row r="760" ht="15.75" customHeight="1" spans="5:5">
+    <row r="760" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B760" s="109"/>
       <c r="E760" s="114"/>
     </row>
-    <row r="761" ht="15.75" customHeight="1" spans="5:5">
+    <row r="761" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B761" s="109"/>
       <c r="E761" s="114"/>
     </row>
-    <row r="762" ht="15.75" customHeight="1" spans="5:5">
+    <row r="762" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B762" s="109"/>
       <c r="E762" s="114"/>
     </row>
-    <row r="763" ht="15.75" customHeight="1" spans="5:5">
+    <row r="763" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B763" s="109"/>
       <c r="E763" s="114"/>
     </row>
-    <row r="764" ht="15.75" customHeight="1" spans="5:5">
+    <row r="764" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B764" s="109"/>
       <c r="E764" s="114"/>
     </row>
-    <row r="765" ht="15.75" customHeight="1" spans="5:5">
+    <row r="765" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B765" s="109"/>
       <c r="E765" s="114"/>
     </row>
-    <row r="766" ht="15.75" customHeight="1" spans="5:5">
+    <row r="766" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B766" s="109"/>
       <c r="E766" s="114"/>
     </row>
-    <row r="767" ht="15.75" customHeight="1" spans="5:5">
+    <row r="767" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B767" s="109"/>
       <c r="E767" s="114"/>
     </row>
-    <row r="768" ht="15.75" customHeight="1" spans="5:5">
+    <row r="768" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B768" s="109"/>
       <c r="E768" s="114"/>
     </row>
-    <row r="769" ht="15.75" customHeight="1" spans="5:5">
+    <row r="769" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B769" s="109"/>
       <c r="E769" s="114"/>
     </row>
-    <row r="770" ht="15.75" customHeight="1" spans="5:5">
+    <row r="770" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B770" s="109"/>
       <c r="E770" s="114"/>
     </row>
-    <row r="771" ht="15.75" customHeight="1" spans="5:5">
+    <row r="771" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B771" s="109"/>
       <c r="E771" s="114"/>
     </row>
-    <row r="772" ht="15.75" customHeight="1" spans="5:5">
+    <row r="772" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B772" s="109"/>
       <c r="E772" s="114"/>
     </row>
-    <row r="773" ht="15.75" customHeight="1" spans="5:5">
+    <row r="773" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B773" s="109"/>
       <c r="E773" s="114"/>
     </row>
-    <row r="774" ht="15.75" customHeight="1" spans="5:5">
+    <row r="774" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B774" s="109"/>
       <c r="E774" s="114"/>
     </row>
-    <row r="775" ht="15.75" customHeight="1" spans="5:5">
+    <row r="775" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B775" s="109"/>
       <c r="E775" s="114"/>
     </row>
-    <row r="776" ht="15.75" customHeight="1" spans="5:5">
+    <row r="776" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B776" s="109"/>
       <c r="E776" s="114"/>
     </row>
-    <row r="777" ht="15.75" customHeight="1" spans="5:5">
+    <row r="777" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B777" s="109"/>
       <c r="E777" s="114"/>
     </row>
-    <row r="778" ht="15.75" customHeight="1" spans="5:5">
+    <row r="778" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B778" s="109"/>
       <c r="E778" s="114"/>
     </row>
-    <row r="779" ht="15.75" customHeight="1" spans="5:5">
+    <row r="779" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B779" s="109"/>
       <c r="E779" s="114"/>
     </row>
-    <row r="780" ht="15.75" customHeight="1" spans="5:5">
+    <row r="780" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B780" s="109"/>
       <c r="E780" s="114"/>
     </row>
-    <row r="781" ht="15.75" customHeight="1" spans="5:5">
+    <row r="781" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B781" s="109"/>
       <c r="E781" s="114"/>
     </row>
-    <row r="782" ht="15.75" customHeight="1" spans="5:5">
+    <row r="782" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B782" s="109"/>
       <c r="E782" s="114"/>
     </row>
-    <row r="783" ht="15.75" customHeight="1" spans="5:5">
+    <row r="783" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B783" s="109"/>
       <c r="E783" s="114"/>
     </row>
-    <row r="784" ht="15.75" customHeight="1" spans="5:5">
+    <row r="784" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B784" s="109"/>
       <c r="E784" s="114"/>
     </row>
-    <row r="785" ht="15.75" customHeight="1" spans="5:5">
+    <row r="785" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B785" s="109"/>
       <c r="E785" s="114"/>
     </row>
-    <row r="786" ht="15.75" customHeight="1" spans="5:5">
+    <row r="786" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B786" s="109"/>
       <c r="E786" s="114"/>
     </row>
-    <row r="787" ht="15.75" customHeight="1" spans="5:5">
+    <row r="787" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B787" s="109"/>
       <c r="E787" s="114"/>
     </row>
-    <row r="788" ht="15.75" customHeight="1" spans="5:5">
+    <row r="788" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B788" s="109"/>
       <c r="E788" s="114"/>
     </row>
-    <row r="789" ht="15.75" customHeight="1" spans="5:5">
+    <row r="789" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B789" s="109"/>
       <c r="E789" s="114"/>
     </row>
-    <row r="790" ht="15.75" customHeight="1" spans="5:5">
+    <row r="790" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B790" s="109"/>
       <c r="E790" s="114"/>
     </row>
-    <row r="791" ht="15.75" customHeight="1" spans="5:5">
+    <row r="791" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B791" s="109"/>
       <c r="E791" s="114"/>
     </row>
-    <row r="792" ht="15.75" customHeight="1" spans="5:5">
+    <row r="792" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B792" s="109"/>
       <c r="E792" s="114"/>
     </row>
-    <row r="793" ht="15.75" customHeight="1" spans="5:5">
+    <row r="793" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B793" s="109"/>
       <c r="E793" s="114"/>
     </row>
-    <row r="794" ht="15.75" customHeight="1" spans="5:5">
+    <row r="794" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B794" s="109"/>
       <c r="E794" s="114"/>
     </row>
-    <row r="795" ht="15.75" customHeight="1" spans="5:5">
+    <row r="795" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B795" s="109"/>
       <c r="E795" s="114"/>
     </row>
-    <row r="796" ht="15.75" customHeight="1" spans="5:5">
+    <row r="796" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B796" s="109"/>
       <c r="E796" s="114"/>
     </row>
-    <row r="797" ht="15.75" customHeight="1" spans="5:5">
+    <row r="797" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B797" s="109"/>
       <c r="E797" s="114"/>
     </row>
-    <row r="798" ht="15.75" customHeight="1" spans="5:5">
+    <row r="798" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B798" s="109"/>
       <c r="E798" s="114"/>
     </row>
-    <row r="799" ht="15.75" customHeight="1" spans="5:5">
+    <row r="799" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B799" s="109"/>
       <c r="E799" s="114"/>
     </row>
-    <row r="800" ht="15.75" customHeight="1" spans="5:5">
+    <row r="800" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B800" s="109"/>
       <c r="E800" s="114"/>
     </row>
-    <row r="801" ht="15.75" customHeight="1" spans="5:5">
+    <row r="801" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B801" s="109"/>
       <c r="E801" s="114"/>
     </row>
-    <row r="802" ht="15.75" customHeight="1" spans="5:5">
+    <row r="802" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B802" s="109"/>
       <c r="E802" s="114"/>
     </row>
-    <row r="803" ht="15.75" customHeight="1" spans="5:5">
+    <row r="803" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B803" s="109"/>
       <c r="E803" s="114"/>
     </row>
-    <row r="804" ht="15.75" customHeight="1" spans="5:5">
+    <row r="804" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B804" s="109"/>
       <c r="E804" s="114"/>
     </row>
-    <row r="805" ht="15.75" customHeight="1" spans="5:5">
+    <row r="805" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B805" s="109"/>
       <c r="E805" s="114"/>
     </row>
-    <row r="806" ht="15.75" customHeight="1" spans="5:5">
+    <row r="806" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B806" s="109"/>
       <c r="E806" s="114"/>
     </row>
-    <row r="807" ht="15.75" customHeight="1" spans="5:5">
+    <row r="807" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B807" s="109"/>
       <c r="E807" s="114"/>
     </row>
-    <row r="808" ht="15.75" customHeight="1" spans="5:5">
+    <row r="808" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B808" s="109"/>
       <c r="E808" s="114"/>
     </row>
-    <row r="809" ht="15.75" customHeight="1" spans="5:5">
+    <row r="809" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B809" s="109"/>
       <c r="E809" s="114"/>
     </row>
-    <row r="810" ht="15.75" customHeight="1" spans="5:5">
+    <row r="810" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B810" s="109"/>
       <c r="E810" s="114"/>
     </row>
-    <row r="811" ht="15.75" customHeight="1" spans="5:5">
+    <row r="811" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B811" s="109"/>
       <c r="E811" s="114"/>
     </row>
-    <row r="812" ht="15.75" customHeight="1" spans="5:5">
+    <row r="812" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B812" s="109"/>
       <c r="E812" s="114"/>
     </row>
-    <row r="813" ht="15.75" customHeight="1" spans="5:5">
+    <row r="813" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B813" s="109"/>
       <c r="E813" s="114"/>
     </row>
-    <row r="814" ht="15.75" customHeight="1" spans="5:5">
+    <row r="814" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B814" s="109"/>
       <c r="E814" s="114"/>
     </row>
-    <row r="815" ht="15.75" customHeight="1" spans="5:5">
+    <row r="815" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B815" s="109"/>
       <c r="E815" s="114"/>
     </row>
-    <row r="816" ht="15.75" customHeight="1" spans="5:5">
+    <row r="816" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B816" s="109"/>
       <c r="E816" s="114"/>
     </row>
-    <row r="817" ht="15.75" customHeight="1" spans="5:5">
+    <row r="817" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B817" s="109"/>
       <c r="E817" s="114"/>
     </row>
-    <row r="818" ht="15.75" customHeight="1" spans="5:5">
+    <row r="818" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B818" s="109"/>
       <c r="E818" s="114"/>
     </row>
-    <row r="819" ht="15.75" customHeight="1" spans="5:5">
+    <row r="819" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B819" s="109"/>
       <c r="E819" s="114"/>
     </row>
-    <row r="820" ht="15.75" customHeight="1" spans="5:5">
+    <row r="820" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B820" s="109"/>
       <c r="E820" s="114"/>
     </row>
-    <row r="821" ht="15.75" customHeight="1" spans="5:5">
+    <row r="821" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B821" s="109"/>
       <c r="E821" s="114"/>
     </row>
-    <row r="822" ht="15.75" customHeight="1" spans="5:5">
+    <row r="822" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B822" s="109"/>
       <c r="E822" s="114"/>
     </row>
-    <row r="823" ht="15.75" customHeight="1" spans="5:5">
+    <row r="823" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B823" s="109"/>
       <c r="E823" s="114"/>
     </row>
-    <row r="824" ht="15.75" customHeight="1" spans="5:5">
+    <row r="824" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B824" s="109"/>
       <c r="E824" s="114"/>
     </row>
-    <row r="825" ht="15.75" customHeight="1" spans="5:5">
+    <row r="825" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B825" s="109"/>
       <c r="E825" s="114"/>
     </row>
-    <row r="826" ht="15.75" customHeight="1" spans="5:5">
+    <row r="826" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B826" s="109"/>
       <c r="E826" s="114"/>
     </row>
-    <row r="827" ht="15.75" customHeight="1" spans="5:5">
+    <row r="827" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B827" s="109"/>
       <c r="E827" s="114"/>
     </row>
-    <row r="828" ht="15.75" customHeight="1" spans="5:5">
+    <row r="828" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B828" s="109"/>
       <c r="E828" s="114"/>
     </row>
-    <row r="829" ht="15.75" customHeight="1" spans="5:5">
+    <row r="829" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B829" s="109"/>
       <c r="E829" s="114"/>
     </row>
-    <row r="830" ht="15.75" customHeight="1" spans="5:5">
+    <row r="830" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B830" s="109"/>
       <c r="E830" s="114"/>
     </row>
-    <row r="831" ht="15.75" customHeight="1" spans="5:5">
+    <row r="831" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B831" s="109"/>
       <c r="E831" s="114"/>
     </row>
-    <row r="832" ht="15.75" customHeight="1" spans="5:5">
+    <row r="832" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B832" s="109"/>
       <c r="E832" s="114"/>
     </row>
-    <row r="833" ht="15.75" customHeight="1" spans="5:5">
+    <row r="833" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B833" s="109"/>
       <c r="E833" s="114"/>
     </row>
-    <row r="834" ht="15.75" customHeight="1" spans="5:5">
+    <row r="834" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B834" s="109"/>
       <c r="E834" s="114"/>
     </row>
-    <row r="835" ht="15.75" customHeight="1" spans="5:5">
+    <row r="835" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B835" s="109"/>
       <c r="E835" s="114"/>
     </row>
-    <row r="836" ht="15.75" customHeight="1" spans="5:5">
+    <row r="836" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B836" s="109"/>
       <c r="E836" s="114"/>
     </row>
-    <row r="837" ht="15.75" customHeight="1" spans="5:5">
+    <row r="837" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B837" s="109"/>
       <c r="E837" s="114"/>
     </row>
-    <row r="838" ht="15.75" customHeight="1" spans="5:5">
+    <row r="838" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B838" s="109"/>
       <c r="E838" s="114"/>
     </row>
-    <row r="839" ht="15.75" customHeight="1" spans="5:5">
+    <row r="839" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B839" s="109"/>
       <c r="E839" s="114"/>
     </row>
-    <row r="840" ht="15.75" customHeight="1" spans="5:5">
+    <row r="840" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B840" s="109"/>
       <c r="E840" s="114"/>
     </row>
-    <row r="841" ht="15.75" customHeight="1" spans="5:5">
+    <row r="841" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B841" s="109"/>
       <c r="E841" s="114"/>
     </row>
-    <row r="842" ht="15.75" customHeight="1" spans="5:5">
+    <row r="842" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B842" s="109"/>
       <c r="E842" s="114"/>
     </row>
-    <row r="843" ht="15.75" customHeight="1" spans="5:5">
+    <row r="843" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B843" s="109"/>
       <c r="E843" s="114"/>
     </row>
-    <row r="844" ht="15.75" customHeight="1" spans="5:5">
+    <row r="844" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B844" s="109"/>
       <c r="E844" s="114"/>
     </row>
-    <row r="845" ht="15.75" customHeight="1" spans="5:5">
+    <row r="845" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B845" s="109"/>
       <c r="E845" s="114"/>
     </row>
-    <row r="846" ht="15.75" customHeight="1" spans="5:5">
+    <row r="846" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B846" s="109"/>
       <c r="E846" s="114"/>
     </row>
-    <row r="847" ht="15.75" customHeight="1" spans="5:5">
+    <row r="847" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B847" s="109"/>
       <c r="E847" s="114"/>
     </row>
-    <row r="848" ht="15.75" customHeight="1" spans="5:5">
+    <row r="848" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B848" s="109"/>
       <c r="E848" s="114"/>
     </row>
-    <row r="849" ht="15.75" customHeight="1" spans="5:5">
+    <row r="849" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B849" s="109"/>
       <c r="E849" s="114"/>
     </row>
-    <row r="850" ht="15.75" customHeight="1" spans="5:5">
+    <row r="850" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B850" s="109"/>
       <c r="E850" s="114"/>
     </row>
-    <row r="851" ht="15.75" customHeight="1" spans="5:5">
+    <row r="851" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B851" s="109"/>
       <c r="E851" s="114"/>
     </row>
-    <row r="852" ht="15.75" customHeight="1" spans="5:5">
+    <row r="852" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B852" s="109"/>
       <c r="E852" s="114"/>
     </row>
-    <row r="853" ht="15.75" customHeight="1" spans="5:5">
+    <row r="853" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B853" s="109"/>
       <c r="E853" s="114"/>
     </row>
-    <row r="854" ht="15.75" customHeight="1" spans="5:5">
+    <row r="854" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B854" s="109"/>
       <c r="E854" s="114"/>
     </row>
-    <row r="855" ht="15.75" customHeight="1" spans="5:5">
+    <row r="855" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B855" s="109"/>
       <c r="E855" s="114"/>
     </row>
-    <row r="856" ht="15.75" customHeight="1" spans="5:5">
+    <row r="856" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B856" s="109"/>
       <c r="E856" s="114"/>
     </row>
-    <row r="857" ht="15.75" customHeight="1" spans="5:5">
+    <row r="857" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B857" s="109"/>
       <c r="E857" s="114"/>
     </row>
-    <row r="858" ht="15.75" customHeight="1" spans="5:5">
+    <row r="858" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B858" s="109"/>
       <c r="E858" s="114"/>
     </row>
-    <row r="859" ht="15.75" customHeight="1" spans="5:5">
+    <row r="859" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B859" s="109"/>
       <c r="E859" s="114"/>
     </row>
-    <row r="860" ht="15.75" customHeight="1" spans="5:5">
+    <row r="860" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B860" s="109"/>
       <c r="E860" s="114"/>
     </row>
-    <row r="861" ht="15.75" customHeight="1" spans="5:5">
+    <row r="861" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B861" s="109"/>
       <c r="E861" s="114"/>
     </row>
-    <row r="862" ht="15.75" customHeight="1" spans="5:5">
+    <row r="862" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B862" s="109"/>
       <c r="E862" s="114"/>
     </row>
-    <row r="863" ht="15.75" customHeight="1" spans="5:5">
+    <row r="863" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B863" s="109"/>
       <c r="E863" s="114"/>
     </row>
-    <row r="864" ht="15.75" customHeight="1" spans="5:5">
+    <row r="864" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B864" s="109"/>
       <c r="E864" s="114"/>
     </row>
-    <row r="865" ht="15.75" customHeight="1" spans="5:5">
+    <row r="865" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B865" s="109"/>
       <c r="E865" s="114"/>
     </row>
-    <row r="866" ht="15.75" customHeight="1" spans="5:5">
+    <row r="866" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B866" s="109"/>
       <c r="E866" s="114"/>
     </row>
-    <row r="867" ht="15.75" customHeight="1" spans="5:5">
+    <row r="867" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B867" s="109"/>
       <c r="E867" s="114"/>
     </row>
-    <row r="868" ht="15.75" customHeight="1" spans="5:5">
+    <row r="868" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B868" s="109"/>
       <c r="E868" s="114"/>
     </row>
-    <row r="869" ht="15.75" customHeight="1" spans="5:5">
+    <row r="869" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B869" s="109"/>
       <c r="E869" s="114"/>
     </row>
-    <row r="870" ht="15.75" customHeight="1" spans="5:5">
+    <row r="870" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B870" s="109"/>
       <c r="E870" s="114"/>
     </row>
-    <row r="871" ht="15.75" customHeight="1" spans="5:5">
+    <row r="871" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B871" s="109"/>
       <c r="E871" s="114"/>
     </row>
-    <row r="872" ht="15.75" customHeight="1" spans="5:5">
+    <row r="872" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B872" s="109"/>
       <c r="E872" s="114"/>
     </row>
-    <row r="873" ht="15.75" customHeight="1" spans="5:5">
+    <row r="873" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B873" s="109"/>
       <c r="E873" s="114"/>
     </row>
-    <row r="874" ht="15.75" customHeight="1" spans="5:5">
+    <row r="874" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B874" s="109"/>
       <c r="E874" s="114"/>
     </row>
-    <row r="875" ht="15.75" customHeight="1" spans="5:5">
+    <row r="875" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B875" s="109"/>
       <c r="E875" s="114"/>
     </row>
-    <row r="876" ht="15.75" customHeight="1" spans="5:5">
+    <row r="876" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B876" s="109"/>
       <c r="E876" s="114"/>
     </row>
-    <row r="877" ht="15.75" customHeight="1" spans="5:5">
+    <row r="877" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B877" s="109"/>
       <c r="E877" s="114"/>
     </row>
-    <row r="878" ht="15.75" customHeight="1" spans="5:5">
+    <row r="878" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B878" s="109"/>
       <c r="E878" s="114"/>
     </row>
-    <row r="879" ht="15.75" customHeight="1" spans="5:5">
+    <row r="879" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B879" s="109"/>
       <c r="E879" s="114"/>
     </row>
-    <row r="880" ht="15.75" customHeight="1" spans="5:5">
+    <row r="880" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B880" s="109"/>
       <c r="E880" s="114"/>
     </row>
-    <row r="881" ht="15.75" customHeight="1" spans="5:5">
+    <row r="881" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B881" s="109"/>
       <c r="E881" s="114"/>
     </row>
-    <row r="882" ht="15.75" customHeight="1" spans="5:5">
+    <row r="882" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B882" s="109"/>
       <c r="E882" s="114"/>
     </row>
-    <row r="883" ht="15.75" customHeight="1" spans="5:5">
+    <row r="883" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B883" s="109"/>
       <c r="E883" s="114"/>
     </row>
-    <row r="884" ht="15.75" customHeight="1" spans="5:5">
+    <row r="884" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B884" s="109"/>
       <c r="E884" s="114"/>
     </row>
-    <row r="885" ht="15.75" customHeight="1" spans="5:5">
+    <row r="885" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B885" s="109"/>
       <c r="E885" s="114"/>
     </row>
-    <row r="886" ht="15.75" customHeight="1" spans="5:5">
+    <row r="886" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B886" s="109"/>
       <c r="E886" s="114"/>
     </row>
-    <row r="887" ht="15.75" customHeight="1" spans="5:5">
+    <row r="887" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B887" s="109"/>
       <c r="E887" s="114"/>
     </row>
-    <row r="888" ht="15.75" customHeight="1" spans="5:5">
+    <row r="888" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B888" s="109"/>
       <c r="E888" s="114"/>
     </row>
-    <row r="889" ht="15.75" customHeight="1" spans="5:5">
+    <row r="889" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B889" s="109"/>
       <c r="E889" s="114"/>
     </row>
-    <row r="890" ht="15.75" customHeight="1" spans="5:5">
+    <row r="890" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B890" s="109"/>
       <c r="E890" s="114"/>
     </row>
-    <row r="891" ht="15.75" customHeight="1" spans="5:5">
+    <row r="891" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B891" s="109"/>
       <c r="E891" s="114"/>
     </row>
-    <row r="892" ht="15.75" customHeight="1" spans="5:5">
+    <row r="892" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B892" s="109"/>
       <c r="E892" s="114"/>
     </row>
-    <row r="893" ht="15.75" customHeight="1" spans="5:5">
+    <row r="893" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B893" s="109"/>
       <c r="E893" s="114"/>
     </row>
-    <row r="894" ht="15.75" customHeight="1" spans="5:5">
+    <row r="894" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B894" s="109"/>
       <c r="E894" s="114"/>
     </row>
-    <row r="895" ht="15.75" customHeight="1" spans="5:5">
+    <row r="895" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B895" s="109"/>
       <c r="E895" s="114"/>
     </row>
-    <row r="896" ht="15.75" customHeight="1" spans="5:5">
+    <row r="896" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B896" s="109"/>
       <c r="E896" s="114"/>
     </row>
-    <row r="897" ht="15.75" customHeight="1" spans="5:5">
+    <row r="897" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B897" s="109"/>
       <c r="E897" s="114"/>
     </row>
-    <row r="898" ht="15.75" customHeight="1" spans="5:5">
+    <row r="898" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B898" s="109"/>
       <c r="E898" s="114"/>
     </row>
-    <row r="899" ht="15.75" customHeight="1" spans="5:5">
+    <row r="899" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B899" s="109"/>
       <c r="E899" s="114"/>
     </row>
-    <row r="900" ht="15.75" customHeight="1" spans="5:5">
+    <row r="900" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B900" s="109"/>
       <c r="E900" s="114"/>
     </row>
-    <row r="901" ht="15.75" customHeight="1" spans="5:5">
+    <row r="901" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B901" s="109"/>
       <c r="E901" s="114"/>
     </row>
-    <row r="902" ht="15.75" customHeight="1" spans="5:5">
+    <row r="902" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B902" s="109"/>
       <c r="E902" s="114"/>
     </row>
-    <row r="903" ht="15.75" customHeight="1" spans="5:5">
+    <row r="903" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B903" s="109"/>
       <c r="E903" s="114"/>
     </row>
-    <row r="904" ht="15.75" customHeight="1" spans="5:5">
+    <row r="904" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B904" s="109"/>
       <c r="E904" s="114"/>
     </row>
-    <row r="905" ht="15.75" customHeight="1" spans="5:5">
+    <row r="905" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B905" s="109"/>
       <c r="E905" s="114"/>
     </row>
-    <row r="906" ht="15.75" customHeight="1" spans="5:5">
+    <row r="906" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B906" s="109"/>
       <c r="E906" s="114"/>
     </row>
-    <row r="907" ht="15.75" customHeight="1" spans="5:5">
+    <row r="907" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B907" s="109"/>
       <c r="E907" s="114"/>
     </row>
-    <row r="908" ht="15.75" customHeight="1" spans="5:5">
+    <row r="908" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B908" s="109"/>
       <c r="E908" s="114"/>
     </row>
-    <row r="909" ht="15.75" customHeight="1" spans="5:5">
+    <row r="909" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B909" s="109"/>
       <c r="E909" s="114"/>
     </row>
-    <row r="910" ht="15.75" customHeight="1" spans="5:5">
+    <row r="910" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B910" s="109"/>
       <c r="E910" s="114"/>
     </row>
-    <row r="911" ht="15.75" customHeight="1" spans="5:5">
+    <row r="911" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B911" s="109"/>
       <c r="E911" s="114"/>
     </row>
-    <row r="912" ht="15.75" customHeight="1" spans="5:5">
+    <row r="912" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B912" s="109"/>
       <c r="E912" s="114"/>
     </row>
-    <row r="913" ht="15.75" customHeight="1" spans="5:5">
+    <row r="913" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B913" s="109"/>
       <c r="E913" s="114"/>
     </row>
-    <row r="914" ht="15.75" customHeight="1" spans="5:5">
+    <row r="914" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B914" s="109"/>
       <c r="E914" s="114"/>
     </row>
-    <row r="915" ht="15.75" customHeight="1" spans="5:5">
+    <row r="915" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B915" s="109"/>
       <c r="E915" s="114"/>
     </row>
-    <row r="916" ht="15.75" customHeight="1" spans="5:5">
+    <row r="916" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B916" s="109"/>
       <c r="E916" s="114"/>
     </row>
-    <row r="917" ht="15.75" customHeight="1" spans="5:5">
+    <row r="917" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B917" s="109"/>
       <c r="E917" s="114"/>
     </row>
-    <row r="918" ht="15.75" customHeight="1" spans="5:5">
+    <row r="918" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B918" s="109"/>
       <c r="E918" s="114"/>
     </row>
-    <row r="919" ht="15.75" customHeight="1" spans="5:5">
+    <row r="919" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B919" s="109"/>
       <c r="E919" s="114"/>
     </row>
-    <row r="920" ht="15.75" customHeight="1" spans="5:5">
+    <row r="920" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B920" s="109"/>
       <c r="E920" s="114"/>
     </row>
-    <row r="921" ht="15.75" customHeight="1" spans="5:5">
+    <row r="921" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B921" s="109"/>
       <c r="E921" s="114"/>
     </row>
-    <row r="922" ht="15.75" customHeight="1" spans="5:5">
+    <row r="922" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B922" s="109"/>
       <c r="E922" s="114"/>
     </row>
-    <row r="923" ht="15.75" customHeight="1" spans="5:5">
+    <row r="923" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B923" s="109"/>
       <c r="E923" s="114"/>
     </row>
-    <row r="924" ht="15.75" customHeight="1" spans="5:5">
+    <row r="924" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B924" s="109"/>
       <c r="E924" s="114"/>
     </row>
-    <row r="925" ht="15.75" customHeight="1" spans="5:5">
+    <row r="925" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B925" s="109"/>
       <c r="E925" s="114"/>
     </row>
-    <row r="926" ht="15.75" customHeight="1" spans="5:5">
+    <row r="926" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B926" s="109"/>
       <c r="E926" s="114"/>
     </row>
-    <row r="927" ht="15.75" customHeight="1" spans="5:5">
+    <row r="927" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B927" s="109"/>
       <c r="E927" s="114"/>
     </row>
-    <row r="928" ht="15.75" customHeight="1" spans="5:5">
+    <row r="928" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B928" s="109"/>
       <c r="E928" s="114"/>
     </row>
-    <row r="929" ht="15.75" customHeight="1" spans="5:5">
+    <row r="929" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B929" s="109"/>
       <c r="E929" s="114"/>
     </row>
-    <row r="930" ht="15.75" customHeight="1" spans="5:5">
+    <row r="930" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B930" s="109"/>
       <c r="E930" s="114"/>
     </row>
-    <row r="931" ht="15.75" customHeight="1" spans="5:5">
+    <row r="931" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B931" s="109"/>
       <c r="E931" s="114"/>
     </row>
-    <row r="932" ht="15.75" customHeight="1" spans="5:5">
+    <row r="932" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B932" s="109"/>
       <c r="E932" s="114"/>
     </row>
-    <row r="933" ht="15.75" customHeight="1" spans="5:5">
+    <row r="933" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B933" s="109"/>
       <c r="E933" s="114"/>
     </row>
-    <row r="934" ht="15.75" customHeight="1" spans="5:5">
+    <row r="934" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B934" s="109"/>
       <c r="E934" s="114"/>
     </row>
-    <row r="935" ht="15.75" customHeight="1" spans="5:5">
+    <row r="935" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B935" s="109"/>
       <c r="E935" s="114"/>
     </row>
-    <row r="936" ht="15.75" customHeight="1" spans="5:5">
+    <row r="936" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B936" s="109"/>
       <c r="E936" s="114"/>
     </row>
-    <row r="937" ht="15.75" customHeight="1" spans="5:5">
+    <row r="937" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B937" s="109"/>
       <c r="E937" s="114"/>
     </row>
-    <row r="938" ht="15.75" customHeight="1" spans="5:5">
+    <row r="938" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B938" s="109"/>
       <c r="E938" s="114"/>
     </row>
-    <row r="939" ht="15.75" customHeight="1" spans="5:5">
+    <row r="939" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B939" s="109"/>
       <c r="E939" s="114"/>
     </row>
-    <row r="940" ht="15.75" customHeight="1" spans="5:5">
+    <row r="940" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B940" s="109"/>
       <c r="E940" s="114"/>
     </row>
-    <row r="941" ht="15.75" customHeight="1" spans="5:5">
+    <row r="941" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B941" s="109"/>
       <c r="E941" s="114"/>
     </row>
-    <row r="942" ht="15.75" customHeight="1" spans="5:5">
+    <row r="942" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B942" s="109"/>
       <c r="E942" s="114"/>
     </row>
-    <row r="943" ht="15.75" customHeight="1" spans="5:5">
+    <row r="943" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B943" s="109"/>
       <c r="E943" s="114"/>
     </row>
-    <row r="944" ht="15.75" customHeight="1" spans="5:5">
+    <row r="944" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B944" s="109"/>
       <c r="E944" s="114"/>
     </row>
-    <row r="945" ht="15.75" customHeight="1" spans="5:5">
+    <row r="945" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B945" s="109"/>
       <c r="E945" s="114"/>
     </row>
-    <row r="946" ht="15.75" customHeight="1" spans="5:5">
+    <row r="946" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B946" s="109"/>
       <c r="E946" s="114"/>
     </row>
-    <row r="947" ht="15.75" customHeight="1" spans="5:5">
+    <row r="947" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B947" s="109"/>
       <c r="E947" s="114"/>
     </row>
-    <row r="948" ht="15.75" customHeight="1" spans="5:5">
+    <row r="948" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B948" s="109"/>
       <c r="E948" s="114"/>
     </row>
-    <row r="949" ht="15.75" customHeight="1" spans="5:5">
+    <row r="949" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B949" s="109"/>
       <c r="E949" s="114"/>
     </row>
-    <row r="950" ht="15.75" customHeight="1" spans="5:5">
+    <row r="950" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B950" s="109"/>
       <c r="E950" s="114"/>
     </row>
-    <row r="951" ht="15.75" customHeight="1" spans="5:5">
+    <row r="951" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B951" s="109"/>
       <c r="E951" s="114"/>
     </row>
-    <row r="952" ht="15.75" customHeight="1" spans="5:5">
+    <row r="952" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B952" s="109"/>
       <c r="E952" s="114"/>
     </row>
-    <row r="953" ht="15.75" customHeight="1" spans="5:5">
+    <row r="953" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B953" s="109"/>
       <c r="E953" s="114"/>
     </row>
-    <row r="954" ht="15.75" customHeight="1" spans="5:5">
+    <row r="954" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B954" s="109"/>
       <c r="E954" s="114"/>
     </row>
-    <row r="955" ht="15.75" customHeight="1" spans="5:5">
+    <row r="955" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B955" s="109"/>
       <c r="E955" s="114"/>
     </row>
-    <row r="956" ht="15.75" customHeight="1" spans="5:5">
+    <row r="956" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B956" s="109"/>
       <c r="E956" s="114"/>
     </row>
-    <row r="957" ht="15.75" customHeight="1" spans="5:5">
+    <row r="957" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B957" s="109"/>
       <c r="E957" s="114"/>
     </row>
-    <row r="958" ht="15.75" customHeight="1" spans="5:5">
+    <row r="958" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B958" s="109"/>
       <c r="E958" s="114"/>
     </row>
-    <row r="959" ht="15.75" customHeight="1" spans="5:5">
+    <row r="959" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B959" s="109"/>
       <c r="E959" s="114"/>
     </row>
-    <row r="960" ht="15.75" customHeight="1" spans="5:5">
+    <row r="960" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B960" s="109"/>
       <c r="E960" s="114"/>
     </row>
-    <row r="961" ht="15.75" customHeight="1" spans="5:5">
+    <row r="961" s="107" customFormat="1" ht="15.75" customHeight="1" spans="2:5">
+      <c r="B961" s="109"/>
       <c r="E961" s="114"/>
     </row>
   </sheetData>
@@ -9945,7 +10766,7 @@
       <c r="B2" s="47"/>
       <c r="C2" s="47"/>
       <c r="D2" s="50" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E2" s="50"/>
       <c r="F2" s="51"/>
@@ -9958,7 +10779,7 @@
       <c r="B3" s="47"/>
       <c r="C3" s="47"/>
       <c r="D3" s="52" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E3" s="52"/>
       <c r="F3" s="51"/>
@@ -9977,7 +10798,7 @@
       <c r="C5" s="54"/>
       <c r="D5" s="54"/>
       <c r="E5" s="54" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F5" s="54"/>
       <c r="G5" s="54"/>
@@ -9995,7 +10816,7 @@
       <c r="C6" s="54"/>
       <c r="D6" s="54"/>
       <c r="E6" s="54" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F6" s="54"/>
       <c r="G6" s="54"/>
@@ -10029,43 +10850,43 @@
         <v>13</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C8" s="56" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="56" t="s">
+        <v>168</v>
+      </c>
+      <c r="E8" s="56" t="s">
+        <v>169</v>
+      </c>
+      <c r="F8" s="56" t="s">
+        <v>170</v>
+      </c>
+      <c r="G8" s="56" t="s">
         <v>171</v>
       </c>
-      <c r="E8" s="56" t="s">
+      <c r="H8" s="56" t="s">
         <v>172</v>
       </c>
-      <c r="F8" s="56" t="s">
+      <c r="I8" s="56" t="s">
         <v>173</v>
       </c>
-      <c r="G8" s="56" t="s">
+      <c r="J8" s="92" t="s">
         <v>174</v>
       </c>
-      <c r="H8" s="56" t="s">
+      <c r="K8" s="93" t="s">
         <v>175</v>
       </c>
-      <c r="I8" s="56" t="s">
+      <c r="L8" s="92" t="s">
         <v>176</v>
       </c>
-      <c r="J8" s="92" t="s">
+      <c r="M8" s="92" t="s">
         <v>177</v>
       </c>
-      <c r="K8" s="93" t="s">
+      <c r="N8" s="92" t="s">
         <v>178</v>
-      </c>
-      <c r="L8" s="92" t="s">
-        <v>179</v>
-      </c>
-      <c r="M8" s="92" t="s">
-        <v>180</v>
-      </c>
-      <c r="N8" s="92" t="s">
-        <v>181</v>
       </c>
       <c r="O8" s="94" t="s">
         <v>21</v>
@@ -10073,7 +10894,7 @@
     </row>
     <row r="9" s="44" customFormat="1" ht="29.25" customHeight="1" spans="1:15">
       <c r="A9" s="57" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B9" s="58"/>
       <c r="C9" s="58"/>
@@ -10139,7 +10960,7 @@
     </row>
     <row r="11" s="44" customFormat="1" ht="23.25" customHeight="1" spans="1:15">
       <c r="A11" s="57" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B11" s="58"/>
       <c r="C11" s="58"/>
@@ -10202,7 +11023,7 @@
     </row>
     <row r="13" s="44" customFormat="1" ht="38.4" customHeight="1" spans="1:17">
       <c r="A13" s="57" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B13" s="58"/>
       <c r="C13" s="58"/>
@@ -10266,7 +11087,7 @@
     </row>
     <row r="15" s="44" customFormat="1" ht="38.4" customHeight="1" spans="1:17">
       <c r="A15" s="57" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B15" s="58"/>
       <c r="C15" s="58"/>
@@ -10338,7 +11159,7 @@
     </row>
     <row r="17" s="44" customFormat="1" ht="38.4" customHeight="1" spans="1:17">
       <c r="A17" s="57" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B17" s="58"/>
       <c r="C17" s="58"/>
@@ -10402,7 +11223,7 @@
     </row>
     <row r="19" s="44" customFormat="1" ht="38.4" customHeight="1" spans="1:17">
       <c r="A19" s="57" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B19" s="58"/>
       <c r="C19" s="58"/>
@@ -10466,7 +11287,7 @@
     </row>
     <row r="21" s="44" customFormat="1" ht="38.4" customHeight="1" spans="1:15">
       <c r="A21" s="57" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B21" s="58"/>
       <c r="C21" s="58"/>
@@ -10529,7 +11350,7 @@
     </row>
     <row r="23" s="46" customFormat="1" ht="33" customHeight="1" spans="1:15">
       <c r="A23" s="81" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B23" s="82"/>
       <c r="C23" s="82"/>
@@ -10575,7 +11396,7 @@
     </row>
     <row r="24" s="46" customFormat="1" ht="17.25" customHeight="1" spans="3:14">
       <c r="C24" s="85" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D24" s="85"/>
       <c r="E24" s="85"/>
@@ -10594,7 +11415,7 @@
     </row>
     <row r="25" s="46" customFormat="1" ht="17.25" customHeight="1" spans="3:15">
       <c r="C25" s="86" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D25" s="86"/>
       <c r="E25" s="86"/>
@@ -10614,7 +11435,7 @@
     </row>
     <row r="26" s="46" customFormat="1" ht="17.25" customHeight="1" spans="3:14">
       <c r="C26" s="86" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D26" s="86"/>
       <c r="E26" s="86"/>
@@ -10633,7 +11454,7 @@
     </row>
     <row r="27" s="46" customFormat="1" ht="17.25" customHeight="1" spans="3:14">
       <c r="C27" s="46" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D27" s="86"/>
       <c r="E27" s="86"/>
@@ -10647,7 +11468,7 @@
       </c>
       <c r="K27" s="102"/>
       <c r="L27" s="100" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="M27" s="103"/>
       <c r="N27" s="103"/>
@@ -10666,7 +11487,7 @@
     </row>
     <row r="29" s="47" customFormat="1" spans="1:15">
       <c r="A29" s="87" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B29" s="87"/>
       <c r="C29" s="87"/>
@@ -10681,7 +11502,7 @@
       <c r="L29" s="89"/>
       <c r="M29" s="89"/>
       <c r="N29" s="89" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="O29" s="89"/>
     </row>
@@ -10690,7 +11511,7 @@
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="89" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B36" s="89"/>
       <c r="C36" s="89"/>
@@ -10702,7 +11523,7 @@
       <c r="L36" s="89"/>
       <c r="M36" s="89"/>
       <c r="N36" s="89" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O36" s="89"/>
     </row>
@@ -10814,15 +11635,15 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="18.65" customHeight="1" spans="3:6">
       <c r="C1" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="18.65" customHeight="1" spans="3:7">
       <c r="C2" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>3</v>
@@ -10831,11 +11652,11 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="18.65" customHeight="1" spans="3:7">
       <c r="C3" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D3" s="4"/>
       <c r="F3" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G3" s="4"/>
     </row>
@@ -10849,7 +11670,7 @@
     </row>
     <row r="5" s="1" customFormat="1" ht="15" customHeight="1" spans="1:10">
       <c r="A5" s="11" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -10863,7 +11684,7 @@
     </row>
     <row r="6" s="1" customFormat="1" ht="15" customHeight="1" spans="1:10">
       <c r="A6" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -10877,7 +11698,7 @@
     </row>
     <row r="7" s="1" customFormat="1" ht="15" customHeight="1" spans="1:10">
       <c r="A7" s="12" t="s">
-        <v>131</v>
+        <v>197</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
@@ -10891,7 +11712,7 @@
     </row>
     <row r="8" s="1" customFormat="1" ht="15" customHeight="1" spans="1:10">
       <c r="A8" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
@@ -10911,29 +11732,29 @@
         <v>13</v>
       </c>
       <c r="B10" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="D10" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="E10" s="13" t="s">
         <v>202</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>204</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="I10" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="J10" s="13" t="s">
         <v>206</v>
-      </c>
-      <c r="I10" s="37" t="s">
-        <v>207</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:10">
@@ -10942,10 +11763,10 @@
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
       <c r="E11" s="13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="13"/>
@@ -10954,16 +11775,16 @@
     </row>
     <row r="12" ht="19.25" customHeight="1" spans="1:10">
       <c r="A12" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="D12" s="16" t="s">
         <v>212</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>214</v>
       </c>
       <c r="E12" s="16">
         <v>1</v>
@@ -11081,14 +11902,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="J19" s="33"/>
     </row>
     <row r="20" ht="19.4" customHeight="1" spans="1:10">
       <c r="A20" s="34" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B20" s="35"/>
       <c r="C20" s="35"/>
@@ -11107,7 +11925,7 @@
       <c r="B22" s="8"/>
       <c r="D22" s="11"/>
       <c r="H22" s="12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I22" s="41"/>
       <c r="J22" s="41"/>

--- a/public/templates/cac_mau_doi_soat_v3.xlsx
+++ b/public/templates/cac_mau_doi_soat_v3.xlsx
@@ -11550,7 +11550,7 @@
       <c r="I27" s="73"/>
       <c r="J27" s="73"/>
       <c r="K27" s="90">
-        <f>G23-O23-K26</f>
+        <f>O23-K26</f>
         <v>0</v>
       </c>
       <c r="L27" s="90"/>
